--- a/table/resources/sample/WinPosWeight.xlsx
+++ b/table/resources/sample/WinPosWeight.xlsx
@@ -14952,7 +14952,7 @@
         <v>35</v>
       </c>
       <c r="I264" s="2">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="J264" s="2">
         <v>0</v>
@@ -14996,7 +14996,7 @@
         <v>35</v>
       </c>
       <c r="I265" s="2">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="J265" s="2">
         <v>0</v>
@@ -15040,7 +15040,7 @@
         <v>35</v>
       </c>
       <c r="I266" s="2">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="J266" s="2">
         <v>0</v>
@@ -15084,7 +15084,7 @@
         <v>35</v>
       </c>
       <c r="I267" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J267" s="2">
         <v>0</v>
@@ -15128,7 +15128,7 @@
         <v>35</v>
       </c>
       <c r="I268" s="2">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="J268" s="2">
         <v>0</v>
@@ -15172,7 +15172,7 @@
         <v>35</v>
       </c>
       <c r="I269" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J269" s="2">
         <v>0</v>
@@ -15216,7 +15216,7 @@
         <v>35</v>
       </c>
       <c r="I270" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J270" s="2">
         <v>0</v>
@@ -15260,7 +15260,7 @@
         <v>35</v>
       </c>
       <c r="I271" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J271" s="2">
         <v>0</v>
@@ -15304,7 +15304,7 @@
         <v>35</v>
       </c>
       <c r="I272" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J272" s="2">
         <v>0</v>

--- a/table/resources/sample/WinPosWeight.xlsx
+++ b/table/resources/sample/WinPosWeight.xlsx
@@ -15040,7 +15040,7 @@
         <v>35</v>
       </c>
       <c r="I266" s="2">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="J266" s="2">
         <v>0</v>
@@ -15128,7 +15128,7 @@
         <v>35</v>
       </c>
       <c r="I268" s="2">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="J268" s="2">
         <v>0</v>

--- a/table/resources/sample/WinPosWeight.xlsx
+++ b/table/resources/sample/WinPosWeight.xlsx
@@ -5209,10 +5209,10 @@
         <v>35</v>
       </c>
       <c r="I59" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J59" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L59" s="2">
         <v>1</v>
@@ -5257,10 +5257,10 @@
         <v>35</v>
       </c>
       <c r="I60" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J60" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L60" s="2">
         <v>1</v>
@@ -5305,10 +5305,10 @@
         <v>35</v>
       </c>
       <c r="I61" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J61" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L61" s="2">
         <v>1</v>
@@ -5353,10 +5353,10 @@
         <v>35</v>
       </c>
       <c r="I62" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J62" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L62" s="2">
         <v>1</v>
@@ -5401,10 +5401,10 @@
         <v>35</v>
       </c>
       <c r="I63" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J63" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L63" s="2">
         <v>1</v>
@@ -5449,10 +5449,10 @@
         <v>35</v>
       </c>
       <c r="I64" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J64" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L64" s="2">
         <v>1</v>
@@ -5497,10 +5497,10 @@
         <v>35</v>
       </c>
       <c r="I65" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J65" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L65" s="2">
         <v>1</v>
@@ -5545,10 +5545,10 @@
         <v>35</v>
       </c>
       <c r="I66" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J66" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L66" s="2">
         <v>1</v>
@@ -5593,10 +5593,10 @@
         <v>35</v>
       </c>
       <c r="I67" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J67" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L67" s="2">
         <v>1</v>
@@ -5641,10 +5641,10 @@
         <v>35</v>
       </c>
       <c r="I68" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J68" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L68" s="2">
         <v>1</v>
@@ -5689,10 +5689,10 @@
         <v>35</v>
       </c>
       <c r="I69" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J69" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L69" s="2">
         <v>1</v>
@@ -5737,10 +5737,10 @@
         <v>35</v>
       </c>
       <c r="I70" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J70" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L70" s="2">
         <v>1</v>
@@ -5785,10 +5785,10 @@
         <v>35</v>
       </c>
       <c r="I71" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J71" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L71" s="2">
         <v>1</v>
@@ -5833,10 +5833,10 @@
         <v>35</v>
       </c>
       <c r="I72" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J72" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L72" s="2">
         <v>1</v>
@@ -5881,10 +5881,10 @@
         <v>35</v>
       </c>
       <c r="I73" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J73" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L73" s="2">
         <v>1</v>
@@ -5929,10 +5929,10 @@
         <v>35</v>
       </c>
       <c r="I74" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J74" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L74" s="2">
         <v>1</v>
@@ -5977,10 +5977,10 @@
         <v>35</v>
       </c>
       <c r="I75" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J75" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L75" s="2">
         <v>1</v>
@@ -6025,10 +6025,10 @@
         <v>35</v>
       </c>
       <c r="I76" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J76" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L76" s="2">
         <v>1</v>
@@ -6073,10 +6073,10 @@
         <v>35</v>
       </c>
       <c r="I77" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J77" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L77" s="2">
         <v>1</v>
@@ -6121,10 +6121,10 @@
         <v>35</v>
       </c>
       <c r="I78" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J78" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L78" s="2">
         <v>1</v>
@@ -6169,10 +6169,10 @@
         <v>35</v>
       </c>
       <c r="I79" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J79" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L79" s="2">
         <v>1</v>
@@ -6217,10 +6217,10 @@
         <v>35</v>
       </c>
       <c r="I80" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J80" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L80" s="2">
         <v>1</v>
@@ -6265,10 +6265,10 @@
         <v>35</v>
       </c>
       <c r="I81" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J81" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L81" s="2">
         <v>1</v>
@@ -6313,10 +6313,10 @@
         <v>35</v>
       </c>
       <c r="I82" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J82" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="L82" s="2">
         <v>1</v>
@@ -14957,6 +14957,7 @@
       <c r="J264" s="2">
         <v>0</v>
       </c>
+      <c r="K264" s="2"/>
       <c r="L264" s="2">
         <v>1</v>
       </c>
@@ -15001,6 +15002,7 @@
       <c r="J265" s="2">
         <v>0</v>
       </c>
+      <c r="K265" s="2"/>
       <c r="L265" s="2">
         <v>1</v>
       </c>
@@ -15045,6 +15047,7 @@
       <c r="J266" s="2">
         <v>0</v>
       </c>
+      <c r="K266" s="2"/>
       <c r="L266" s="2">
         <v>1</v>
       </c>
@@ -15084,11 +15087,12 @@
         <v>35</v>
       </c>
       <c r="I267" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J267" s="2">
-        <v>0</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="K267" s="2"/>
       <c r="L267" s="2">
         <v>1</v>
       </c>
@@ -15133,6 +15137,7 @@
       <c r="J268" s="2">
         <v>0</v>
       </c>
+      <c r="K268" s="2"/>
       <c r="L268" s="2">
         <v>1</v>
       </c>
@@ -15172,11 +15177,12 @@
         <v>35</v>
       </c>
       <c r="I269" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J269" s="2">
-        <v>0</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="K269" s="2"/>
       <c r="L269" s="2">
         <v>1</v>
       </c>
@@ -15216,11 +15222,12 @@
         <v>35</v>
       </c>
       <c r="I270" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J270" s="2">
-        <v>0</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="K270" s="2"/>
       <c r="L270" s="2">
         <v>1</v>
       </c>
@@ -15260,11 +15267,12 @@
         <v>35</v>
       </c>
       <c r="I271" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J271" s="2">
-        <v>0</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="K271" s="2"/>
       <c r="L271" s="2">
         <v>1</v>
       </c>
@@ -15304,11 +15312,12 @@
         <v>35</v>
       </c>
       <c r="I272" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J272" s="2">
-        <v>0</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="K272" s="2"/>
       <c r="L272" s="2">
         <v>1</v>
       </c>
@@ -15354,6 +15363,7 @@
       <c r="J273" s="2">
         <v>10000</v>
       </c>
+      <c r="K273" s="2"/>
       <c r="L273" s="2">
         <v>1</v>
       </c>

--- a/table/resources/sample/WinPosWeight.xlsx
+++ b/table/resources/sample/WinPosWeight.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="WinPosWeight" sheetId="20" r:id="rId1"/>
@@ -148,12 +148,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="D108" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+结果为和时，由服务器处理返还【庄】【闲】的下注</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="374">
   <si>
     <t>开奖结果ID</t>
   </si>
@@ -566,16 +588,28 @@
     <t>百家乐</t>
   </si>
   <si>
+    <t>庄对 B Pair</t>
+  </si>
+  <si>
     <t>B Pair</t>
   </si>
   <si>
     <t>Tie</t>
   </si>
   <si>
+    <t>闲对 P Pair</t>
+  </si>
+  <si>
     <t>P Pair</t>
   </si>
   <si>
+    <t>闲赢 Player win</t>
+  </si>
+  <si>
     <t>Player</t>
+  </si>
+  <si>
+    <t>庄赢 Bank win</t>
   </si>
   <si>
     <t>Banker</t>
@@ -2382,7 +2416,7 @@
     <col min="1" max="1" width="11.625" style="2"/>
     <col min="2" max="2" width="12.375" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.625" style="2" customWidth="1"/>
     <col min="6" max="9" width="11.125" style="2" customWidth="1"/>
     <col min="10" max="12" width="17.125" style="2" customWidth="1"/>
@@ -7501,7 +7535,7 @@
         <v>20050001</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O107" s="2">
         <v>20050001</v>
@@ -7521,7 +7555,7 @@
         <v>136</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E108" s="2">
         <v>2</v>
@@ -7548,7 +7582,7 @@
         <v>20050002</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O108" s="2">
         <v>20050002</v>
@@ -7568,7 +7602,7 @@
         <v>136</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E109" s="2">
         <v>3</v>
@@ -7595,7 +7629,7 @@
         <v>20050003</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O109" s="2">
         <v>20050003</v>
@@ -7615,7 +7649,7 @@
         <v>136</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E110" s="2">
         <v>4</v>
@@ -7642,7 +7676,7 @@
         <v>20050004</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="O110" s="2">
         <v>20050004</v>
@@ -7662,7 +7696,7 @@
         <v>136</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E111" s="2">
         <v>5</v>
@@ -7689,7 +7723,7 @@
         <v>20050005</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="O111" s="2">
         <v>20050005</v>
@@ -7706,7 +7740,7 @@
         <v>200600</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D112" s="2">
         <v>111</v>
@@ -7733,7 +7767,7 @@
         <v>1</v>
       </c>
       <c r="M112" s="14" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N112" s="2">
         <v>111</v>
@@ -7750,7 +7784,7 @@
         <v>200600</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D113" s="2">
         <v>112</v>
@@ -7777,10 +7811,10 @@
         <v>1</v>
       </c>
       <c r="M113" s="14" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="O113" s="16">
         <v>20060009</v>
@@ -7794,7 +7828,7 @@
         <v>200600</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D114" s="2">
         <v>113</v>
@@ -7821,10 +7855,10 @@
         <v>1</v>
       </c>
       <c r="M114" s="14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O114" s="16">
         <v>20060010</v>
@@ -7838,7 +7872,7 @@
         <v>200600</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D115" s="2">
         <v>114</v>
@@ -7865,10 +7899,10 @@
         <v>1</v>
       </c>
       <c r="M115" s="14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="O115" s="16">
         <v>20060011</v>
@@ -7882,7 +7916,7 @@
         <v>200600</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D116" s="2">
         <v>115</v>
@@ -7909,10 +7943,10 @@
         <v>1</v>
       </c>
       <c r="M116" s="14" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="O116" s="16">
         <v>20060012</v>
@@ -7926,7 +7960,7 @@
         <v>200600</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D117" s="2">
         <v>116</v>
@@ -7953,10 +7987,10 @@
         <v>1</v>
       </c>
       <c r="M117" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O117" s="16">
         <v>20060013</v>
@@ -7970,7 +8004,7 @@
         <v>200600</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D118" s="2">
         <v>122</v>
@@ -7997,10 +8031,10 @@
         <v>1</v>
       </c>
       <c r="M118" s="14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O118" s="16">
         <v>20060010</v>
@@ -8014,7 +8048,7 @@
         <v>200600</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D119" s="2">
         <v>123</v>
@@ -8041,10 +8075,10 @@
         <v>1</v>
       </c>
       <c r="M119" s="14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="O119" s="16">
         <v>20060011</v>
@@ -8058,7 +8092,7 @@
         <v>200600</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D120" s="2">
         <v>124</v>
@@ -8085,10 +8119,10 @@
         <v>1</v>
       </c>
       <c r="M120" s="14" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="O120" s="16">
         <v>20060012</v>
@@ -8102,7 +8136,7 @@
         <v>200600</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D121" s="2">
         <v>125</v>
@@ -8129,10 +8163,10 @@
         <v>1</v>
       </c>
       <c r="M121" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O121" s="16">
         <v>20060013</v>
@@ -8146,7 +8180,7 @@
         <v>200600</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D122" s="2">
         <v>126</v>
@@ -8173,10 +8207,10 @@
         <v>1</v>
       </c>
       <c r="M122" s="14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O122" s="16">
         <v>20060014</v>
@@ -8190,7 +8224,7 @@
         <v>200600</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D123" s="2">
         <v>133</v>
@@ -8217,10 +8251,10 @@
         <v>1</v>
       </c>
       <c r="M123" s="14" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="O123" s="16">
         <v>20060012</v>
@@ -8234,7 +8268,7 @@
         <v>200600</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D124" s="2">
         <v>134</v>
@@ -8261,10 +8295,10 @@
         <v>1</v>
       </c>
       <c r="M124" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O124" s="16">
         <v>20060013</v>
@@ -8278,7 +8312,7 @@
         <v>200600</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D125" s="2">
         <v>135</v>
@@ -8305,10 +8339,10 @@
         <v>1</v>
       </c>
       <c r="M125" s="14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O125" s="16">
         <v>20060014</v>
@@ -8322,7 +8356,7 @@
         <v>200600</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D126" s="2">
         <v>136</v>
@@ -8349,10 +8383,10 @@
         <v>1</v>
       </c>
       <c r="M126" s="14" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O126" s="16">
         <v>20060015</v>
@@ -8366,7 +8400,7 @@
         <v>200600</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D127" s="2">
         <v>144</v>
@@ -8393,10 +8427,10 @@
         <v>1</v>
       </c>
       <c r="M127" s="14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O127" s="16">
         <v>20060014</v>
@@ -8410,7 +8444,7 @@
         <v>200600</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D128" s="2">
         <v>145</v>
@@ -8437,10 +8471,10 @@
         <v>1</v>
       </c>
       <c r="M128" s="14" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O128" s="16">
         <v>20060015</v>
@@ -8454,7 +8488,7 @@
         <v>200600</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D129" s="2">
         <v>146</v>
@@ -8481,10 +8515,10 @@
         <v>1</v>
       </c>
       <c r="M129" s="14" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O129" s="16">
         <v>20060016</v>
@@ -8498,7 +8532,7 @@
         <v>200600</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D130" s="2">
         <v>155</v>
@@ -8525,10 +8559,10 @@
         <v>1</v>
       </c>
       <c r="M130" s="14" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O130" s="16">
         <v>20060016</v>
@@ -8542,7 +8576,7 @@
         <v>200600</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D131" s="2">
         <v>156</v>
@@ -8569,10 +8603,10 @@
         <v>1</v>
       </c>
       <c r="M131" s="14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O131" s="16">
         <v>20060017</v>
@@ -8586,7 +8620,7 @@
         <v>200600</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D132" s="2">
         <v>166</v>
@@ -8613,10 +8647,10 @@
         <v>1</v>
       </c>
       <c r="M132" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O132" s="16">
         <v>20060018</v>
@@ -8630,7 +8664,7 @@
         <v>200600</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D133" s="2">
         <v>222</v>
@@ -8657,7 +8691,7 @@
         <v>1</v>
       </c>
       <c r="M133" s="14" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N133" s="2">
         <v>222</v>
@@ -8674,7 +8708,7 @@
         <v>200600</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D134" s="2">
         <v>223</v>
@@ -8701,10 +8735,10 @@
         <v>1</v>
       </c>
       <c r="M134" s="14" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="O134" s="16">
         <v>20060012</v>
@@ -8718,7 +8752,7 @@
         <v>200600</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D135" s="2">
         <v>224</v>
@@ -8745,10 +8779,10 @@
         <v>1</v>
       </c>
       <c r="M135" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O135" s="16">
         <v>20060013</v>
@@ -8762,7 +8796,7 @@
         <v>200600</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D136" s="2">
         <v>225</v>
@@ -8789,10 +8823,10 @@
         <v>1</v>
       </c>
       <c r="M136" s="14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O136" s="16">
         <v>20060014</v>
@@ -8806,7 +8840,7 @@
         <v>200600</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D137" s="2">
         <v>226</v>
@@ -8833,10 +8867,10 @@
         <v>1</v>
       </c>
       <c r="M137" s="14" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O137" s="16">
         <v>20060015</v>
@@ -8850,7 +8884,7 @@
         <v>200600</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D138" s="2">
         <v>233</v>
@@ -8877,10 +8911,10 @@
         <v>1</v>
       </c>
       <c r="M138" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O138" s="16">
         <v>20060013</v>
@@ -8894,7 +8928,7 @@
         <v>200600</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D139" s="2">
         <v>234</v>
@@ -8921,10 +8955,10 @@
         <v>1</v>
       </c>
       <c r="M139" s="14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O139" s="16">
         <v>20060014</v>
@@ -8938,7 +8972,7 @@
         <v>200600</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D140" s="2">
         <v>235</v>
@@ -8965,10 +8999,10 @@
         <v>1</v>
       </c>
       <c r="M140" s="14" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O140" s="16">
         <v>20060015</v>
@@ -8982,7 +9016,7 @@
         <v>200600</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D141" s="2">
         <v>236</v>
@@ -9009,10 +9043,10 @@
         <v>1</v>
       </c>
       <c r="M141" s="14" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O141" s="16">
         <v>20060016</v>
@@ -9026,7 +9060,7 @@
         <v>200600</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D142" s="2">
         <v>244</v>
@@ -9053,10 +9087,10 @@
         <v>1</v>
       </c>
       <c r="M142" s="14" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O142" s="16">
         <v>20060015</v>
@@ -9070,7 +9104,7 @@
         <v>200600</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D143" s="2">
         <v>245</v>
@@ -9097,10 +9131,10 @@
         <v>1</v>
       </c>
       <c r="M143" s="14" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O143" s="16">
         <v>20060016</v>
@@ -9114,7 +9148,7 @@
         <v>200600</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D144" s="2">
         <v>246</v>
@@ -9141,10 +9175,10 @@
         <v>1</v>
       </c>
       <c r="M144" s="14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O144" s="16">
         <v>20060017</v>
@@ -9158,7 +9192,7 @@
         <v>200600</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D145" s="2">
         <v>255</v>
@@ -9185,10 +9219,10 @@
         <v>1</v>
       </c>
       <c r="M145" s="14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O145" s="16">
         <v>20060017</v>
@@ -9202,7 +9236,7 @@
         <v>200600</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D146" s="2">
         <v>256</v>
@@ -9229,10 +9263,10 @@
         <v>1</v>
       </c>
       <c r="M146" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N146" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O146" s="16">
         <v>20060018</v>
@@ -9246,7 +9280,7 @@
         <v>200600</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D147" s="2">
         <v>266</v>
@@ -9273,10 +9307,10 @@
         <v>1</v>
       </c>
       <c r="M147" s="14" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O147" s="16">
         <v>20060019</v>
@@ -9290,7 +9324,7 @@
         <v>200600</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D148" s="2">
         <v>333</v>
@@ -9317,7 +9351,7 @@
         <v>1</v>
       </c>
       <c r="M148" s="14" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="N148" s="2">
         <v>333</v>
@@ -9334,7 +9368,7 @@
         <v>200600</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D149" s="2">
         <v>334</v>
@@ -9361,10 +9395,10 @@
         <v>1</v>
       </c>
       <c r="M149" s="14" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O149" s="16">
         <v>20060015</v>
@@ -9378,7 +9412,7 @@
         <v>200600</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D150" s="2">
         <v>335</v>
@@ -9405,10 +9439,10 @@
         <v>1</v>
       </c>
       <c r="M150" s="14" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="N150" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O150" s="16">
         <v>20060016</v>
@@ -9422,7 +9456,7 @@
         <v>200600</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D151" s="2">
         <v>336</v>
@@ -9449,10 +9483,10 @@
         <v>1</v>
       </c>
       <c r="M151" s="14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="N151" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O151" s="16">
         <v>20060017</v>
@@ -9466,7 +9500,7 @@
         <v>200600</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D152" s="2">
         <v>344</v>
@@ -9493,10 +9527,10 @@
         <v>1</v>
       </c>
       <c r="M152" s="14" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O152" s="16">
         <v>20060016</v>
@@ -9510,7 +9544,7 @@
         <v>200600</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D153" s="2">
         <v>345</v>
@@ -9537,10 +9571,10 @@
         <v>1</v>
       </c>
       <c r="M153" s="14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="N153" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O153" s="16">
         <v>20060017</v>
@@ -9554,7 +9588,7 @@
         <v>200600</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D154" s="2">
         <v>346</v>
@@ -9581,10 +9615,10 @@
         <v>1</v>
       </c>
       <c r="M154" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N154" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O154" s="16">
         <v>20060018</v>
@@ -9598,7 +9632,7 @@
         <v>200600</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D155" s="2">
         <v>355</v>
@@ -9625,10 +9659,10 @@
         <v>1</v>
       </c>
       <c r="M155" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N155" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O155" s="16">
         <v>20060018</v>
@@ -9642,7 +9676,7 @@
         <v>200600</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D156" s="2">
         <v>356</v>
@@ -9669,10 +9703,10 @@
         <v>1</v>
       </c>
       <c r="M156" s="14" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N156" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O156" s="16">
         <v>20060019</v>
@@ -9686,7 +9720,7 @@
         <v>200600</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D157" s="2">
         <v>366</v>
@@ -9713,10 +9747,10 @@
         <v>1</v>
       </c>
       <c r="M157" s="14" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N157" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="O157" s="16">
         <v>20060020</v>
@@ -9730,7 +9764,7 @@
         <v>200600</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D158" s="2">
         <v>444</v>
@@ -9757,7 +9791,7 @@
         <v>1</v>
       </c>
       <c r="M158" s="14" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="N158" s="2">
         <v>444</v>
@@ -9774,7 +9808,7 @@
         <v>200600</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D159" s="2">
         <v>445</v>
@@ -9801,10 +9835,10 @@
         <v>1</v>
       </c>
       <c r="M159" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N159" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O159" s="16">
         <v>20060018</v>
@@ -9818,7 +9852,7 @@
         <v>200600</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D160" s="2">
         <v>446</v>
@@ -9845,10 +9879,10 @@
         <v>1</v>
       </c>
       <c r="M160" s="14" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N160" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O160" s="16">
         <v>20060019</v>
@@ -9862,7 +9896,7 @@
         <v>200600</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D161" s="2">
         <v>455</v>
@@ -9889,10 +9923,10 @@
         <v>1</v>
       </c>
       <c r="M161" s="14" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N161" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O161" s="16">
         <v>20060019</v>
@@ -9906,7 +9940,7 @@
         <v>200600</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D162" s="2">
         <v>456</v>
@@ -9933,10 +9967,10 @@
         <v>1</v>
       </c>
       <c r="M162" s="14" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N162" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="O162" s="16">
         <v>20060020</v>
@@ -9950,7 +9984,7 @@
         <v>200600</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D163" s="2">
         <v>466</v>
@@ -9977,10 +10011,10 @@
         <v>1</v>
       </c>
       <c r="M163" s="14" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="N163" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="O163" s="16">
         <v>20060021</v>
@@ -9994,7 +10028,7 @@
         <v>200600</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D164" s="2">
         <v>555</v>
@@ -10021,7 +10055,7 @@
         <v>1</v>
       </c>
       <c r="M164" s="14" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="N164" s="2">
         <v>555</v>
@@ -10038,7 +10072,7 @@
         <v>200600</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D165" s="2">
         <v>556</v>
@@ -10065,10 +10099,10 @@
         <v>1</v>
       </c>
       <c r="M165" s="14" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="N165" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="O165" s="16">
         <v>20060021</v>
@@ -10082,7 +10116,7 @@
         <v>200600</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D166" s="2">
         <v>566</v>
@@ -10109,10 +10143,10 @@
         <v>1</v>
       </c>
       <c r="M166" s="14" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="N166" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="O166" s="16">
         <v>20060022</v>
@@ -10126,7 +10160,7 @@
         <v>200600</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D167" s="2">
         <v>666</v>
@@ -10153,7 +10187,7 @@
         <v>1</v>
       </c>
       <c r="M167" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="N167" s="2">
         <v>666</v>
@@ -10170,7 +10204,7 @@
         <v>200600</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D168" s="2">
         <v>111</v>
@@ -10197,10 +10231,10 @@
         <v>1</v>
       </c>
       <c r="M168" s="14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N168" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O168" s="16">
         <v>20060004</v>
@@ -10214,7 +10248,7 @@
         <v>200600</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D169" s="2">
         <v>111</v>
@@ -10241,10 +10275,10 @@
         <v>1</v>
       </c>
       <c r="M169" s="14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="N169" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="O169" s="16">
         <v>20060023</v>
@@ -10258,7 +10292,7 @@
         <v>200600</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D170" s="2">
         <v>112</v>
@@ -10285,16 +10319,16 @@
         <v>1</v>
       </c>
       <c r="M170" s="14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="N170" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O170" s="16">
         <v>20060008</v>
       </c>
       <c r="P170" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q170" s="16">
         <v>20060024</v>
@@ -10308,7 +10342,7 @@
         <v>200600</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D171" s="2">
         <v>112</v>
@@ -10335,10 +10369,10 @@
         <v>1</v>
       </c>
       <c r="M171" s="14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="N171" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="O171" s="16">
         <v>20060023</v>
@@ -10352,7 +10386,7 @@
         <v>200600</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D172" s="2">
         <v>113</v>
@@ -10379,16 +10413,16 @@
         <v>1</v>
       </c>
       <c r="M172" s="14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N172" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O172" s="16">
         <v>20060008</v>
       </c>
       <c r="P172" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q172" s="16">
         <v>20060025</v>
@@ -10402,7 +10436,7 @@
         <v>200600</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D173" s="2">
         <v>113</v>
@@ -10429,10 +10463,10 @@
         <v>1</v>
       </c>
       <c r="M173" s="14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="N173" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="O173" s="16">
         <v>20060023</v>
@@ -10446,7 +10480,7 @@
         <v>200600</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D174" s="2">
         <v>114</v>
@@ -10473,16 +10507,16 @@
         <v>1</v>
       </c>
       <c r="M174" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="N174" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="N174" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="O174" s="16">
         <v>20060008</v>
       </c>
       <c r="P174" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q174" s="16">
         <v>20060026</v>
@@ -10496,7 +10530,7 @@
         <v>200600</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D175" s="2">
         <v>114</v>
@@ -10523,10 +10557,10 @@
         <v>1</v>
       </c>
       <c r="M175" s="14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="N175" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="O175" s="16">
         <v>20060023</v>
@@ -10540,7 +10574,7 @@
         <v>200600</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D176" s="2">
         <v>115</v>
@@ -10567,16 +10601,16 @@
         <v>1</v>
       </c>
       <c r="M176" s="14" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="N176" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O176" s="16">
         <v>20060008</v>
       </c>
       <c r="P176" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q176" s="16">
         <v>20060027</v>
@@ -10590,7 +10624,7 @@
         <v>200600</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D177" s="2">
         <v>115</v>
@@ -10617,10 +10651,10 @@
         <v>1</v>
       </c>
       <c r="M177" s="14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="N177" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="O177" s="16">
         <v>20060023</v>
@@ -10634,7 +10668,7 @@
         <v>200600</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D178" s="2">
         <v>116</v>
@@ -10661,16 +10695,16 @@
         <v>1</v>
       </c>
       <c r="M178" s="14" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N178" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O178" s="16">
         <v>20060008</v>
       </c>
       <c r="P178" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q178" s="16">
         <v>20060028</v>
@@ -10684,7 +10718,7 @@
         <v>200600</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D179" s="2">
         <v>116</v>
@@ -10711,10 +10745,10 @@
         <v>1</v>
       </c>
       <c r="M179" s="14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="N179" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="O179" s="16">
         <v>20060023</v>
@@ -10728,7 +10762,7 @@
         <v>200600</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D180" s="2">
         <v>122</v>
@@ -10755,16 +10789,16 @@
         <v>1</v>
       </c>
       <c r="M180" s="14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N180" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O180" s="16">
         <v>20060008</v>
       </c>
       <c r="P180" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q180" s="16">
         <v>20060023</v>
@@ -10778,7 +10812,7 @@
         <v>200600</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D181" s="2">
         <v>122</v>
@@ -10805,10 +10839,10 @@
         <v>1</v>
       </c>
       <c r="M181" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N181" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="O181" s="16">
         <v>20060024</v>
@@ -10822,7 +10856,7 @@
         <v>200600</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D182" s="2">
         <v>123</v>
@@ -10849,28 +10883,28 @@
         <v>1</v>
       </c>
       <c r="M182" s="14" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N182" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O182" s="16">
         <v>20060008</v>
       </c>
       <c r="P182" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q182" s="16">
         <v>20060023</v>
       </c>
       <c r="R182" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="S182" s="16">
         <v>20060024</v>
       </c>
       <c r="T182" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="U182" s="16">
         <v>20060025</v>
@@ -10884,7 +10918,7 @@
         <v>200600</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D183" s="2">
         <v>124</v>
@@ -10911,28 +10945,28 @@
         <v>1</v>
       </c>
       <c r="M183" s="14" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="N183" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O183" s="16">
         <v>20060008</v>
       </c>
       <c r="P183" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q183" s="16">
         <v>20060023</v>
       </c>
       <c r="R183" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="S183" s="16">
         <v>20060024</v>
       </c>
       <c r="T183" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="U183" s="16">
         <v>20060026</v>
@@ -10946,7 +10980,7 @@
         <v>200600</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D184" s="2">
         <v>125</v>
@@ -10973,28 +11007,28 @@
         <v>1</v>
       </c>
       <c r="M184" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N184" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O184" s="16">
         <v>20060008</v>
       </c>
       <c r="P184" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q184" s="16">
         <v>20060023</v>
       </c>
       <c r="R184" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="S184" s="16">
         <v>20060024</v>
       </c>
       <c r="T184" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="U184" s="16">
         <v>20060027</v>
@@ -11008,7 +11042,7 @@
         <v>200600</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D185" s="2">
         <v>126</v>
@@ -11035,28 +11069,28 @@
         <v>1</v>
       </c>
       <c r="M185" s="14" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="N185" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O185" s="16">
         <v>20060008</v>
       </c>
       <c r="P185" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q185" s="16">
         <v>20060023</v>
       </c>
       <c r="R185" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="S185" s="16">
         <v>20060024</v>
       </c>
       <c r="T185" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U185" s="16">
         <v>20060028</v>
@@ -11070,7 +11104,7 @@
         <v>200600</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D186" s="2">
         <v>133</v>
@@ -11097,16 +11131,16 @@
         <v>1</v>
       </c>
       <c r="M186" s="14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N186" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O186" s="16">
         <v>20060008</v>
       </c>
       <c r="P186" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q186" s="16">
         <v>20060023</v>
@@ -11120,7 +11154,7 @@
         <v>200600</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D187" s="2">
         <v>133</v>
@@ -11147,10 +11181,10 @@
         <v>1</v>
       </c>
       <c r="M187" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N187" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="O187" s="16">
         <v>20060025</v>
@@ -11164,7 +11198,7 @@
         <v>200600</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D188" s="2">
         <v>134</v>
@@ -11191,28 +11225,28 @@
         <v>1</v>
       </c>
       <c r="M188" s="14" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N188" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O188" s="16">
         <v>20060008</v>
       </c>
       <c r="P188" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q188" s="16">
         <v>20060023</v>
       </c>
       <c r="R188" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="S188" s="16">
         <v>20060025</v>
       </c>
       <c r="T188" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="U188" s="16">
         <v>20060026</v>
@@ -11226,7 +11260,7 @@
         <v>200600</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D189" s="2">
         <v>135</v>
@@ -11253,28 +11287,28 @@
         <v>1</v>
       </c>
       <c r="M189" s="14" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="N189" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O189" s="16">
         <v>20060008</v>
       </c>
       <c r="P189" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q189" s="16">
         <v>20060023</v>
       </c>
       <c r="R189" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="S189" s="16">
         <v>20060025</v>
       </c>
       <c r="T189" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="U189" s="16">
         <v>20060027</v>
@@ -11288,7 +11322,7 @@
         <v>200600</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D190" s="2">
         <v>136</v>
@@ -11315,28 +11349,28 @@
         <v>1</v>
       </c>
       <c r="M190" s="14" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="N190" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O190" s="16">
         <v>20060008</v>
       </c>
       <c r="P190" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q190" s="16">
         <v>20060023</v>
       </c>
       <c r="R190" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="S190" s="16">
         <v>20060025</v>
       </c>
       <c r="T190" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U190" s="16">
         <v>20060028</v>
@@ -11350,7 +11384,7 @@
         <v>200600</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D191" s="2">
         <v>144</v>
@@ -11377,16 +11411,16 @@
         <v>1</v>
       </c>
       <c r="M191" s="14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N191" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O191" s="16">
         <v>20060008</v>
       </c>
       <c r="P191" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q191" s="16">
         <v>20060023</v>
@@ -11400,7 +11434,7 @@
         <v>200600</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D192" s="2">
         <v>144</v>
@@ -11427,10 +11461,10 @@
         <v>1</v>
       </c>
       <c r="M192" s="14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N192" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O192" s="16">
         <v>20060026</v>
@@ -11444,7 +11478,7 @@
         <v>200600</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D193" s="2">
         <v>145</v>
@@ -11471,28 +11505,28 @@
         <v>1</v>
       </c>
       <c r="M193" s="14" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N193" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O193" s="16">
         <v>20060008</v>
       </c>
       <c r="P193" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q193" s="16">
         <v>20060023</v>
       </c>
       <c r="R193" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="S193" s="16">
         <v>20060026</v>
       </c>
       <c r="T193" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="U193" s="16">
         <v>20060027</v>
@@ -11506,7 +11540,7 @@
         <v>200600</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D194" s="2">
         <v>146</v>
@@ -11533,28 +11567,28 @@
         <v>1</v>
       </c>
       <c r="M194" s="14" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N194" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O194" s="16">
         <v>20060029</v>
       </c>
       <c r="P194" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q194" s="16">
         <v>20060023</v>
       </c>
       <c r="R194" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="S194" s="16">
         <v>20060026</v>
       </c>
       <c r="T194" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U194" s="16">
         <v>20060028</v>
@@ -11568,7 +11602,7 @@
         <v>200600</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D195" s="2">
         <v>155</v>
@@ -11595,16 +11629,16 @@
         <v>1</v>
       </c>
       <c r="M195" s="14" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N195" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O195" s="16">
         <v>20060029</v>
       </c>
       <c r="P195" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q195" s="16">
         <v>20060023</v>
@@ -11618,7 +11652,7 @@
         <v>200600</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D196" s="2">
         <v>155</v>
@@ -11645,10 +11679,10 @@
         <v>1</v>
       </c>
       <c r="M196" s="14" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N196" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="O196" s="16">
         <v>20060027</v>
@@ -11662,7 +11696,7 @@
         <v>200600</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D197" s="2">
         <v>156</v>
@@ -11689,28 +11723,28 @@
         <v>1</v>
       </c>
       <c r="M197" s="14" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="N197" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O197" s="16">
         <v>20060029</v>
       </c>
       <c r="P197" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q197" s="16">
         <v>20060023</v>
       </c>
       <c r="R197" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="S197" s="16">
         <v>20060027</v>
       </c>
       <c r="T197" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U197" s="16">
         <v>20060028</v>
@@ -11724,7 +11758,7 @@
         <v>200600</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D198" s="2">
         <v>166</v>
@@ -11751,16 +11785,16 @@
         <v>1</v>
       </c>
       <c r="M198" s="14" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N198" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O198" s="16">
         <v>20060029</v>
       </c>
       <c r="P198" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q198" s="16">
         <v>20060023</v>
@@ -11774,7 +11808,7 @@
         <v>200600</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D199" s="2">
         <v>166</v>
@@ -11801,10 +11835,10 @@
         <v>1</v>
       </c>
       <c r="M199" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N199" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O199" s="16">
         <v>20060028</v>
@@ -11818,7 +11852,7 @@
         <v>200600</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D200" s="2">
         <v>222</v>
@@ -11845,10 +11879,10 @@
         <v>1</v>
       </c>
       <c r="M200" s="14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N200" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O200" s="16">
         <v>20060004</v>
@@ -11862,7 +11896,7 @@
         <v>200600</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D201" s="2">
         <v>222</v>
@@ -11889,10 +11923,10 @@
         <v>1</v>
       </c>
       <c r="M201" s="14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N201" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="O201" s="16">
         <v>20060011</v>
@@ -11906,7 +11940,7 @@
         <v>200600</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D202" s="2">
         <v>222</v>
@@ -11933,10 +11967,10 @@
         <v>1</v>
       </c>
       <c r="M202" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N202" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="O202" s="16">
         <v>20060024</v>
@@ -11950,7 +11984,7 @@
         <v>200600</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D203" s="2">
         <v>223</v>
@@ -11977,16 +12011,16 @@
         <v>1</v>
       </c>
       <c r="M203" s="14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N203" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O203" s="16">
         <v>20060008</v>
       </c>
       <c r="P203" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q203" s="16">
         <v>20060025</v>
@@ -12000,7 +12034,7 @@
         <v>200600</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D204" s="2">
         <v>223</v>
@@ -12027,10 +12061,10 @@
         <v>1</v>
       </c>
       <c r="M204" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N204" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="O204" s="16">
         <v>20060024</v>
@@ -12044,7 +12078,7 @@
         <v>200600</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D205" s="2">
         <v>224</v>
@@ -12071,16 +12105,16 @@
         <v>1</v>
       </c>
       <c r="M205" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="N205" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="N205" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="O205" s="16">
         <v>20060008</v>
       </c>
       <c r="P205" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q205" s="16">
         <v>20060026</v>
@@ -12094,7 +12128,7 @@
         <v>200600</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D206" s="2">
         <v>224</v>
@@ -12121,10 +12155,10 @@
         <v>1</v>
       </c>
       <c r="M206" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N206" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="O206" s="16">
         <v>20060024</v>
@@ -12138,7 +12172,7 @@
         <v>200600</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D207" s="2">
         <v>225</v>
@@ -12165,16 +12199,16 @@
         <v>1</v>
       </c>
       <c r="M207" s="14" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="N207" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O207" s="16">
         <v>20060008</v>
       </c>
       <c r="P207" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q207" s="16">
         <v>20060027</v>
@@ -12188,7 +12222,7 @@
         <v>200600</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D208" s="2">
         <v>225</v>
@@ -12215,10 +12249,10 @@
         <v>1</v>
       </c>
       <c r="M208" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N208" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="O208" s="16">
         <v>20060024</v>
@@ -12232,7 +12266,7 @@
         <v>200600</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D209" s="2">
         <v>226</v>
@@ -12259,16 +12293,16 @@
         <v>1</v>
       </c>
       <c r="M209" s="14" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N209" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O209" s="16">
         <v>20060008</v>
       </c>
       <c r="P209" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q209" s="16">
         <v>20060028</v>
@@ -12282,7 +12316,7 @@
         <v>200600</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D210" s="2">
         <v>226</v>
@@ -12309,10 +12343,10 @@
         <v>1</v>
       </c>
       <c r="M210" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N210" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="O210" s="16">
         <v>20060024</v>
@@ -12326,7 +12360,7 @@
         <v>200600</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D211" s="2">
         <v>233</v>
@@ -12353,16 +12387,16 @@
         <v>1</v>
       </c>
       <c r="M211" s="14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="N211" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O211" s="16">
         <v>20060008</v>
       </c>
       <c r="P211" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q211" s="16">
         <v>20060024</v>
@@ -12376,7 +12410,7 @@
         <v>200600</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D212" s="2">
         <v>233</v>
@@ -12403,10 +12437,10 @@
         <v>1</v>
       </c>
       <c r="M212" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N212" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="O212" s="16">
         <v>20060025</v>
@@ -12420,7 +12454,7 @@
         <v>200600</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D213" s="2">
         <v>234</v>
@@ -12447,28 +12481,28 @@
         <v>1</v>
       </c>
       <c r="M213" s="14" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N213" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O213" s="16">
         <v>20060008</v>
       </c>
       <c r="P213" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q213" s="16">
         <v>20060024</v>
       </c>
       <c r="R213" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="S213" s="16">
         <v>20060025</v>
       </c>
       <c r="T213" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="U213" s="16">
         <v>20060026</v>
@@ -12482,7 +12516,7 @@
         <v>200600</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D214" s="2">
         <v>235</v>
@@ -12509,28 +12543,28 @@
         <v>1</v>
       </c>
       <c r="M214" s="14" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="N214" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O214" s="16">
         <v>20060008</v>
       </c>
       <c r="P214" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q214" s="16">
         <v>20060024</v>
       </c>
       <c r="R214" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="S214" s="16">
         <v>20060025</v>
       </c>
       <c r="T214" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="U214" s="16">
         <v>20060027</v>
@@ -12544,7 +12578,7 @@
         <v>200600</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D215" s="2">
         <v>236</v>
@@ -12571,28 +12605,28 @@
         <v>1</v>
       </c>
       <c r="M215" s="14" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="N215" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O215" s="16">
         <v>20060029</v>
       </c>
       <c r="P215" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q215" s="16">
         <v>20060024</v>
       </c>
       <c r="R215" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="S215" s="16">
         <v>20060025</v>
       </c>
       <c r="T215" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U215" s="16">
         <v>20060028</v>
@@ -12606,7 +12640,7 @@
         <v>200600</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D216" s="2">
         <v>244</v>
@@ -12633,16 +12667,16 @@
         <v>1</v>
       </c>
       <c r="M216" s="14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="N216" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O216" s="16">
         <v>20060008</v>
       </c>
       <c r="P216" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q216" s="16">
         <v>20060024</v>
@@ -12656,7 +12690,7 @@
         <v>200600</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D217" s="2">
         <v>244</v>
@@ -12683,10 +12717,10 @@
         <v>1</v>
       </c>
       <c r="M217" s="14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N217" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O217" s="16">
         <v>20060026</v>
@@ -12700,7 +12734,7 @@
         <v>200600</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D218" s="2">
         <v>245</v>
@@ -12727,28 +12761,28 @@
         <v>1</v>
       </c>
       <c r="M218" s="14" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="N218" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O218" s="16">
         <v>20060029</v>
       </c>
       <c r="P218" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q218" s="16">
         <v>20060024</v>
       </c>
       <c r="R218" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="S218" s="16">
         <v>20060026</v>
       </c>
       <c r="T218" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="U218" s="16">
         <v>20060027</v>
@@ -12762,7 +12796,7 @@
         <v>200600</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D219" s="2">
         <v>246</v>
@@ -12789,28 +12823,28 @@
         <v>1</v>
       </c>
       <c r="M219" s="14" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N219" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O219" s="16">
         <v>20060029</v>
       </c>
       <c r="P219" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q219" s="16">
         <v>20060024</v>
       </c>
       <c r="R219" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="S219" s="16">
         <v>20060026</v>
       </c>
       <c r="T219" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U219" s="16">
         <v>20060028</v>
@@ -12824,7 +12858,7 @@
         <v>200600</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D220" s="2">
         <v>255</v>
@@ -12851,16 +12885,16 @@
         <v>1</v>
       </c>
       <c r="M220" s="14" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N220" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O220" s="16">
         <v>20060029</v>
       </c>
       <c r="P220" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q220" s="16">
         <v>20060024</v>
@@ -12874,7 +12908,7 @@
         <v>200600</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D221" s="2">
         <v>255</v>
@@ -12901,10 +12935,10 @@
         <v>1</v>
       </c>
       <c r="M221" s="14" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N221" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="O221" s="16">
         <v>20060027</v>
@@ -12918,7 +12952,7 @@
         <v>200600</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D222" s="2">
         <v>256</v>
@@ -12945,28 +12979,28 @@
         <v>1</v>
       </c>
       <c r="M222" s="14" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="N222" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O222" s="16">
         <v>20060029</v>
       </c>
       <c r="P222" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q222" s="16">
         <v>20060024</v>
       </c>
       <c r="R222" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="S222" s="16">
         <v>20060027</v>
       </c>
       <c r="T222" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U222" s="16">
         <v>20060028</v>
@@ -12980,7 +13014,7 @@
         <v>200600</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D223" s="2">
         <v>266</v>
@@ -13007,16 +13041,16 @@
         <v>1</v>
       </c>
       <c r="M223" s="14" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N223" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O223" s="16">
         <v>20060029</v>
       </c>
       <c r="P223" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q223" s="16">
         <v>20060024</v>
@@ -13030,7 +13064,7 @@
         <v>200600</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D224" s="2">
         <v>266</v>
@@ -13057,10 +13091,10 @@
         <v>1</v>
       </c>
       <c r="M224" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N224" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O224" s="16">
         <v>20060028</v>
@@ -13074,7 +13108,7 @@
         <v>200600</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D225" s="2">
         <v>333</v>
@@ -13101,10 +13135,10 @@
         <v>1</v>
       </c>
       <c r="M225" s="14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N225" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O225" s="16">
         <v>20060004</v>
@@ -13118,7 +13152,7 @@
         <v>200600</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D226" s="2">
         <v>333</v>
@@ -13145,10 +13179,10 @@
         <v>1</v>
       </c>
       <c r="M226" s="14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N226" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O226" s="16">
         <v>20060014</v>
@@ -13162,7 +13196,7 @@
         <v>200600</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D227" s="2">
         <v>333</v>
@@ -13189,10 +13223,10 @@
         <v>1</v>
       </c>
       <c r="M227" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N227" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="O227" s="16">
         <v>20060025</v>
@@ -13206,7 +13240,7 @@
         <v>200600</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D228" s="2">
         <v>334</v>
@@ -13233,16 +13267,16 @@
         <v>1</v>
       </c>
       <c r="M228" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="N228" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="N228" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="O228" s="16">
         <v>20060008</v>
       </c>
       <c r="P228" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q228" s="16">
         <v>20060026</v>
@@ -13256,7 +13290,7 @@
         <v>200600</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D229" s="2">
         <v>334</v>
@@ -13283,10 +13317,10 @@
         <v>1</v>
       </c>
       <c r="M229" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N229" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="O229" s="16">
         <v>20060025</v>
@@ -13300,7 +13334,7 @@
         <v>200600</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D230" s="2">
         <v>335</v>
@@ -13327,16 +13361,16 @@
         <v>1</v>
       </c>
       <c r="M230" s="14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N230" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O230" s="16">
         <v>20060029</v>
       </c>
       <c r="P230" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q230" s="16">
         <v>20060027</v>
@@ -13350,7 +13384,7 @@
         <v>200600</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D231" s="2">
         <v>335</v>
@@ -13377,10 +13411,10 @@
         <v>1</v>
       </c>
       <c r="M231" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N231" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="O231" s="16">
         <v>20060025</v>
@@ -13394,7 +13428,7 @@
         <v>200600</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D232" s="2">
         <v>336</v>
@@ -13421,16 +13455,16 @@
         <v>1</v>
       </c>
       <c r="M232" s="14" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="N232" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O232" s="16">
         <v>20060029</v>
       </c>
       <c r="P232" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q232" s="16">
         <v>20060028</v>
@@ -13444,7 +13478,7 @@
         <v>200600</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D233" s="2">
         <v>336</v>
@@ -13471,10 +13505,10 @@
         <v>1</v>
       </c>
       <c r="M233" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N233" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="O233" s="16">
         <v>20060025</v>
@@ -13488,7 +13522,7 @@
         <v>200600</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D234" s="2">
         <v>344</v>
@@ -13515,16 +13549,16 @@
         <v>1</v>
       </c>
       <c r="M234" s="14" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N234" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O234" s="16">
         <v>20060029</v>
       </c>
       <c r="P234" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q234" s="16">
         <v>20060025</v>
@@ -13538,7 +13572,7 @@
         <v>200600</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D235" s="2">
         <v>344</v>
@@ -13565,10 +13599,10 @@
         <v>1</v>
       </c>
       <c r="M235" s="14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N235" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O235" s="16">
         <v>20060026</v>
@@ -13582,7 +13616,7 @@
         <v>200600</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D236" s="2">
         <v>345</v>
@@ -13609,28 +13643,28 @@
         <v>1</v>
       </c>
       <c r="M236" s="14" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N236" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O236" s="16">
         <v>20060029</v>
       </c>
       <c r="P236" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q236" s="16">
         <v>20060025</v>
       </c>
       <c r="R236" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="S236" s="16">
         <v>20060026</v>
       </c>
       <c r="T236" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="U236" s="16">
         <v>20060027</v>
@@ -13644,7 +13678,7 @@
         <v>200600</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D237" s="2">
         <v>346</v>
@@ -13671,28 +13705,28 @@
         <v>1</v>
       </c>
       <c r="M237" s="14" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N237" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O237" s="16">
         <v>20060029</v>
       </c>
       <c r="P237" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q237" s="16">
         <v>20060025</v>
       </c>
       <c r="R237" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="S237" s="16">
         <v>20060026</v>
       </c>
       <c r="T237" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U237" s="16">
         <v>20060028</v>
@@ -13706,7 +13740,7 @@
         <v>200600</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D238" s="2">
         <v>355</v>
@@ -13733,16 +13767,16 @@
         <v>1</v>
       </c>
       <c r="M238" s="14" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N238" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O238" s="16">
         <v>20060029</v>
       </c>
       <c r="P238" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q238" s="16">
         <v>20060025</v>
@@ -13756,7 +13790,7 @@
         <v>200600</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D239" s="2">
         <v>355</v>
@@ -13783,10 +13817,10 @@
         <v>1</v>
       </c>
       <c r="M239" s="14" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N239" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="O239" s="16">
         <v>20060027</v>
@@ -13800,7 +13834,7 @@
         <v>200600</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D240" s="2">
         <v>356</v>
@@ -13827,28 +13861,28 @@
         <v>1</v>
       </c>
       <c r="M240" s="14" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="N240" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O240" s="16">
         <v>20060029</v>
       </c>
       <c r="P240" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q240" s="16">
         <v>20060025</v>
       </c>
       <c r="R240" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="S240" s="16">
         <v>20060027</v>
       </c>
       <c r="T240" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U240" s="16">
         <v>20060028</v>
@@ -13862,7 +13896,7 @@
         <v>200600</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D241" s="2">
         <v>366</v>
@@ -13889,16 +13923,16 @@
         <v>1</v>
       </c>
       <c r="M241" s="14" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N241" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O241" s="16">
         <v>20060029</v>
       </c>
       <c r="P241" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q241" s="16">
         <v>20060025</v>
@@ -13912,7 +13946,7 @@
         <v>200600</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D242" s="2">
         <v>366</v>
@@ -13939,10 +13973,10 @@
         <v>1</v>
       </c>
       <c r="M242" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N242" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O242" s="16">
         <v>20060028</v>
@@ -13956,7 +13990,7 @@
         <v>200600</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D243" s="2">
         <v>444</v>
@@ -13983,10 +14017,10 @@
         <v>1</v>
       </c>
       <c r="M243" s="14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N243" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O243" s="16">
         <v>20060004</v>
@@ -14000,7 +14034,7 @@
         <v>200600</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D244" s="2">
         <v>444</v>
@@ -14027,10 +14061,10 @@
         <v>1</v>
       </c>
       <c r="M244" s="14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="N244" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O244" s="16">
         <v>20060017</v>
@@ -14044,7 +14078,7 @@
         <v>200600</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D245" s="2">
         <v>444</v>
@@ -14071,10 +14105,10 @@
         <v>1</v>
       </c>
       <c r="M245" s="14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N245" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O245" s="16">
         <v>20060026</v>
@@ -14088,7 +14122,7 @@
         <v>200600</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D246" s="2">
         <v>445</v>
@@ -14115,16 +14149,16 @@
         <v>1</v>
       </c>
       <c r="M246" s="14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N246" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O246" s="16">
         <v>20060029</v>
       </c>
       <c r="P246" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q246" s="16">
         <v>20060027</v>
@@ -14138,7 +14172,7 @@
         <v>200600</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D247" s="2">
         <v>445</v>
@@ -14165,10 +14199,10 @@
         <v>1</v>
       </c>
       <c r="M247" s="14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N247" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O247" s="16">
         <v>20060026</v>
@@ -14182,7 +14216,7 @@
         <v>200600</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D248" s="2">
         <v>446</v>
@@ -14209,16 +14243,16 @@
         <v>1</v>
       </c>
       <c r="M248" s="14" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="N248" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O248" s="16">
         <v>20060029</v>
       </c>
       <c r="P248" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q248" s="16">
         <v>20060028</v>
@@ -14232,7 +14266,7 @@
         <v>200600</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D249" s="2">
         <v>446</v>
@@ -14259,10 +14293,10 @@
         <v>1</v>
       </c>
       <c r="M249" s="14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N249" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O249" s="16">
         <v>20060026</v>
@@ -14276,7 +14310,7 @@
         <v>200600</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D250" s="2">
         <v>455</v>
@@ -14303,16 +14337,16 @@
         <v>1</v>
       </c>
       <c r="M250" s="14" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N250" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O250" s="16">
         <v>20060029</v>
       </c>
       <c r="P250" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q250" s="16">
         <v>20060026</v>
@@ -14326,7 +14360,7 @@
         <v>200600</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D251" s="2">
         <v>455</v>
@@ -14353,10 +14387,10 @@
         <v>1</v>
       </c>
       <c r="M251" s="14" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N251" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="O251" s="16">
         <v>20060027</v>
@@ -14370,7 +14404,7 @@
         <v>200600</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D252" s="2">
         <v>456</v>
@@ -14397,28 +14431,28 @@
         <v>1</v>
       </c>
       <c r="M252" s="14" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="N252" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O252" s="16">
         <v>20060029</v>
       </c>
       <c r="P252" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q252" s="16">
         <v>20060026</v>
       </c>
       <c r="R252" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="S252" s="16">
         <v>20060027</v>
       </c>
       <c r="T252" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U252" s="16">
         <v>20060028</v>
@@ -14432,7 +14466,7 @@
         <v>200600</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D253" s="2">
         <v>466</v>
@@ -14459,16 +14493,16 @@
         <v>1</v>
       </c>
       <c r="M253" s="14" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N253" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O253" s="16">
         <v>20060029</v>
       </c>
       <c r="P253" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q253" s="16">
         <v>20060026</v>
@@ -14482,7 +14516,7 @@
         <v>200600</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D254" s="2">
         <v>466</v>
@@ -14509,10 +14543,10 @@
         <v>1</v>
       </c>
       <c r="M254" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N254" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O254" s="16">
         <v>20060028</v>
@@ -14526,7 +14560,7 @@
         <v>200600</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D255" s="2">
         <v>555</v>
@@ -14553,10 +14587,10 @@
         <v>1</v>
       </c>
       <c r="M255" s="14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N255" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O255" s="16">
         <v>20060004</v>
@@ -14570,7 +14604,7 @@
         <v>200600</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D256" s="2">
         <v>555</v>
@@ -14597,10 +14631,10 @@
         <v>1</v>
       </c>
       <c r="M256" s="14" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N256" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="O256" s="16">
         <v>20060020</v>
@@ -14614,7 +14648,7 @@
         <v>200600</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D257" s="2">
         <v>555</v>
@@ -14641,10 +14675,10 @@
         <v>1</v>
       </c>
       <c r="M257" s="14" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N257" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="O257" s="16">
         <v>20060027</v>
@@ -14658,7 +14692,7 @@
         <v>200600</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D258" s="2">
         <v>556</v>
@@ -14685,16 +14719,16 @@
         <v>1</v>
       </c>
       <c r="M258" s="14" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="N258" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O258" s="16">
         <v>20060029</v>
       </c>
       <c r="P258" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q258" s="16">
         <v>20060028</v>
@@ -14708,7 +14742,7 @@
         <v>200600</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D259" s="2">
         <v>556</v>
@@ -14735,10 +14769,10 @@
         <v>1</v>
       </c>
       <c r="M259" s="14" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N259" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="O259" s="16">
         <v>20060027</v>
@@ -14752,7 +14786,7 @@
         <v>200600</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D260" s="2">
         <v>566</v>
@@ -14779,16 +14813,16 @@
         <v>1</v>
       </c>
       <c r="M260" s="14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N260" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O260" s="16">
         <v>20060029</v>
       </c>
       <c r="P260" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q260" s="16">
         <v>20060027</v>
@@ -14802,7 +14836,7 @@
         <v>200600</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D261" s="2">
         <v>566</v>
@@ -14829,10 +14863,10 @@
         <v>1</v>
       </c>
       <c r="M261" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N261" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O261" s="16">
         <v>20060028</v>
@@ -14846,7 +14880,7 @@
         <v>200600</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D262" s="2">
         <v>666</v>
@@ -14873,10 +14907,10 @@
         <v>1</v>
       </c>
       <c r="M262" s="14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N262" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O262" s="16">
         <v>20060004</v>
@@ -14890,7 +14924,7 @@
         <v>200600</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D263" s="2">
         <v>666</v>
@@ -14917,10 +14951,10 @@
         <v>1</v>
       </c>
       <c r="M263" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N263" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O263" s="16">
         <v>20060028</v>
@@ -14934,10 +14968,10 @@
         <v>200700</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E264" s="2">
         <v>1112</v>
@@ -14957,15 +14991,14 @@
       <c r="J264" s="2">
         <v>0</v>
       </c>
-      <c r="K264" s="2"/>
       <c r="L264" s="2">
         <v>1</v>
       </c>
       <c r="M264" s="14" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N264" s="16" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="O264" s="2">
         <v>20070005</v>
@@ -14979,10 +15012,10 @@
         <v>200700</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E265" s="2">
         <v>2221</v>
@@ -15002,15 +15035,14 @@
       <c r="J265" s="2">
         <v>0</v>
       </c>
-      <c r="K265" s="2"/>
       <c r="L265" s="2">
         <v>1</v>
       </c>
       <c r="M265" s="14" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N265" s="16" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="O265" s="2">
         <v>20070006</v>
@@ -15024,10 +15056,10 @@
         <v>200700</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E266" s="2">
         <v>2222</v>
@@ -15047,15 +15079,14 @@
       <c r="J266" s="2">
         <v>0</v>
       </c>
-      <c r="K266" s="2"/>
       <c r="L266" s="2">
         <v>1</v>
       </c>
       <c r="M266" s="14" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="N266" s="16" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O266" s="2">
         <v>20070002</v>
@@ -15069,10 +15100,10 @@
         <v>200700</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E267" s="2">
         <v>1122</v>
@@ -15092,15 +15123,14 @@
       <c r="J267" s="2">
         <v>10000</v>
       </c>
-      <c r="K267" s="2"/>
       <c r="L267" s="2">
         <v>1</v>
       </c>
       <c r="M267" s="14" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="N267" s="16" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="O267" s="2">
         <v>20070003</v>
@@ -15114,10 +15144,10 @@
         <v>200700</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E268" s="2">
         <v>1111</v>
@@ -15137,15 +15167,14 @@
       <c r="J268" s="2">
         <v>0</v>
       </c>
-      <c r="K268" s="2"/>
       <c r="L268" s="2">
         <v>1</v>
       </c>
       <c r="M268" s="14" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="N268" s="16" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="O268" s="2">
         <v>20070001</v>
@@ -15159,10 +15188,10 @@
         <v>200700</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E269" s="2">
         <v>1112</v>
@@ -15182,15 +15211,14 @@
       <c r="J269" s="2">
         <v>10000</v>
       </c>
-      <c r="K269" s="2"/>
       <c r="L269" s="2">
         <v>1</v>
       </c>
       <c r="M269" s="14" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N269" s="16" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="O269" s="2">
         <v>20070004</v>
@@ -15204,10 +15232,10 @@
         <v>200700</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E270" s="2">
         <v>2221</v>
@@ -15227,15 +15255,14 @@
       <c r="J270" s="2">
         <v>10000</v>
       </c>
-      <c r="K270" s="2"/>
       <c r="L270" s="2">
         <v>1</v>
       </c>
       <c r="M270" s="14" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N270" s="16" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="O270" s="2">
         <v>20070004</v>
@@ -15249,10 +15276,10 @@
         <v>200700</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E271" s="2">
         <v>2222</v>
@@ -15272,15 +15299,14 @@
       <c r="J271" s="2">
         <v>10000</v>
       </c>
-      <c r="K271" s="2"/>
       <c r="L271" s="2">
         <v>1</v>
       </c>
       <c r="M271" s="14" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="N271" s="16" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="O271" s="2">
         <v>20070003</v>
@@ -15294,10 +15320,10 @@
         <v>200700</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E272" s="2">
         <v>1111</v>
@@ -15317,15 +15343,14 @@
       <c r="J272" s="2">
         <v>10000</v>
       </c>
-      <c r="K272" s="2"/>
       <c r="L272" s="2">
         <v>1</v>
       </c>
       <c r="M272" s="14" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="N272" s="16" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="O272" s="2">
         <v>20070003</v>
@@ -15340,7 +15365,7 @@
         <v>200800</v>
       </c>
       <c r="C273" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D273" s="2">
         <v>111</v>
@@ -15363,7 +15388,6 @@
       <c r="J273" s="2">
         <v>10000</v>
       </c>
-      <c r="K273" s="2"/>
       <c r="L273" s="2">
         <v>1</v>
       </c>
@@ -15371,7 +15395,7 @@
         <v>20080001</v>
       </c>
       <c r="N273" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O273" s="2">
         <v>20080001</v>
@@ -15386,7 +15410,7 @@
         <v>200800</v>
       </c>
       <c r="C274" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D274" s="2">
         <v>112</v>
@@ -15416,7 +15440,7 @@
         <v>20080001</v>
       </c>
       <c r="N274" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O274" s="2">
         <v>20080001</v>
@@ -15431,7 +15455,7 @@
         <v>200800</v>
       </c>
       <c r="C275" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D275" s="2">
         <v>113</v>
@@ -15461,7 +15485,7 @@
         <v>20080001</v>
       </c>
       <c r="N275" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O275" s="2">
         <v>20080001</v>
@@ -15476,7 +15500,7 @@
         <v>200800</v>
       </c>
       <c r="C276" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D276" s="2">
         <v>114</v>
@@ -15506,7 +15530,7 @@
         <v>20080001</v>
       </c>
       <c r="N276" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O276" s="2">
         <v>20080001</v>
@@ -15521,7 +15545,7 @@
         <v>200800</v>
       </c>
       <c r="C277" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D277" s="2">
         <v>115</v>
@@ -15551,7 +15575,7 @@
         <v>20080001</v>
       </c>
       <c r="N277" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O277" s="2">
         <v>20080001</v>
@@ -15566,7 +15590,7 @@
         <v>200800</v>
       </c>
       <c r="C278" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D278" s="2">
         <v>116</v>
@@ -15596,7 +15620,7 @@
         <v>20080001</v>
       </c>
       <c r="N278" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O278" s="2">
         <v>20080001</v>
@@ -15611,7 +15635,7 @@
         <v>200800</v>
       </c>
       <c r="C279" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D279" s="2">
         <v>122</v>
@@ -15641,7 +15665,7 @@
         <v>20080001</v>
       </c>
       <c r="N279" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O279" s="2">
         <v>20080001</v>
@@ -15656,7 +15680,7 @@
         <v>200800</v>
       </c>
       <c r="C280" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D280" s="2">
         <v>123</v>
@@ -15686,7 +15710,7 @@
         <v>20080001</v>
       </c>
       <c r="N280" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O280" s="2">
         <v>20080001</v>
@@ -15701,7 +15725,7 @@
         <v>200800</v>
       </c>
       <c r="C281" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D281" s="2">
         <v>124</v>
@@ -15731,7 +15755,7 @@
         <v>20080001</v>
       </c>
       <c r="N281" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O281" s="2">
         <v>20080001</v>
@@ -15746,7 +15770,7 @@
         <v>200800</v>
       </c>
       <c r="C282" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D282" s="2">
         <v>125</v>
@@ -15776,7 +15800,7 @@
         <v>20080001</v>
       </c>
       <c r="N282" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O282" s="2">
         <v>20080001</v>
@@ -15791,7 +15815,7 @@
         <v>200800</v>
       </c>
       <c r="C283" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D283" s="2">
         <v>126</v>
@@ -15821,7 +15845,7 @@
         <v>20080001</v>
       </c>
       <c r="N283" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O283" s="2">
         <v>20080001</v>
@@ -15836,7 +15860,7 @@
         <v>200800</v>
       </c>
       <c r="C284" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D284" s="2">
         <v>133</v>
@@ -15866,7 +15890,7 @@
         <v>20080001</v>
       </c>
       <c r="N284" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O284" s="2">
         <v>20080001</v>
@@ -15881,7 +15905,7 @@
         <v>200800</v>
       </c>
       <c r="C285" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D285" s="2">
         <v>134</v>
@@ -15911,7 +15935,7 @@
         <v>20080001</v>
       </c>
       <c r="N285" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O285" s="2">
         <v>20080001</v>
@@ -15926,7 +15950,7 @@
         <v>200800</v>
       </c>
       <c r="C286" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D286" s="2">
         <v>135</v>
@@ -15956,7 +15980,7 @@
         <v>20080001</v>
       </c>
       <c r="N286" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O286" s="2">
         <v>20080001</v>
@@ -15971,7 +15995,7 @@
         <v>200800</v>
       </c>
       <c r="C287" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D287" s="2">
         <v>136</v>
@@ -16001,7 +16025,7 @@
         <v>20080001</v>
       </c>
       <c r="N287" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O287" s="2">
         <v>20080001</v>
@@ -16016,7 +16040,7 @@
         <v>200800</v>
       </c>
       <c r="C288" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D288" s="2">
         <v>144</v>
@@ -16046,7 +16070,7 @@
         <v>20080001</v>
       </c>
       <c r="N288" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O288" s="2">
         <v>20080001</v>
@@ -16061,7 +16085,7 @@
         <v>200800</v>
       </c>
       <c r="C289" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D289" s="2">
         <v>145</v>
@@ -16091,7 +16115,7 @@
         <v>20080001</v>
       </c>
       <c r="N289" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O289" s="2">
         <v>20080001</v>
@@ -16106,7 +16130,7 @@
         <v>200800</v>
       </c>
       <c r="C290" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D290" s="2">
         <v>146</v>
@@ -16136,7 +16160,7 @@
         <v>20080002</v>
       </c>
       <c r="N290" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O290" s="2">
         <v>20080002</v>
@@ -16151,7 +16175,7 @@
         <v>200800</v>
       </c>
       <c r="C291" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D291" s="2">
         <v>155</v>
@@ -16181,7 +16205,7 @@
         <v>20080002</v>
       </c>
       <c r="N291" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O291" s="2">
         <v>20080002</v>
@@ -16196,7 +16220,7 @@
         <v>200800</v>
       </c>
       <c r="C292" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D292" s="2">
         <v>156</v>
@@ -16226,7 +16250,7 @@
         <v>20080002</v>
       </c>
       <c r="N292" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O292" s="2">
         <v>20080002</v>
@@ -16241,7 +16265,7 @@
         <v>200800</v>
       </c>
       <c r="C293" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D293" s="2">
         <v>166</v>
@@ -16271,7 +16295,7 @@
         <v>20080002</v>
       </c>
       <c r="N293" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O293" s="2">
         <v>20080002</v>
@@ -16286,7 +16310,7 @@
         <v>200800</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D294" s="2">
         <v>222</v>
@@ -16316,7 +16340,7 @@
         <v>20080001</v>
       </c>
       <c r="N294" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O294" s="2">
         <v>20080001</v>
@@ -16331,7 +16355,7 @@
         <v>200800</v>
       </c>
       <c r="C295" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D295" s="2">
         <v>223</v>
@@ -16361,7 +16385,7 @@
         <v>20080001</v>
       </c>
       <c r="N295" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O295" s="2">
         <v>20080001</v>
@@ -16376,7 +16400,7 @@
         <v>200800</v>
       </c>
       <c r="C296" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D296" s="2">
         <v>224</v>
@@ -16406,7 +16430,7 @@
         <v>20080001</v>
       </c>
       <c r="N296" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O296" s="2">
         <v>20080001</v>
@@ -16421,7 +16445,7 @@
         <v>200800</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D297" s="2">
         <v>225</v>
@@ -16451,7 +16475,7 @@
         <v>20080001</v>
       </c>
       <c r="N297" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O297" s="2">
         <v>20080001</v>
@@ -16466,7 +16490,7 @@
         <v>200800</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D298" s="2">
         <v>226</v>
@@ -16496,7 +16520,7 @@
         <v>20080001</v>
       </c>
       <c r="N298" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O298" s="2">
         <v>20080001</v>
@@ -16511,7 +16535,7 @@
         <v>200800</v>
       </c>
       <c r="C299" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D299" s="2">
         <v>233</v>
@@ -16541,7 +16565,7 @@
         <v>20080001</v>
       </c>
       <c r="N299" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O299" s="2">
         <v>20080001</v>
@@ -16556,7 +16580,7 @@
         <v>200800</v>
       </c>
       <c r="C300" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D300" s="2">
         <v>234</v>
@@ -16586,7 +16610,7 @@
         <v>20080001</v>
       </c>
       <c r="N300" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O300" s="2">
         <v>20080001</v>
@@ -16601,7 +16625,7 @@
         <v>200800</v>
       </c>
       <c r="C301" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D301" s="2">
         <v>235</v>
@@ -16631,7 +16655,7 @@
         <v>20080001</v>
       </c>
       <c r="N301" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O301" s="2">
         <v>20080001</v>
@@ -16646,7 +16670,7 @@
         <v>200800</v>
       </c>
       <c r="C302" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D302" s="2">
         <v>236</v>
@@ -16676,7 +16700,7 @@
         <v>20080002</v>
       </c>
       <c r="N302" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O302" s="2">
         <v>20080002</v>
@@ -16691,7 +16715,7 @@
         <v>200800</v>
       </c>
       <c r="C303" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D303" s="2">
         <v>244</v>
@@ -16721,7 +16745,7 @@
         <v>20080001</v>
       </c>
       <c r="N303" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O303" s="2">
         <v>20080001</v>
@@ -16736,7 +16760,7 @@
         <v>200800</v>
       </c>
       <c r="C304" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D304" s="2">
         <v>245</v>
@@ -16766,7 +16790,7 @@
         <v>20080002</v>
       </c>
       <c r="N304" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O304" s="2">
         <v>20080002</v>
@@ -16781,7 +16805,7 @@
         <v>200800</v>
       </c>
       <c r="C305" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D305" s="2">
         <v>246</v>
@@ -16811,7 +16835,7 @@
         <v>20080002</v>
       </c>
       <c r="N305" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O305" s="2">
         <v>20080002</v>
@@ -16826,7 +16850,7 @@
         <v>200800</v>
       </c>
       <c r="C306" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D306" s="2">
         <v>255</v>
@@ -16856,7 +16880,7 @@
         <v>20080002</v>
       </c>
       <c r="N306" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O306" s="2">
         <v>20080002</v>
@@ -16871,7 +16895,7 @@
         <v>200800</v>
       </c>
       <c r="C307" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D307" s="2">
         <v>256</v>
@@ -16901,7 +16925,7 @@
         <v>20080002</v>
       </c>
       <c r="N307" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O307" s="2">
         <v>20080002</v>
@@ -16916,7 +16940,7 @@
         <v>200800</v>
       </c>
       <c r="C308" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D308" s="2">
         <v>266</v>
@@ -16946,7 +16970,7 @@
         <v>20080002</v>
       </c>
       <c r="N308" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O308" s="2">
         <v>20080002</v>
@@ -16961,7 +16985,7 @@
         <v>200800</v>
       </c>
       <c r="C309" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D309" s="2">
         <v>333</v>
@@ -16991,7 +17015,7 @@
         <v>20080001</v>
       </c>
       <c r="N309" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O309" s="2">
         <v>20080001</v>
@@ -17006,7 +17030,7 @@
         <v>200800</v>
       </c>
       <c r="C310" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D310" s="2">
         <v>334</v>
@@ -17036,7 +17060,7 @@
         <v>20080001</v>
       </c>
       <c r="N310" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O310" s="2">
         <v>20080001</v>
@@ -17051,7 +17075,7 @@
         <v>200800</v>
       </c>
       <c r="C311" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D311" s="2">
         <v>335</v>
@@ -17081,7 +17105,7 @@
         <v>20080002</v>
       </c>
       <c r="N311" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O311" s="2">
         <v>20080002</v>
@@ -17096,7 +17120,7 @@
         <v>200800</v>
       </c>
       <c r="C312" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D312" s="2">
         <v>336</v>
@@ -17126,7 +17150,7 @@
         <v>20080002</v>
       </c>
       <c r="N312" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O312" s="2">
         <v>20080002</v>
@@ -17141,7 +17165,7 @@
         <v>200800</v>
       </c>
       <c r="C313" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D313" s="2">
         <v>344</v>
@@ -17171,7 +17195,7 @@
         <v>20080002</v>
       </c>
       <c r="N313" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O313" s="2">
         <v>20080002</v>
@@ -17186,7 +17210,7 @@
         <v>200800</v>
       </c>
       <c r="C314" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D314" s="2">
         <v>345</v>
@@ -17216,7 +17240,7 @@
         <v>20080002</v>
       </c>
       <c r="N314" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O314" s="2">
         <v>20080002</v>
@@ -17231,7 +17255,7 @@
         <v>200800</v>
       </c>
       <c r="C315" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D315" s="2">
         <v>346</v>
@@ -17261,7 +17285,7 @@
         <v>20080002</v>
       </c>
       <c r="N315" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O315" s="2">
         <v>20080002</v>
@@ -17276,7 +17300,7 @@
         <v>200800</v>
       </c>
       <c r="C316" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D316" s="2">
         <v>355</v>
@@ -17306,7 +17330,7 @@
         <v>20080002</v>
       </c>
       <c r="N316" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O316" s="2">
         <v>20080002</v>
@@ -17321,7 +17345,7 @@
         <v>200800</v>
       </c>
       <c r="C317" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D317" s="2">
         <v>356</v>
@@ -17351,7 +17375,7 @@
         <v>20080002</v>
       </c>
       <c r="N317" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O317" s="2">
         <v>20080002</v>
@@ -17366,7 +17390,7 @@
         <v>200800</v>
       </c>
       <c r="C318" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D318" s="2">
         <v>366</v>
@@ -17396,7 +17420,7 @@
         <v>20080002</v>
       </c>
       <c r="N318" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O318" s="2">
         <v>20080002</v>
@@ -17411,7 +17435,7 @@
         <v>200800</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D319" s="2">
         <v>444</v>
@@ -17441,7 +17465,7 @@
         <v>20080002</v>
       </c>
       <c r="N319" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O319" s="2">
         <v>20080002</v>
@@ -17456,7 +17480,7 @@
         <v>200800</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D320" s="2">
         <v>445</v>
@@ -17486,7 +17510,7 @@
         <v>20080002</v>
       </c>
       <c r="N320" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O320" s="2">
         <v>20080002</v>
@@ -17501,7 +17525,7 @@
         <v>200800</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D321" s="2">
         <v>446</v>
@@ -17531,7 +17555,7 @@
         <v>20080002</v>
       </c>
       <c r="N321" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O321" s="2">
         <v>20080002</v>
@@ -17546,7 +17570,7 @@
         <v>200800</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D322" s="2">
         <v>455</v>
@@ -17576,7 +17600,7 @@
         <v>20080002</v>
       </c>
       <c r="N322" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O322" s="2">
         <v>20080002</v>
@@ -17591,7 +17615,7 @@
         <v>200800</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D323" s="2">
         <v>456</v>
@@ -17621,7 +17645,7 @@
         <v>20080002</v>
       </c>
       <c r="N323" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O323" s="2">
         <v>20080002</v>
@@ -17636,7 +17660,7 @@
         <v>200800</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D324" s="2">
         <v>466</v>
@@ -17666,7 +17690,7 @@
         <v>20080002</v>
       </c>
       <c r="N324" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O324" s="2">
         <v>20080002</v>
@@ -17681,7 +17705,7 @@
         <v>200800</v>
       </c>
       <c r="C325" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D325" s="2">
         <v>555</v>
@@ -17711,7 +17735,7 @@
         <v>20080002</v>
       </c>
       <c r="N325" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O325" s="2">
         <v>20080002</v>
@@ -17726,7 +17750,7 @@
         <v>200800</v>
       </c>
       <c r="C326" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D326" s="2">
         <v>556</v>
@@ -17756,7 +17780,7 @@
         <v>20080002</v>
       </c>
       <c r="N326" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O326" s="2">
         <v>20080002</v>
@@ -17771,7 +17795,7 @@
         <v>200800</v>
       </c>
       <c r="C327" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D327" s="2">
         <v>566</v>
@@ -17801,7 +17825,7 @@
         <v>20080002</v>
       </c>
       <c r="N327" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O327" s="2">
         <v>20080002</v>
@@ -17816,7 +17840,7 @@
         <v>200800</v>
       </c>
       <c r="C328" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D328" s="2">
         <v>666</v>
@@ -17846,7 +17870,7 @@
         <v>20080002</v>
       </c>
       <c r="N328" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O328" s="2">
         <v>20080002</v>
@@ -17860,10 +17884,10 @@
         <v>200900</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E329" s="2">
         <v>111</v>
@@ -17887,10 +17911,10 @@
         <v>1</v>
       </c>
       <c r="M329" s="14" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="N329" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O329" s="15">
         <v>20090001</v>
@@ -17906,10 +17930,10 @@
         <v>200900</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E330" s="2">
         <v>112</v>
@@ -17933,10 +17957,10 @@
         <v>1</v>
       </c>
       <c r="M330" s="14" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="N330" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O330" s="15">
         <v>20090001</v>
@@ -17952,10 +17976,10 @@
         <v>200900</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E331" s="2">
         <v>113</v>
@@ -17979,10 +18003,10 @@
         <v>1</v>
       </c>
       <c r="M331" s="14" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="N331" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O331" s="15">
         <v>20090001</v>
@@ -17998,10 +18022,10 @@
         <v>200900</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E332" s="2">
         <v>114</v>
@@ -18025,10 +18049,10 @@
         <v>1</v>
       </c>
       <c r="M332" s="14" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="N332" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O332" s="15">
         <v>20090001</v>
@@ -18044,10 +18068,10 @@
         <v>200900</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E333" s="2">
         <v>115</v>
@@ -18071,10 +18095,10 @@
         <v>1</v>
       </c>
       <c r="M333" s="14" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="N333" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O333" s="15">
         <v>20090001</v>
@@ -18090,10 +18114,10 @@
         <v>200900</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E334" s="2">
         <v>116</v>
@@ -18117,10 +18141,10 @@
         <v>1</v>
       </c>
       <c r="M334" s="14" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="N334" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O334" s="15">
         <v>20090001</v>
@@ -18136,10 +18160,10 @@
         <v>200900</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E335" s="2">
         <v>122</v>
@@ -18163,10 +18187,10 @@
         <v>1</v>
       </c>
       <c r="M335" s="14" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="N335" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O335" s="15">
         <v>20090002</v>
@@ -18180,10 +18204,10 @@
         <v>200900</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E336" s="2">
         <v>123</v>
@@ -18207,22 +18231,22 @@
         <v>1</v>
       </c>
       <c r="M336" s="14" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="N336" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O336" s="15">
         <v>20090001</v>
       </c>
       <c r="P336" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q336" s="15">
         <v>20090002</v>
       </c>
       <c r="R336" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="S336" s="15">
         <v>20090003</v>
@@ -18236,10 +18260,10 @@
         <v>200900</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E337" s="2">
         <v>124</v>
@@ -18263,22 +18287,22 @@
         <v>1</v>
       </c>
       <c r="M337" s="14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="N337" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O337" s="15">
         <v>20090001</v>
       </c>
       <c r="P337" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q337" s="15">
         <v>20090002</v>
       </c>
       <c r="R337" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="S337" s="15">
         <v>20090004</v>
@@ -18292,10 +18316,10 @@
         <v>200900</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E338" s="2">
         <v>125</v>
@@ -18319,22 +18343,22 @@
         <v>1</v>
       </c>
       <c r="M338" s="14" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="N338" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O338" s="15">
         <v>20090001</v>
       </c>
       <c r="P338" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q338" s="15">
         <v>20090002</v>
       </c>
       <c r="R338" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="S338" s="15">
         <v>20090005</v>
@@ -18348,10 +18372,10 @@
         <v>200900</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E339" s="2">
         <v>126</v>
@@ -18375,22 +18399,22 @@
         <v>1</v>
       </c>
       <c r="M339" s="14" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="N339" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O339" s="15">
         <v>20090001</v>
       </c>
       <c r="P339" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q339" s="15">
         <v>20090002</v>
       </c>
       <c r="R339" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="S339" s="15">
         <v>20090006</v>
@@ -18404,10 +18428,10 @@
         <v>200900</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E340" s="2">
         <v>133</v>
@@ -18434,7 +18458,7 @@
         <v>20090003</v>
       </c>
       <c r="N340" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O340" s="15">
         <v>20090003</v>
@@ -18448,10 +18472,10 @@
         <v>200900</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E341" s="2">
         <v>134</v>
@@ -18475,22 +18499,22 @@
         <v>1</v>
       </c>
       <c r="M341" s="14" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="N341" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O341" s="15">
         <v>20090001</v>
       </c>
       <c r="P341" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q341" s="15">
         <v>20090003</v>
       </c>
       <c r="R341" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="S341" s="15">
         <v>20090004</v>
@@ -18504,10 +18528,10 @@
         <v>200900</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E342" s="2">
         <v>135</v>
@@ -18531,22 +18555,22 @@
         <v>1</v>
       </c>
       <c r="M342" s="14" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="N342" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O342" s="15">
         <v>20090001</v>
       </c>
       <c r="P342" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q342" s="15">
         <v>20090003</v>
       </c>
       <c r="R342" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="S342" s="15">
         <v>20090005</v>
@@ -18560,10 +18584,10 @@
         <v>200900</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E343" s="2">
         <v>136</v>
@@ -18587,22 +18611,22 @@
         <v>1</v>
       </c>
       <c r="M343" s="14" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="N343" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O343" s="15">
         <v>20090001</v>
       </c>
       <c r="P343" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q343" s="15">
         <v>20090003</v>
       </c>
       <c r="R343" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="S343" s="15">
         <v>20090006</v>
@@ -18616,10 +18640,10 @@
         <v>200900</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E344" s="2">
         <v>144</v>
@@ -18643,10 +18667,10 @@
         <v>1</v>
       </c>
       <c r="M344" s="14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="N344" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O344" s="15">
         <v>20090004</v>
@@ -18660,10 +18684,10 @@
         <v>200900</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E345" s="2">
         <v>145</v>
@@ -18687,22 +18711,22 @@
         <v>1</v>
       </c>
       <c r="M345" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="N345" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O345" s="15">
         <v>20090001</v>
       </c>
       <c r="P345" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q345" s="15">
         <v>20090004</v>
       </c>
       <c r="R345" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="S345" s="15">
         <v>20090005</v>
@@ -18716,10 +18740,10 @@
         <v>200900</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E346" s="2">
         <v>146</v>
@@ -18743,22 +18767,22 @@
         <v>1</v>
       </c>
       <c r="M346" s="14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="N346" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O346" s="15">
         <v>20090001</v>
       </c>
       <c r="P346" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q346" s="15">
         <v>20090004</v>
       </c>
       <c r="R346" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="S346" s="15">
         <v>20090006</v>
@@ -18772,10 +18796,10 @@
         <v>200900</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E347" s="2">
         <v>155</v>
@@ -18799,10 +18823,10 @@
         <v>1</v>
       </c>
       <c r="M347" s="14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N347" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O347" s="15">
         <v>20090005</v>
@@ -18816,10 +18840,10 @@
         <v>200900</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E348" s="2">
         <v>156</v>
@@ -18843,22 +18867,22 @@
         <v>1</v>
       </c>
       <c r="M348" s="14" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="N348" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O348" s="15">
         <v>20090001</v>
       </c>
       <c r="P348" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q348" s="15">
         <v>20090005</v>
       </c>
       <c r="R348" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="S348" s="15">
         <v>20090006</v>
@@ -18872,10 +18896,10 @@
         <v>200900</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E349" s="2">
         <v>166</v>
@@ -18899,10 +18923,10 @@
         <v>1</v>
       </c>
       <c r="M349" s="14" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="N349" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O349" s="15">
         <v>20090006</v>
@@ -18916,10 +18940,10 @@
         <v>200900</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E350" s="2">
         <v>222</v>
@@ -18946,7 +18970,7 @@
         <v>20090002</v>
       </c>
       <c r="N350" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O350" s="15">
         <v>20090002</v>
@@ -18960,10 +18984,10 @@
         <v>200900</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E351" s="2">
         <v>223</v>
@@ -18990,7 +19014,7 @@
         <v>20090002</v>
       </c>
       <c r="N351" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O351" s="15">
         <v>20090002</v>
@@ -19004,10 +19028,10 @@
         <v>200900</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E352" s="2">
         <v>224</v>
@@ -19034,7 +19058,7 @@
         <v>20090002</v>
       </c>
       <c r="N352" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O352" s="15">
         <v>20090002</v>
@@ -19048,10 +19072,10 @@
         <v>200900</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E353" s="2">
         <v>225</v>
@@ -19078,7 +19102,7 @@
         <v>20090002</v>
       </c>
       <c r="N353" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O353" s="15">
         <v>20090002</v>
@@ -19092,10 +19116,10 @@
         <v>200900</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E354" s="2">
         <v>226</v>
@@ -19122,7 +19146,7 @@
         <v>20090002</v>
       </c>
       <c r="N354" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O354" s="15">
         <v>20090002</v>
@@ -19136,10 +19160,10 @@
         <v>200900</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E355" s="2">
         <v>233</v>
@@ -19166,7 +19190,7 @@
         <v>20090003</v>
       </c>
       <c r="N355" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O355" s="15">
         <v>20090003</v>
@@ -19180,10 +19204,10 @@
         <v>200900</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E356" s="2">
         <v>234</v>
@@ -19207,22 +19231,22 @@
         <v>1</v>
       </c>
       <c r="M356" s="14" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="N356" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O356" s="15">
         <v>20090002</v>
       </c>
       <c r="P356" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q356" s="15">
         <v>20090003</v>
       </c>
       <c r="R356" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="S356" s="15">
         <v>20090004</v>
@@ -19236,10 +19260,10 @@
         <v>200900</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E357" s="2">
         <v>235</v>
@@ -19263,22 +19287,22 @@
         <v>1</v>
       </c>
       <c r="M357" s="14" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N357" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O357" s="15">
         <v>20090002</v>
       </c>
       <c r="P357" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q357" s="15">
         <v>20090003</v>
       </c>
       <c r="R357" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="S357" s="15">
         <v>20090005</v>
@@ -19292,10 +19316,10 @@
         <v>200900</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E358" s="2">
         <v>236</v>
@@ -19319,22 +19343,22 @@
         <v>1</v>
       </c>
       <c r="M358" s="14" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="N358" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O358" s="15">
         <v>20090002</v>
       </c>
       <c r="P358" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q358" s="15">
         <v>20090003</v>
       </c>
       <c r="R358" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="S358" s="15">
         <v>20090006</v>
@@ -19348,10 +19372,10 @@
         <v>200900</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E359" s="2">
         <v>244</v>
@@ -19378,7 +19402,7 @@
         <v>20090004</v>
       </c>
       <c r="N359" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O359" s="15">
         <v>20090004</v>
@@ -19392,10 +19416,10 @@
         <v>200900</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E360" s="2">
         <v>245</v>
@@ -19419,22 +19443,22 @@
         <v>1</v>
       </c>
       <c r="M360" s="14" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="N360" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O360" s="15">
         <v>20090002</v>
       </c>
       <c r="P360" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q360" s="15">
         <v>20090004</v>
       </c>
       <c r="R360" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="S360" s="15">
         <v>20090005</v>
@@ -19448,10 +19472,10 @@
         <v>200900</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E361" s="2">
         <v>246</v>
@@ -19475,22 +19499,22 @@
         <v>1</v>
       </c>
       <c r="M361" s="14" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="N361" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O361" s="15">
         <v>20090002</v>
       </c>
       <c r="P361" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q361" s="15">
         <v>20090004</v>
       </c>
       <c r="R361" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="S361" s="15">
         <v>20090006</v>
@@ -19504,10 +19528,10 @@
         <v>200900</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E362" s="2">
         <v>255</v>
@@ -19531,10 +19555,10 @@
         <v>1</v>
       </c>
       <c r="M362" s="14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N362" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O362" s="15">
         <v>20090005</v>
@@ -19548,10 +19572,10 @@
         <v>200900</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E363" s="2">
         <v>256</v>
@@ -19575,22 +19599,22 @@
         <v>1</v>
       </c>
       <c r="M363" s="14" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="N363" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O363" s="15">
         <v>20090002</v>
       </c>
       <c r="P363" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q363" s="15">
         <v>20090005</v>
       </c>
       <c r="R363" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="S363" s="15">
         <v>20090006</v>
@@ -19604,10 +19628,10 @@
         <v>200900</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E364" s="2">
         <v>266</v>
@@ -19631,10 +19655,10 @@
         <v>1</v>
       </c>
       <c r="M364" s="14" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="N364" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O364" s="15">
         <v>20090006</v>
@@ -19648,10 +19672,10 @@
         <v>200900</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E365" s="2">
         <v>333</v>
@@ -19678,7 +19702,7 @@
         <v>20090003</v>
       </c>
       <c r="N365" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O365" s="15">
         <v>20090003</v>
@@ -19692,10 +19716,10 @@
         <v>200900</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E366" s="2">
         <v>334</v>
@@ -19722,7 +19746,7 @@
         <v>20090003</v>
       </c>
       <c r="N366" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O366" s="15">
         <v>20090003</v>
@@ -19736,10 +19760,10 @@
         <v>200900</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E367" s="2">
         <v>335</v>
@@ -19766,7 +19790,7 @@
         <v>20090003</v>
       </c>
       <c r="N367" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O367" s="15">
         <v>20090003</v>
@@ -19780,10 +19804,10 @@
         <v>200900</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E368" s="2">
         <v>336</v>
@@ -19810,7 +19834,7 @@
         <v>20090003</v>
       </c>
       <c r="N368" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O368" s="15">
         <v>20090003</v>
@@ -19824,10 +19848,10 @@
         <v>200900</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E369" s="2">
         <v>344</v>
@@ -19854,7 +19878,7 @@
         <v>20090004</v>
       </c>
       <c r="N369" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O369" s="15">
         <v>20090004</v>
@@ -19868,10 +19892,10 @@
         <v>200900</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E370" s="2">
         <v>345</v>
@@ -19895,22 +19919,22 @@
         <v>1</v>
       </c>
       <c r="M370" s="14" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="N370" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O370" s="15">
         <v>20090003</v>
       </c>
       <c r="P370" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q370" s="15">
         <v>20090004</v>
       </c>
       <c r="R370" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="S370" s="15">
         <v>20090005</v>
@@ -19924,10 +19948,10 @@
         <v>200900</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E371" s="2">
         <v>346</v>
@@ -19951,22 +19975,22 @@
         <v>1</v>
       </c>
       <c r="M371" s="14" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="N371" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O371" s="15">
         <v>20090003</v>
       </c>
       <c r="P371" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q371" s="15">
         <v>20090004</v>
       </c>
       <c r="R371" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="S371" s="15">
         <v>20090006</v>
@@ -19980,10 +20004,10 @@
         <v>200900</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E372" s="2">
         <v>355</v>
@@ -20007,10 +20031,10 @@
         <v>1</v>
       </c>
       <c r="M372" s="14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N372" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O372" s="15">
         <v>20090005</v>
@@ -20024,10 +20048,10 @@
         <v>200900</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E373" s="2">
         <v>356</v>
@@ -20051,22 +20075,22 @@
         <v>1</v>
       </c>
       <c r="M373" s="14" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="N373" s="15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O373" s="15">
         <v>20090003</v>
       </c>
       <c r="P373" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q373" s="15">
         <v>20090005</v>
       </c>
       <c r="R373" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="S373" s="15">
         <v>20090006</v>
@@ -20080,10 +20104,10 @@
         <v>200900</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E374" s="2">
         <v>366</v>
@@ -20107,10 +20131,10 @@
         <v>1</v>
       </c>
       <c r="M374" s="14" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="N374" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O374" s="15">
         <v>20090006</v>
@@ -20124,10 +20148,10 @@
         <v>200900</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E375" s="2">
         <v>444</v>
@@ -20154,7 +20178,7 @@
         <v>20090004</v>
       </c>
       <c r="N375" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O375" s="15">
         <v>20090004</v>
@@ -20168,10 +20192,10 @@
         <v>200900</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E376" s="2">
         <v>445</v>
@@ -20198,7 +20222,7 @@
         <v>20090004</v>
       </c>
       <c r="N376" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O376" s="15">
         <v>20090004</v>
@@ -20212,10 +20236,10 @@
         <v>200900</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E377" s="2">
         <v>446</v>
@@ -20242,7 +20266,7 @@
         <v>20090004</v>
       </c>
       <c r="N377" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O377" s="15">
         <v>20090004</v>
@@ -20256,10 +20280,10 @@
         <v>200900</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E378" s="2">
         <v>455</v>
@@ -20283,10 +20307,10 @@
         <v>1</v>
       </c>
       <c r="M378" s="14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N378" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O378" s="15">
         <v>20090005</v>
@@ -20300,10 +20324,10 @@
         <v>200900</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E379" s="2">
         <v>456</v>
@@ -20327,22 +20351,22 @@
         <v>1</v>
       </c>
       <c r="M379" s="14" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="N379" s="15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O379" s="15">
         <v>20090004</v>
       </c>
       <c r="P379" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q379" s="15">
         <v>20090005</v>
       </c>
       <c r="R379" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="S379" s="15">
         <v>20090006</v>
@@ -20356,10 +20380,10 @@
         <v>200900</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E380" s="2">
         <v>466</v>
@@ -20383,10 +20407,10 @@
         <v>1</v>
       </c>
       <c r="M380" s="14" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="N380" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O380" s="15">
         <v>20090006</v>
@@ -20400,10 +20424,10 @@
         <v>200900</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E381" s="2">
         <v>555</v>
@@ -20427,10 +20451,10 @@
         <v>1</v>
       </c>
       <c r="M381" s="14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N381" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O381" s="15">
         <v>20090005</v>
@@ -20444,10 +20468,10 @@
         <v>200900</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E382" s="2">
         <v>556</v>
@@ -20471,10 +20495,10 @@
         <v>1</v>
       </c>
       <c r="M382" s="14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N382" s="15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O382" s="15">
         <v>20090005</v>
@@ -20488,10 +20512,10 @@
         <v>200900</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E383" s="2">
         <v>566</v>
@@ -20515,10 +20539,10 @@
         <v>1</v>
       </c>
       <c r="M383" s="14" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="N383" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O383" s="15">
         <v>20090006</v>
@@ -20532,10 +20556,10 @@
         <v>200900</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E384" s="2">
         <v>666</v>
@@ -20559,10 +20583,10 @@
         <v>1</v>
       </c>
       <c r="M384" s="14" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="N384" s="15" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O384" s="15">
         <v>20090006</v>
@@ -20576,10 +20600,10 @@
         <v>200900</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E385" s="2">
         <v>112</v>
@@ -20603,10 +20627,10 @@
         <v>1</v>
       </c>
       <c r="M385" s="14" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="N385" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O385" s="15">
         <v>20090002</v>
@@ -20620,10 +20644,10 @@
         <v>200900</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E386" s="2">
         <v>113</v>
@@ -20650,7 +20674,7 @@
         <v>20090003</v>
       </c>
       <c r="N386" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O386" s="2">
         <v>20090003</v>
@@ -20664,10 +20688,10 @@
         <v>200900</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E387" s="2">
         <v>114</v>
@@ -20694,7 +20718,7 @@
         <v>20090004</v>
       </c>
       <c r="N387" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O387" s="2">
         <v>20090004</v>
@@ -20708,10 +20732,10 @@
         <v>200900</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E388" s="2">
         <v>115</v>
@@ -20738,7 +20762,7 @@
         <v>20090005</v>
       </c>
       <c r="N388" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O388" s="2">
         <v>20090005</v>
@@ -20753,10 +20777,10 @@
         <v>200900</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E389" s="2">
         <v>116</v>
@@ -20783,7 +20807,7 @@
         <v>20090006</v>
       </c>
       <c r="N389" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O389" s="2">
         <v>20090006</v>
@@ -20798,10 +20822,10 @@
         <v>200900</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E390" s="2">
         <v>122</v>
@@ -20828,7 +20852,7 @@
         <v>20090001</v>
       </c>
       <c r="N390" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O390" s="15">
         <v>20090001</v>
@@ -20843,10 +20867,10 @@
         <v>200900</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E391" s="2">
         <v>133</v>
@@ -20873,7 +20897,7 @@
         <v>20090001</v>
       </c>
       <c r="N391" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O391" s="15">
         <v>20090001</v>
@@ -20888,10 +20912,10 @@
         <v>200900</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E392" s="2">
         <v>144</v>
@@ -20918,7 +20942,7 @@
         <v>20090001</v>
       </c>
       <c r="N392" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O392" s="15">
         <v>20090001</v>
@@ -20933,10 +20957,10 @@
         <v>200900</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E393" s="2">
         <v>155</v>
@@ -20963,7 +20987,7 @@
         <v>20090001</v>
       </c>
       <c r="N393" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O393" s="15">
         <v>20090001</v>
@@ -20978,10 +21002,10 @@
         <v>200900</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E394" s="2">
         <v>166</v>
@@ -21008,7 +21032,7 @@
         <v>20090001</v>
       </c>
       <c r="N394" s="15" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O394" s="15">
         <v>20090001</v>
@@ -21023,10 +21047,10 @@
         <v>200900</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E395" s="2">
         <v>223</v>
@@ -21053,7 +21077,7 @@
         <v>20090003</v>
       </c>
       <c r="N395" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O395" s="2">
         <v>20090003</v>
@@ -21068,10 +21092,10 @@
         <v>200900</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E396" s="2">
         <v>224</v>
@@ -21098,7 +21122,7 @@
         <v>20090004</v>
       </c>
       <c r="N396" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O396" s="2">
         <v>20090004</v>
@@ -21113,10 +21137,10 @@
         <v>200900</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E397" s="2">
         <v>225</v>
@@ -21143,7 +21167,7 @@
         <v>20090005</v>
       </c>
       <c r="N397" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O397" s="2">
         <v>20090005</v>
@@ -21158,10 +21182,10 @@
         <v>200900</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E398" s="2">
         <v>226</v>
@@ -21188,7 +21212,7 @@
         <v>20090006</v>
       </c>
       <c r="N398" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O398" s="2">
         <v>20090006</v>
@@ -21203,10 +21227,10 @@
         <v>200900</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E399" s="2">
         <v>233</v>
@@ -21230,10 +21254,10 @@
         <v>1</v>
       </c>
       <c r="M399" s="14" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="N399" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O399" s="15">
         <v>20090002</v>
@@ -21248,10 +21272,10 @@
         <v>200900</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E400" s="2">
         <v>244</v>
@@ -21275,10 +21299,10 @@
         <v>1</v>
       </c>
       <c r="M400" s="14" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="N400" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O400" s="15">
         <v>20090002</v>
@@ -21293,10 +21317,10 @@
         <v>200900</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E401" s="2">
         <v>255</v>
@@ -21320,10 +21344,10 @@
         <v>1</v>
       </c>
       <c r="M401" s="14" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="N401" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O401" s="15">
         <v>20090002</v>
@@ -21338,10 +21362,10 @@
         <v>200900</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E402" s="2">
         <v>266</v>
@@ -21365,10 +21389,10 @@
         <v>1</v>
       </c>
       <c r="M402" s="14" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="N402" s="15" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O402" s="15">
         <v>20090002</v>
@@ -21383,10 +21407,10 @@
         <v>200900</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E403" s="2">
         <v>334</v>
@@ -21413,7 +21437,7 @@
         <v>20090004</v>
       </c>
       <c r="N403" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O403" s="2">
         <v>20090004</v>
@@ -21428,10 +21452,10 @@
         <v>200900</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E404" s="2">
         <v>335</v>
@@ -21458,7 +21482,7 @@
         <v>20090005</v>
       </c>
       <c r="N404" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O404" s="2">
         <v>20090005</v>
@@ -21473,10 +21497,10 @@
         <v>200900</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E405" s="2">
         <v>336</v>
@@ -21503,7 +21527,7 @@
         <v>20090006</v>
       </c>
       <c r="N405" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O405" s="2">
         <v>20090006</v>
@@ -21518,10 +21542,10 @@
         <v>200900</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E406" s="2">
         <v>344</v>
@@ -21548,7 +21572,7 @@
         <v>20090003</v>
       </c>
       <c r="N406" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O406" s="2">
         <v>20090003</v>
@@ -21563,10 +21587,10 @@
         <v>200900</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E407" s="2">
         <v>355</v>
@@ -21593,7 +21617,7 @@
         <v>20090003</v>
       </c>
       <c r="N407" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O407" s="2">
         <v>20090003</v>
@@ -21608,10 +21632,10 @@
         <v>200900</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E408" s="2">
         <v>366</v>
@@ -21638,7 +21662,7 @@
         <v>20090003</v>
       </c>
       <c r="N408" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="O408" s="2">
         <v>20090003</v>
@@ -21653,10 +21677,10 @@
         <v>200900</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E409" s="2">
         <v>445</v>
@@ -21683,7 +21707,7 @@
         <v>20090005</v>
       </c>
       <c r="N409" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O409" s="2">
         <v>20090005</v>
@@ -21698,10 +21722,10 @@
         <v>200900</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E410" s="2">
         <v>446</v>
@@ -21728,7 +21752,7 @@
         <v>20090006</v>
       </c>
       <c r="N410" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O410" s="2">
         <v>20090006</v>
@@ -21743,10 +21767,10 @@
         <v>200900</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E411" s="2">
         <v>455</v>
@@ -21773,7 +21797,7 @@
         <v>20090004</v>
       </c>
       <c r="N411" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O411" s="2">
         <v>20090004</v>
@@ -21788,10 +21812,10 @@
         <v>200900</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E412" s="2">
         <v>466</v>
@@ -21818,7 +21842,7 @@
         <v>20090004</v>
       </c>
       <c r="N412" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="O412" s="2">
         <v>20090004</v>
@@ -21833,10 +21857,10 @@
         <v>200900</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E413" s="2">
         <v>556</v>
@@ -21863,7 +21887,7 @@
         <v>20090006</v>
       </c>
       <c r="N413" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O413" s="2">
         <v>20090006</v>
@@ -21878,10 +21902,10 @@
         <v>200900</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E414" s="2">
         <v>566</v>
@@ -21908,7 +21932,7 @@
         <v>20090005</v>
       </c>
       <c r="N414" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O414" s="2">
         <v>20090005</v>
@@ -21923,10 +21947,10 @@
         <v>201000</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E415" s="2">
         <v>1</v>
@@ -21953,7 +21977,7 @@
         <v>20100002</v>
       </c>
       <c r="N415" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="O415" s="2">
         <v>20100002</v>
@@ -21968,10 +21992,10 @@
         <v>201000</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E416" s="2">
         <v>2</v>
@@ -21998,7 +22022,7 @@
         <v>20100004</v>
       </c>
       <c r="N416" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O416" s="2">
         <v>20100004</v>
@@ -22013,10 +22037,10 @@
         <v>201000</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E417" s="2">
         <v>3</v>
@@ -22043,7 +22067,7 @@
         <v>20100008</v>
       </c>
       <c r="N417" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="O417" s="2">
         <v>20100008</v>
@@ -22058,10 +22082,10 @@
         <v>201000</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E418" s="2">
         <v>4</v>
@@ -22088,7 +22112,7 @@
         <v>20100008</v>
       </c>
       <c r="N418" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="O418" s="2">
         <v>20100008</v>
@@ -22103,10 +22127,10 @@
         <v>201000</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E419" s="2">
         <v>5</v>
@@ -22133,7 +22157,7 @@
         <v>20100001</v>
       </c>
       <c r="N419" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O419" s="2">
         <v>20100001</v>
@@ -22148,10 +22172,10 @@
         <v>201000</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E420" s="2">
         <v>6</v>
@@ -22178,7 +22202,7 @@
         <v>20100001</v>
       </c>
       <c r="N420" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O420" s="2">
         <v>20100001</v>
@@ -22193,10 +22217,10 @@
         <v>201000</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E421" s="2">
         <v>7</v>
@@ -22223,7 +22247,7 @@
         <v>20100003</v>
       </c>
       <c r="N421" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="O421" s="2">
         <v>20100003</v>
@@ -22238,10 +22262,10 @@
         <v>201000</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E422" s="2">
         <v>8</v>
@@ -22268,7 +22292,7 @@
         <v>20100005</v>
       </c>
       <c r="N422" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O422" s="2">
         <v>20100005</v>
@@ -22283,10 +22307,10 @@
         <v>201000</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E423" s="2">
         <v>9</v>
@@ -22313,7 +22337,7 @@
         <v>20100005</v>
       </c>
       <c r="N423" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O423" s="2">
         <v>20100005</v>
@@ -22328,10 +22352,10 @@
         <v>201000</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E424" s="2">
         <v>10</v>
@@ -22352,7 +22376,7 @@
         <v>0</v>
       </c>
       <c r="K424" s="19" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L424" s="2">
         <v>0</v>
@@ -22361,7 +22385,7 @@
         <v>20100000</v>
       </c>
       <c r="N424" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="O424" s="2">
         <v>20100000</v>
@@ -22376,10 +22400,10 @@
         <v>201000</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E425" s="2">
         <v>11</v>
@@ -22407,7 +22431,7 @@
         <v>20100001</v>
       </c>
       <c r="N425" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O425" s="2">
         <v>20100001</v>
@@ -22422,10 +22446,10 @@
         <v>201000</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E426" s="2">
         <v>12</v>
@@ -22453,7 +22477,7 @@
         <v>20100002</v>
       </c>
       <c r="N426" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="O426" s="2">
         <v>20100002</v>
@@ -22468,10 +22492,10 @@
         <v>201000</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E427" s="2">
         <v>13</v>
@@ -22499,7 +22523,7 @@
         <v>20100002</v>
       </c>
       <c r="N427" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="O427" s="2">
         <v>20100002</v>
@@ -22514,10 +22538,10 @@
         <v>201000</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E428" s="2">
         <v>14</v>
@@ -22545,7 +22569,7 @@
         <v>20100004</v>
       </c>
       <c r="N428" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O428" s="2">
         <v>20100004</v>
@@ -22560,10 +22584,10 @@
         <v>201000</v>
       </c>
       <c r="C429" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E429" s="2">
         <v>15</v>
@@ -22606,7 +22630,7 @@
         <v>201000</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D430" s="2">
         <v>77</v>
@@ -22652,10 +22676,10 @@
         <v>201000</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E431" s="2">
         <v>17</v>
@@ -22683,7 +22707,7 @@
         <v>20100001</v>
       </c>
       <c r="N431" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O431" s="2">
         <v>20100001</v>
@@ -22698,10 +22722,10 @@
         <v>201000</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E432" s="2">
         <v>18</v>
@@ -22729,7 +22753,7 @@
         <v>20100003</v>
       </c>
       <c r="N432" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="O432" s="2">
         <v>20100003</v>
@@ -22744,10 +22768,10 @@
         <v>201000</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E433" s="2">
         <v>19</v>
@@ -22775,7 +22799,7 @@
         <v>20100003</v>
       </c>
       <c r="N433" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="O433" s="2">
         <v>20100003</v>
@@ -22790,10 +22814,10 @@
         <v>201000</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E434" s="2">
         <v>20</v>
@@ -22821,7 +22845,7 @@
         <v>20100006</v>
       </c>
       <c r="N434" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="O434" s="2">
         <v>20100006</v>
@@ -22836,10 +22860,10 @@
         <v>201000</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E435" s="2">
         <v>21</v>
@@ -22867,7 +22891,7 @@
         <v>20100006</v>
       </c>
       <c r="N435" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="O435" s="2">
         <v>20100006</v>
@@ -22882,10 +22906,10 @@
         <v>201000</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E436" s="2">
         <v>22</v>
@@ -22906,7 +22930,7 @@
         <v>0</v>
       </c>
       <c r="K436" s="19" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="L436" s="2">
         <v>0</v>
@@ -22915,7 +22939,7 @@
         <v>20100000</v>
       </c>
       <c r="N436" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="O436" s="2">
         <v>20100000</v>
@@ -22930,10 +22954,10 @@
         <v>201000</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E437" s="2">
         <v>23</v>
@@ -22960,7 +22984,7 @@
         <v>20100001</v>
       </c>
       <c r="N437" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O437" s="2">
         <v>20100001</v>
@@ -22975,10 +22999,10 @@
         <v>201000</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E438" s="2">
         <v>24</v>
@@ -23005,7 +23029,7 @@
         <v>20100004</v>
       </c>
       <c r="N438" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O438" s="2">
         <v>20100004</v>
@@ -23019,10 +23043,10 @@
         <v>201000</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E439" s="2">
         <v>1</v>
@@ -23043,7 +23067,7 @@
         <v>0</v>
       </c>
       <c r="K439" s="19" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L439" s="2">
         <v>1</v>
@@ -23052,7 +23076,7 @@
         <v>20100002</v>
       </c>
       <c r="N439" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="O439" s="2">
         <v>20100002</v>
@@ -23066,10 +23090,10 @@
         <v>201000</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E440" s="2">
         <v>2</v>
@@ -23090,7 +23114,7 @@
         <v>0</v>
       </c>
       <c r="K440" s="19" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L440" s="2">
         <v>1</v>
@@ -23099,7 +23123,7 @@
         <v>20100004</v>
       </c>
       <c r="N440" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O440" s="2">
         <v>20100004</v>
@@ -23113,10 +23137,10 @@
         <v>201000</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E441" s="2">
         <v>3</v>
@@ -23137,7 +23161,7 @@
         <v>0</v>
       </c>
       <c r="K441" s="19" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L441" s="2">
         <v>1</v>
@@ -23146,7 +23170,7 @@
         <v>20100008</v>
       </c>
       <c r="N441" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="O441" s="2">
         <v>20100008</v>
@@ -23160,10 +23184,10 @@
         <v>201000</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E442" s="2">
         <v>4</v>
@@ -23184,7 +23208,7 @@
         <v>0</v>
       </c>
       <c r="K442" s="19" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="L442" s="2">
         <v>1</v>
@@ -23193,7 +23217,7 @@
         <v>20100008</v>
       </c>
       <c r="N442" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="O442" s="2">
         <v>20100008</v>
@@ -23207,10 +23231,10 @@
         <v>201000</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E443" s="2">
         <v>5</v>
@@ -23231,7 +23255,7 @@
         <v>0</v>
       </c>
       <c r="K443" s="19" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="L443" s="2">
         <v>1</v>
@@ -23240,7 +23264,7 @@
         <v>20100001</v>
       </c>
       <c r="N443" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O443" s="2">
         <v>20100001</v>
@@ -23254,10 +23278,10 @@
         <v>201000</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E444" s="2">
         <v>6</v>
@@ -23278,7 +23302,7 @@
         <v>0</v>
       </c>
       <c r="K444" s="19" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L444" s="2">
         <v>1</v>
@@ -23287,7 +23311,7 @@
         <v>20100001</v>
       </c>
       <c r="N444" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O444" s="2">
         <v>20100001</v>
@@ -23301,10 +23325,10 @@
         <v>201000</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E445" s="2">
         <v>7</v>
@@ -23325,7 +23349,7 @@
         <v>0</v>
       </c>
       <c r="K445" s="19" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L445" s="2">
         <v>1</v>
@@ -23334,7 +23358,7 @@
         <v>20100003</v>
       </c>
       <c r="N445" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="O445" s="2">
         <v>20100003</v>
@@ -23348,10 +23372,10 @@
         <v>201000</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E446" s="2">
         <v>8</v>
@@ -23372,7 +23396,7 @@
         <v>0</v>
       </c>
       <c r="K446" s="19" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L446" s="2">
         <v>1</v>
@@ -23381,7 +23405,7 @@
         <v>20100005</v>
       </c>
       <c r="N446" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O446" s="2">
         <v>20100005</v>
@@ -23395,10 +23419,10 @@
         <v>201000</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E447" s="2">
         <v>9</v>
@@ -23419,7 +23443,7 @@
         <v>0</v>
       </c>
       <c r="K447" s="19" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="L447" s="2">
         <v>1</v>
@@ -23428,7 +23452,7 @@
         <v>20100005</v>
       </c>
       <c r="N447" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O447" s="2">
         <v>20100005</v>
@@ -23442,10 +23466,10 @@
         <v>201000</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E448" s="2">
         <v>11</v>
@@ -23466,7 +23490,7 @@
         <v>0</v>
       </c>
       <c r="K448" s="19" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="L448" s="2">
         <v>1</v>
@@ -23475,7 +23499,7 @@
         <v>20100001</v>
       </c>
       <c r="N448" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O448" s="2">
         <v>20100001</v>
@@ -23489,10 +23513,10 @@
         <v>201000</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E449" s="2">
         <v>12</v>
@@ -23513,7 +23537,7 @@
         <v>0</v>
       </c>
       <c r="K449" s="19" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L449" s="2">
         <v>1</v>
@@ -23522,7 +23546,7 @@
         <v>20100002</v>
       </c>
       <c r="N449" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="O449" s="2">
         <v>20100002</v>
@@ -23536,10 +23560,10 @@
         <v>201000</v>
       </c>
       <c r="C450" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E450" s="2">
         <v>13</v>
@@ -23560,7 +23584,7 @@
         <v>0</v>
       </c>
       <c r="K450" s="19" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="L450" s="2">
         <v>1</v>
@@ -23569,7 +23593,7 @@
         <v>20100002</v>
       </c>
       <c r="N450" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="O450" s="2">
         <v>20100002</v>
@@ -23583,10 +23607,10 @@
         <v>201000</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E451" s="2">
         <v>14</v>
@@ -23607,7 +23631,7 @@
         <v>0</v>
       </c>
       <c r="K451" s="19" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L451" s="2">
         <v>1</v>
@@ -23616,7 +23640,7 @@
         <v>20100004</v>
       </c>
       <c r="N451" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O451" s="2">
         <v>20100004</v>
@@ -23630,10 +23654,10 @@
         <v>201000</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E452" s="2">
         <v>15</v>
@@ -23654,7 +23678,7 @@
         <v>0</v>
       </c>
       <c r="K452" s="19" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="L452" s="2">
         <v>1</v>
@@ -23677,7 +23701,7 @@
         <v>201000</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D453" s="2">
         <v>77</v>
@@ -23701,7 +23725,7 @@
         <v>0</v>
       </c>
       <c r="K453" s="19" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="L453" s="2">
         <v>1</v>
@@ -23724,10 +23748,10 @@
         <v>201000</v>
       </c>
       <c r="C454" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E454" s="2">
         <v>17</v>
@@ -23748,7 +23772,7 @@
         <v>0</v>
       </c>
       <c r="K454" s="19" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L454" s="2">
         <v>1</v>
@@ -23757,7 +23781,7 @@
         <v>20100001</v>
       </c>
       <c r="N454" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O454" s="2">
         <v>20100001</v>
@@ -23771,10 +23795,10 @@
         <v>201000</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E455" s="2">
         <v>18</v>
@@ -23795,7 +23819,7 @@
         <v>0</v>
       </c>
       <c r="K455" s="19" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L455" s="2">
         <v>1</v>
@@ -23804,7 +23828,7 @@
         <v>20100003</v>
       </c>
       <c r="N455" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="O455" s="2">
         <v>20100003</v>
@@ -23818,10 +23842,10 @@
         <v>201000</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E456" s="2">
         <v>19</v>
@@ -23842,7 +23866,7 @@
         <v>0</v>
       </c>
       <c r="K456" s="19" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="L456" s="2">
         <v>1</v>
@@ -23851,7 +23875,7 @@
         <v>20100003</v>
       </c>
       <c r="N456" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="O456" s="2">
         <v>20100003</v>
@@ -23865,10 +23889,10 @@
         <v>201000</v>
       </c>
       <c r="C457" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E457" s="2">
         <v>20</v>
@@ -23889,7 +23913,7 @@
         <v>0</v>
       </c>
       <c r="K457" s="19" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="L457" s="2">
         <v>1</v>
@@ -23898,7 +23922,7 @@
         <v>20100006</v>
       </c>
       <c r="N457" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="O457" s="2">
         <v>20100006</v>
@@ -23912,10 +23936,10 @@
         <v>201000</v>
       </c>
       <c r="C458" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E458" s="2">
         <v>21</v>
@@ -23936,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="K458" s="19" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L458" s="2">
         <v>1</v>
@@ -23945,7 +23969,7 @@
         <v>20100006</v>
       </c>
       <c r="N458" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="O458" s="2">
         <v>20100006</v>
@@ -23959,10 +23983,10 @@
         <v>201000</v>
       </c>
       <c r="C459" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E459" s="2">
         <v>23</v>
@@ -23983,7 +24007,7 @@
         <v>0</v>
       </c>
       <c r="K459" s="19" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L459" s="2">
         <v>1</v>
@@ -23992,7 +24016,7 @@
         <v>20100001</v>
       </c>
       <c r="N459" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O459" s="2">
         <v>20100001</v>
@@ -24006,10 +24030,10 @@
         <v>201000</v>
       </c>
       <c r="C460" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E460" s="2">
         <v>24</v>
@@ -24030,7 +24054,7 @@
         <v>0</v>
       </c>
       <c r="K460" s="19" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="L460" s="2">
         <v>1</v>
@@ -24039,7 +24063,7 @@
         <v>20100004</v>
       </c>
       <c r="N460" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O460" s="2">
         <v>20100004</v>
@@ -24050,67 +24074,67 @@
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="S336">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S337">
     <cfRule type="duplicateValues" dxfId="0" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S337">
+  <conditionalFormatting sqref="S345">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S346">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S348">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S360">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S361">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q363">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S363">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S370">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S371">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q373">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S373">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q379">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S379">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A111">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A112:A167">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A168:A272">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S338:S339">
     <cfRule type="duplicateValues" dxfId="0" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S345">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S346">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S348">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S360">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S361">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q363">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S363">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S370">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S371">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q373">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S373">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q379">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S379">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A111">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A112:A167">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A168:A272">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S338:S339">
+  <conditionalFormatting sqref="S342:S343">
     <cfRule type="duplicateValues" dxfId="0" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S342:S343">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="S357:S358">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/table/resources/sample/WinPosWeight.xlsx
+++ b/table/resources/sample/WinPosWeight.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="WinPosWeight" sheetId="20" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WinPosWeight!$A$1:$U$478</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WinPosWeight!$A$1:$U$947</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -22252,7 +22252,7 @@
         <v>1</v>
       </c>
       <c r="M416" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N416" s="3" t="s">
         <v>334</v>
@@ -22296,7 +22296,7 @@
         <v>1</v>
       </c>
       <c r="M417" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N417" s="3" t="s">
         <v>335</v>
@@ -22340,7 +22340,7 @@
         <v>1</v>
       </c>
       <c r="M418" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N418" s="3" t="s">
         <v>187</v>
@@ -22384,7 +22384,7 @@
         <v>1</v>
       </c>
       <c r="M419" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N419" s="23" t="s">
         <v>336</v>
@@ -22428,7 +22428,7 @@
         <v>1</v>
       </c>
       <c r="M420" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N420" s="3" t="s">
         <v>337</v>
@@ -22692,7 +22692,7 @@
         <v>1</v>
       </c>
       <c r="M426" s="22">
-        <v>20120100</v>
+        <v>201200100</v>
       </c>
       <c r="N426" s="3" t="s">
         <v>342</v>
@@ -22736,7 +22736,7 @@
         <v>1</v>
       </c>
       <c r="M427" s="22">
-        <v>20120112</v>
+        <v>201200112</v>
       </c>
       <c r="N427" s="3" t="s">
         <v>343</v>
@@ -22780,7 +22780,7 @@
         <v>1</v>
       </c>
       <c r="M428" s="22">
-        <v>20120134</v>
+        <v>201200134</v>
       </c>
       <c r="N428" s="3" t="s">
         <v>344</v>
@@ -22824,7 +22824,7 @@
         <v>1</v>
       </c>
       <c r="M429" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N429" s="3" t="s">
         <v>345</v>
@@ -22868,7 +22868,7 @@
         <v>1</v>
       </c>
       <c r="M430" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N430" s="3" t="s">
         <v>346</v>
@@ -22912,7 +22912,7 @@
         <v>1</v>
       </c>
       <c r="M431" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N431" s="3" t="s">
         <v>187</v>
@@ -22956,7 +22956,7 @@
         <v>1</v>
       </c>
       <c r="M432" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N432" s="3" t="s">
         <v>336</v>
@@ -23000,7 +23000,7 @@
         <v>1</v>
       </c>
       <c r="M433" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N433" s="3" t="s">
         <v>347</v>
@@ -23352,7 +23352,7 @@
         <v>1</v>
       </c>
       <c r="M441" s="22">
-        <v>20120100</v>
+        <v>201200100</v>
       </c>
       <c r="N441" s="3" t="s">
         <v>342</v>
@@ -23396,7 +23396,7 @@
         <v>1</v>
       </c>
       <c r="M442" s="22">
-        <v>20120112</v>
+        <v>201200112</v>
       </c>
       <c r="N442" s="3" t="s">
         <v>343</v>
@@ -23440,7 +23440,7 @@
         <v>1</v>
       </c>
       <c r="M443" s="22">
-        <v>20120113</v>
+        <v>201200113</v>
       </c>
       <c r="N443" s="3" t="s">
         <v>352</v>
@@ -23484,7 +23484,7 @@
         <v>1</v>
       </c>
       <c r="M444" s="22">
-        <v>20120134</v>
+        <v>201200134</v>
       </c>
       <c r="N444" s="3" t="s">
         <v>344</v>
@@ -23528,7 +23528,7 @@
         <v>1</v>
       </c>
       <c r="M445" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N445" s="3" t="s">
         <v>334</v>
@@ -23572,7 +23572,7 @@
         <v>1</v>
       </c>
       <c r="M446" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N446" s="3" t="s">
         <v>335</v>
@@ -23616,7 +23616,7 @@
         <v>1</v>
       </c>
       <c r="M447" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N447" s="3" t="s">
         <v>187</v>
@@ -23660,7 +23660,7 @@
         <v>1</v>
       </c>
       <c r="M448" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N448" s="3" t="s">
         <v>336</v>
@@ -23704,7 +23704,7 @@
         <v>1</v>
       </c>
       <c r="M449" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N449" s="3" t="s">
         <v>353</v>
@@ -23968,7 +23968,7 @@
         <v>1</v>
       </c>
       <c r="M455" s="22">
-        <v>20120100</v>
+        <v>201200100</v>
       </c>
       <c r="N455" s="3" t="s">
         <v>342</v>
@@ -24012,7 +24012,7 @@
         <v>1</v>
       </c>
       <c r="M456" s="22">
-        <v>20120113</v>
+        <v>201200113</v>
       </c>
       <c r="N456" s="3" t="s">
         <v>352</v>
@@ -24056,7 +24056,7 @@
         <v>1</v>
       </c>
       <c r="M457" s="22">
-        <v>20120134</v>
+        <v>201200134</v>
       </c>
       <c r="N457" s="3" t="s">
         <v>344</v>
@@ -24100,7 +24100,7 @@
         <v>1</v>
       </c>
       <c r="M458" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N458" s="3" t="s">
         <v>345</v>
@@ -24144,7 +24144,7 @@
         <v>1</v>
       </c>
       <c r="M459" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N459" s="3" t="s">
         <v>346</v>
@@ -24188,7 +24188,7 @@
         <v>1</v>
       </c>
       <c r="M460" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N460" s="3" t="s">
         <v>187</v>
@@ -24232,7 +24232,7 @@
         <v>1</v>
       </c>
       <c r="M461" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N461" s="3" t="s">
         <v>336</v>
@@ -24276,7 +24276,7 @@
         <v>1</v>
       </c>
       <c r="M462" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N462" s="3" t="s">
         <v>337</v>
@@ -24496,7 +24496,7 @@
         <v>1</v>
       </c>
       <c r="M467" s="22">
-        <v>20120101</v>
+        <v>201200101</v>
       </c>
       <c r="N467" s="3" t="s">
         <v>358</v>
@@ -24540,7 +24540,7 @@
         <v>1</v>
       </c>
       <c r="M468" s="22">
-        <v>20120112</v>
+        <v>201200112</v>
       </c>
       <c r="N468" s="3" t="s">
         <v>343</v>
@@ -24584,7 +24584,7 @@
         <v>1</v>
       </c>
       <c r="M469" s="22">
-        <v>20120114</v>
+        <v>201200114</v>
       </c>
       <c r="N469" s="3" t="s">
         <v>359</v>
@@ -24628,7 +24628,7 @@
         <v>1</v>
       </c>
       <c r="M470" s="22">
-        <v>20120134</v>
+        <v>201200134</v>
       </c>
       <c r="N470" s="3" t="s">
         <v>344</v>
@@ -24672,7 +24672,7 @@
         <v>1</v>
       </c>
       <c r="M471" s="22">
-        <v>20120135</v>
+        <v>201200135</v>
       </c>
       <c r="N471" s="3" t="s">
         <v>360</v>
@@ -24716,7 +24716,7 @@
         <v>1</v>
       </c>
       <c r="M472" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N472" s="3" t="s">
         <v>334</v>
@@ -24760,7 +24760,7 @@
         <v>1</v>
       </c>
       <c r="M473" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N473" s="3" t="s">
         <v>335</v>
@@ -24804,7 +24804,7 @@
         <v>1</v>
       </c>
       <c r="M474" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N474" s="3" t="s">
         <v>187</v>
@@ -24848,7 +24848,7 @@
         <v>1</v>
       </c>
       <c r="M475" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N475" s="3" t="s">
         <v>336</v>
@@ -24892,7 +24892,7 @@
         <v>1</v>
       </c>
       <c r="M476" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N476" s="3" t="s">
         <v>347</v>
@@ -25156,7 +25156,7 @@
         <v>1</v>
       </c>
       <c r="M482" s="22">
-        <v>20120101</v>
+        <v>201200101</v>
       </c>
       <c r="N482" s="3" t="s">
         <v>358</v>
@@ -25200,7 +25200,7 @@
         <v>1</v>
       </c>
       <c r="M483" s="22">
-        <v>20120112</v>
+        <v>201200112</v>
       </c>
       <c r="N483" s="3" t="s">
         <v>343</v>
@@ -25244,7 +25244,7 @@
         <v>1</v>
       </c>
       <c r="M484" s="22">
-        <v>20120113</v>
+        <v>201200113</v>
       </c>
       <c r="N484" s="3" t="s">
         <v>352</v>
@@ -25288,7 +25288,7 @@
         <v>1</v>
       </c>
       <c r="M485" s="22">
-        <v>20120114</v>
+        <v>201200114</v>
       </c>
       <c r="N485" s="3" t="s">
         <v>359</v>
@@ -25332,7 +25332,7 @@
         <v>1</v>
       </c>
       <c r="M486" s="22">
-        <v>20120115</v>
+        <v>201200115</v>
       </c>
       <c r="N486" s="3" t="s">
         <v>363</v>
@@ -25376,7 +25376,7 @@
         <v>1</v>
       </c>
       <c r="M487" s="22">
-        <v>20120134</v>
+        <v>201200134</v>
       </c>
       <c r="N487" s="3" t="s">
         <v>344</v>
@@ -25420,7 +25420,7 @@
         <v>1</v>
       </c>
       <c r="M488" s="22">
-        <v>20120135</v>
+        <v>201200135</v>
       </c>
       <c r="N488" s="3" t="s">
         <v>360</v>
@@ -25464,7 +25464,7 @@
         <v>1</v>
       </c>
       <c r="M489" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N489" s="3" t="s">
         <v>345</v>
@@ -25508,7 +25508,7 @@
         <v>1</v>
       </c>
       <c r="M490" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N490" s="3" t="s">
         <v>346</v>
@@ -25552,7 +25552,7 @@
         <v>1</v>
       </c>
       <c r="M491" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N491" s="3" t="s">
         <v>187</v>
@@ -25596,7 +25596,7 @@
         <v>1</v>
       </c>
       <c r="M492" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N492" s="3" t="s">
         <v>336</v>
@@ -25640,7 +25640,7 @@
         <v>1</v>
       </c>
       <c r="M493" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N493" s="3" t="s">
         <v>353</v>
@@ -25860,7 +25860,7 @@
         <v>1</v>
       </c>
       <c r="M498" s="22">
-        <v>20120101</v>
+        <v>201200101</v>
       </c>
       <c r="N498" s="3" t="s">
         <v>358</v>
@@ -25904,7 +25904,7 @@
         <v>1</v>
       </c>
       <c r="M499" s="22">
-        <v>20120113</v>
+        <v>201200113</v>
       </c>
       <c r="N499" s="3" t="s">
         <v>352</v>
@@ -25948,7 +25948,7 @@
         <v>1</v>
       </c>
       <c r="M500" s="22">
-        <v>20120115</v>
+        <v>201200115</v>
       </c>
       <c r="N500" s="3" t="s">
         <v>363</v>
@@ -25992,7 +25992,7 @@
         <v>1</v>
       </c>
       <c r="M501" s="22">
-        <v>20120134</v>
+        <v>201200134</v>
       </c>
       <c r="N501" s="3" t="s">
         <v>344</v>
@@ -26036,7 +26036,7 @@
         <v>1</v>
       </c>
       <c r="M502" s="22">
-        <v>20120135</v>
+        <v>201200135</v>
       </c>
       <c r="N502" s="3" t="s">
         <v>360</v>
@@ -26080,7 +26080,7 @@
         <v>1</v>
       </c>
       <c r="M503" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N503" s="3" t="s">
         <v>334</v>
@@ -26124,7 +26124,7 @@
         <v>1</v>
       </c>
       <c r="M504" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N504" s="3" t="s">
         <v>335</v>
@@ -26168,7 +26168,7 @@
         <v>1</v>
       </c>
       <c r="M505" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N505" s="3" t="s">
         <v>187</v>
@@ -26212,7 +26212,7 @@
         <v>1</v>
       </c>
       <c r="M506" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N506" s="3" t="s">
         <v>336</v>
@@ -26256,7 +26256,7 @@
         <v>1</v>
       </c>
       <c r="M507" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N507" s="3" t="s">
         <v>337</v>
@@ -26476,7 +26476,7 @@
         <v>1</v>
       </c>
       <c r="M512" s="22">
-        <v>20120102</v>
+        <v>201200102</v>
       </c>
       <c r="N512" s="3" t="s">
         <v>367</v>
@@ -26520,7 +26520,7 @@
         <v>1</v>
       </c>
       <c r="M513" s="22">
-        <v>20120114</v>
+        <v>201200114</v>
       </c>
       <c r="N513" s="3" t="s">
         <v>359</v>
@@ -26564,7 +26564,7 @@
         <v>1</v>
       </c>
       <c r="M514" s="22">
-        <v>20120116</v>
+        <v>201200116</v>
       </c>
       <c r="N514" s="3" t="s">
         <v>368</v>
@@ -26608,7 +26608,7 @@
         <v>1</v>
       </c>
       <c r="M515" s="22">
-        <v>20120135</v>
+        <v>201200135</v>
       </c>
       <c r="N515" s="3" t="s">
         <v>360</v>
@@ -26652,7 +26652,7 @@
         <v>1</v>
       </c>
       <c r="M516" s="22">
-        <v>20120136</v>
+        <v>201200136</v>
       </c>
       <c r="N516" s="3" t="s">
         <v>369</v>
@@ -26696,7 +26696,7 @@
         <v>1</v>
       </c>
       <c r="M517" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N517" s="3" t="s">
         <v>345</v>
@@ -26740,7 +26740,7 @@
         <v>1</v>
       </c>
       <c r="M518" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N518" s="3" t="s">
         <v>346</v>
@@ -26784,7 +26784,7 @@
         <v>1</v>
       </c>
       <c r="M519" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N519" s="3" t="s">
         <v>187</v>
@@ -26828,7 +26828,7 @@
         <v>1</v>
       </c>
       <c r="M520" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N520" s="3" t="s">
         <v>336</v>
@@ -26872,7 +26872,7 @@
         <v>1</v>
       </c>
       <c r="M521" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N521" s="3" t="s">
         <v>347</v>
@@ -27136,7 +27136,7 @@
         <v>1</v>
       </c>
       <c r="M527" s="22">
-        <v>20120102</v>
+        <v>201200102</v>
       </c>
       <c r="N527" s="3" t="s">
         <v>367</v>
@@ -27180,7 +27180,7 @@
         <v>1</v>
       </c>
       <c r="M528" s="22">
-        <v>20120114</v>
+        <v>201200114</v>
       </c>
       <c r="N528" s="3" t="s">
         <v>359</v>
@@ -27224,7 +27224,7 @@
         <v>1</v>
       </c>
       <c r="M529" s="22">
-        <v>20120115</v>
+        <v>201200115</v>
       </c>
       <c r="N529" s="3" t="s">
         <v>363</v>
@@ -27268,7 +27268,7 @@
         <v>1</v>
       </c>
       <c r="M530" s="22">
-        <v>20120116</v>
+        <v>201200116</v>
       </c>
       <c r="N530" s="3" t="s">
         <v>368</v>
@@ -27312,7 +27312,7 @@
         <v>1</v>
       </c>
       <c r="M531" s="22">
-        <v>20120117</v>
+        <v>201200117</v>
       </c>
       <c r="N531" s="3" t="s">
         <v>372</v>
@@ -27356,7 +27356,7 @@
         <v>1</v>
       </c>
       <c r="M532" s="22">
-        <v>20120135</v>
+        <v>201200135</v>
       </c>
       <c r="N532" s="3" t="s">
         <v>360</v>
@@ -27400,7 +27400,7 @@
         <v>1</v>
       </c>
       <c r="M533" s="22">
-        <v>20120136</v>
+        <v>201200136</v>
       </c>
       <c r="N533" s="3" t="s">
         <v>369</v>
@@ -27444,7 +27444,7 @@
         <v>1</v>
       </c>
       <c r="M534" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N534" s="3" t="s">
         <v>334</v>
@@ -27488,7 +27488,7 @@
         <v>1</v>
       </c>
       <c r="M535" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N535" s="3" t="s">
         <v>335</v>
@@ -27532,7 +27532,7 @@
         <v>1</v>
       </c>
       <c r="M536" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N536" s="3" t="s">
         <v>187</v>
@@ -27576,7 +27576,7 @@
         <v>1</v>
       </c>
       <c r="M537" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N537" s="3" t="s">
         <v>336</v>
@@ -27620,7 +27620,7 @@
         <v>1</v>
       </c>
       <c r="M538" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N538" s="3" t="s">
         <v>353</v>
@@ -27840,7 +27840,7 @@
         <v>1</v>
       </c>
       <c r="M543" s="22">
-        <v>20120102</v>
+        <v>201200102</v>
       </c>
       <c r="N543" s="3" t="s">
         <v>367</v>
@@ -27884,7 +27884,7 @@
         <v>1</v>
       </c>
       <c r="M544" s="22">
-        <v>20120115</v>
+        <v>201200115</v>
       </c>
       <c r="N544" s="3" t="s">
         <v>363</v>
@@ -27928,7 +27928,7 @@
         <v>1</v>
       </c>
       <c r="M545" s="22">
-        <v>20120117</v>
+        <v>201200117</v>
       </c>
       <c r="N545" s="3" t="s">
         <v>372</v>
@@ -27972,7 +27972,7 @@
         <v>1</v>
       </c>
       <c r="M546" s="22">
-        <v>20120135</v>
+        <v>201200135</v>
       </c>
       <c r="N546" s="3" t="s">
         <v>360</v>
@@ -28016,7 +28016,7 @@
         <v>1</v>
       </c>
       <c r="M547" s="22">
-        <v>20120136</v>
+        <v>201200136</v>
       </c>
       <c r="N547" s="3" t="s">
         <v>369</v>
@@ -28060,7 +28060,7 @@
         <v>1</v>
       </c>
       <c r="M548" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N548" s="3" t="s">
         <v>345</v>
@@ -28104,7 +28104,7 @@
         <v>1</v>
       </c>
       <c r="M549" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N549" s="3" t="s">
         <v>346</v>
@@ -28148,7 +28148,7 @@
         <v>1</v>
       </c>
       <c r="M550" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N550" s="3" t="s">
         <v>187</v>
@@ -28192,7 +28192,7 @@
         <v>1</v>
       </c>
       <c r="M551" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N551" s="3" t="s">
         <v>336</v>
@@ -28236,7 +28236,7 @@
         <v>1</v>
       </c>
       <c r="M552" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N552" s="3" t="s">
         <v>337</v>
@@ -28456,7 +28456,7 @@
         <v>1</v>
       </c>
       <c r="M557" s="22">
-        <v>20120103</v>
+        <v>201200103</v>
       </c>
       <c r="N557" s="3" t="s">
         <v>376</v>
@@ -28500,7 +28500,7 @@
         <v>1</v>
       </c>
       <c r="M558" s="22">
-        <v>20120116</v>
+        <v>201200116</v>
       </c>
       <c r="N558" s="3" t="s">
         <v>368</v>
@@ -28544,7 +28544,7 @@
         <v>1</v>
       </c>
       <c r="M559" s="22">
-        <v>20120118</v>
+        <v>201200118</v>
       </c>
       <c r="N559" s="3" t="s">
         <v>377</v>
@@ -28588,7 +28588,7 @@
         <v>1</v>
       </c>
       <c r="M560" s="22">
-        <v>20120137</v>
+        <v>201200137</v>
       </c>
       <c r="N560" s="3" t="s">
         <v>378</v>
@@ -28632,7 +28632,7 @@
         <v>1</v>
       </c>
       <c r="M561" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N561" s="3" t="s">
         <v>334</v>
@@ -28676,7 +28676,7 @@
         <v>1</v>
       </c>
       <c r="M562" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N562" s="3" t="s">
         <v>346</v>
@@ -28720,7 +28720,7 @@
         <v>1</v>
       </c>
       <c r="M563" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N563" s="3" t="s">
         <v>187</v>
@@ -28764,7 +28764,7 @@
         <v>1</v>
       </c>
       <c r="M564" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N564" s="3" t="s">
         <v>336</v>
@@ -28808,7 +28808,7 @@
         <v>1</v>
       </c>
       <c r="M565" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N565" s="3" t="s">
         <v>347</v>
@@ -29072,7 +29072,7 @@
         <v>1</v>
       </c>
       <c r="M571" s="22">
-        <v>20120103</v>
+        <v>201200103</v>
       </c>
       <c r="N571" s="3" t="s">
         <v>376</v>
@@ -29116,7 +29116,7 @@
         <v>1</v>
       </c>
       <c r="M572" s="22">
-        <v>20120116</v>
+        <v>201200116</v>
       </c>
       <c r="N572" s="3" t="s">
         <v>368</v>
@@ -29160,7 +29160,7 @@
         <v>1</v>
       </c>
       <c r="M573" s="22">
-        <v>20120117</v>
+        <v>201200117</v>
       </c>
       <c r="N573" s="3" t="s">
         <v>372</v>
@@ -29204,7 +29204,7 @@
         <v>1</v>
       </c>
       <c r="M574" s="22">
-        <v>20120118</v>
+        <v>201200118</v>
       </c>
       <c r="N574" s="3" t="s">
         <v>377</v>
@@ -29248,7 +29248,7 @@
         <v>1</v>
       </c>
       <c r="M575" s="22">
-        <v>20120119</v>
+        <v>201200119</v>
       </c>
       <c r="N575" s="3" t="s">
         <v>381</v>
@@ -29292,7 +29292,7 @@
         <v>1</v>
       </c>
       <c r="M576" s="22">
-        <v>20120136</v>
+        <v>201200136</v>
       </c>
       <c r="N576" s="3" t="s">
         <v>369</v>
@@ -29336,7 +29336,7 @@
         <v>1</v>
       </c>
       <c r="M577" s="22">
-        <v>20120137</v>
+        <v>201200137</v>
       </c>
       <c r="N577" s="3" t="s">
         <v>378</v>
@@ -29380,7 +29380,7 @@
         <v>1</v>
       </c>
       <c r="M578" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N578" s="3" t="s">
         <v>345</v>
@@ -29424,7 +29424,7 @@
         <v>1</v>
       </c>
       <c r="M579" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N579" s="3" t="s">
         <v>335</v>
@@ -29468,7 +29468,7 @@
         <v>1</v>
       </c>
       <c r="M580" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N580" s="3" t="s">
         <v>187</v>
@@ -29512,7 +29512,7 @@
         <v>1</v>
       </c>
       <c r="M581" s="22">
-        <v>20120151</v>
+        <v>201200151</v>
       </c>
       <c r="N581" s="3" t="s">
         <v>336</v>
@@ -29556,7 +29556,7 @@
         <v>1</v>
       </c>
       <c r="M582" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N582" s="3" t="s">
         <v>353</v>
@@ -29776,7 +29776,7 @@
         <v>1</v>
       </c>
       <c r="M587" s="22">
-        <v>20120103</v>
+        <v>201200103</v>
       </c>
       <c r="N587" s="3" t="s">
         <v>376</v>
@@ -29820,7 +29820,7 @@
         <v>1</v>
       </c>
       <c r="M588" s="22">
-        <v>20120117</v>
+        <v>201200117</v>
       </c>
       <c r="N588" s="3" t="s">
         <v>372</v>
@@ -29864,7 +29864,7 @@
         <v>1</v>
       </c>
       <c r="M589" s="22">
-        <v>20120119</v>
+        <v>201200119</v>
       </c>
       <c r="N589" s="3" t="s">
         <v>381</v>
@@ -29908,7 +29908,7 @@
         <v>1</v>
       </c>
       <c r="M590" s="22">
-        <v>20120136</v>
+        <v>201200136</v>
       </c>
       <c r="N590" s="3" t="s">
         <v>369</v>
@@ -29952,7 +29952,7 @@
         <v>1</v>
       </c>
       <c r="M591" s="22">
-        <v>20120137</v>
+        <v>201200137</v>
       </c>
       <c r="N591" s="3" t="s">
         <v>378</v>
@@ -29996,7 +29996,7 @@
         <v>1</v>
       </c>
       <c r="M592" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N592" s="3" t="s">
         <v>334</v>
@@ -30040,7 +30040,7 @@
         <v>1</v>
       </c>
       <c r="M593" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N593" s="3" t="s">
         <v>346</v>
@@ -30084,7 +30084,7 @@
         <v>1</v>
       </c>
       <c r="M594" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N594" s="3" t="s">
         <v>187</v>
@@ -30128,7 +30128,7 @@
         <v>1</v>
       </c>
       <c r="M595" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N595" s="3" t="s">
         <v>383</v>
@@ -30172,7 +30172,7 @@
         <v>1</v>
       </c>
       <c r="M596" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N596" s="3" t="s">
         <v>337</v>
@@ -30392,7 +30392,7 @@
         <v>1</v>
       </c>
       <c r="M601" s="22">
-        <v>20120104</v>
+        <v>201200104</v>
       </c>
       <c r="N601" s="3" t="s">
         <v>386</v>
@@ -30436,7 +30436,7 @@
         <v>1</v>
       </c>
       <c r="M602" s="22">
-        <v>20120118</v>
+        <v>201200118</v>
       </c>
       <c r="N602" s="3" t="s">
         <v>377</v>
@@ -30480,7 +30480,7 @@
         <v>1</v>
       </c>
       <c r="M603" s="22">
-        <v>20120120</v>
+        <v>201200120</v>
       </c>
       <c r="N603" s="3" t="s">
         <v>387</v>
@@ -30524,7 +30524,7 @@
         <v>1</v>
       </c>
       <c r="M604" s="22">
-        <v>20120137</v>
+        <v>201200137</v>
       </c>
       <c r="N604" s="3" t="s">
         <v>378</v>
@@ -30568,7 +30568,7 @@
         <v>1</v>
       </c>
       <c r="M605" s="22">
-        <v>20120138</v>
+        <v>201200138</v>
       </c>
       <c r="N605" s="3" t="s">
         <v>388</v>
@@ -30612,7 +30612,7 @@
         <v>1</v>
       </c>
       <c r="M606" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N606" s="3" t="s">
         <v>345</v>
@@ -30656,7 +30656,7 @@
         <v>1</v>
       </c>
       <c r="M607" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N607" s="3" t="s">
         <v>335</v>
@@ -30700,7 +30700,7 @@
         <v>1</v>
       </c>
       <c r="M608" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N608" s="3" t="s">
         <v>187</v>
@@ -30744,7 +30744,7 @@
         <v>1</v>
       </c>
       <c r="M609" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N609" s="3" t="s">
         <v>383</v>
@@ -30788,7 +30788,7 @@
         <v>1</v>
       </c>
       <c r="M610" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N610" s="3" t="s">
         <v>347</v>
@@ -31052,7 +31052,7 @@
         <v>1</v>
       </c>
       <c r="M616" s="22">
-        <v>20120104</v>
+        <v>201200104</v>
       </c>
       <c r="N616" s="3" t="s">
         <v>386</v>
@@ -31096,7 +31096,7 @@
         <v>1</v>
       </c>
       <c r="M617" s="22">
-        <v>20120119</v>
+        <v>201200119</v>
       </c>
       <c r="N617" s="3" t="s">
         <v>381</v>
@@ -31140,7 +31140,7 @@
         <v>1</v>
       </c>
       <c r="M618" s="22">
-        <v>20120120</v>
+        <v>201200120</v>
       </c>
       <c r="N618" s="3" t="s">
         <v>387</v>
@@ -31184,7 +31184,7 @@
         <v>1</v>
       </c>
       <c r="M619" s="22">
-        <v>20120118</v>
+        <v>201200118</v>
       </c>
       <c r="N619" s="3" t="s">
         <v>377</v>
@@ -31228,7 +31228,7 @@
         <v>1</v>
       </c>
       <c r="M620" s="22">
-        <v>20120121</v>
+        <v>201200121</v>
       </c>
       <c r="N620" s="3" t="s">
         <v>391</v>
@@ -31272,7 +31272,7 @@
         <v>1</v>
       </c>
       <c r="M621" s="22">
-        <v>20120137</v>
+        <v>201200137</v>
       </c>
       <c r="N621" s="3" t="s">
         <v>378</v>
@@ -31316,7 +31316,7 @@
         <v>1</v>
       </c>
       <c r="M622" s="22">
-        <v>20120138</v>
+        <v>201200138</v>
       </c>
       <c r="N622" s="3" t="s">
         <v>388</v>
@@ -31360,7 +31360,7 @@
         <v>1</v>
       </c>
       <c r="M623" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N623" s="3" t="s">
         <v>334</v>
@@ -31404,7 +31404,7 @@
         <v>1</v>
       </c>
       <c r="M624" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N624" s="3" t="s">
         <v>346</v>
@@ -31448,7 +31448,7 @@
         <v>1</v>
       </c>
       <c r="M625" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N625" s="3" t="s">
         <v>187</v>
@@ -31492,7 +31492,7 @@
         <v>1</v>
       </c>
       <c r="M626" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N626" s="3" t="s">
         <v>383</v>
@@ -31536,7 +31536,7 @@
         <v>1</v>
       </c>
       <c r="M627" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N627" s="3" t="s">
         <v>353</v>
@@ -31756,7 +31756,7 @@
         <v>1</v>
       </c>
       <c r="M632" s="22">
-        <v>20120104</v>
+        <v>201200104</v>
       </c>
       <c r="N632" s="3" t="s">
         <v>386</v>
@@ -31800,7 +31800,7 @@
         <v>1</v>
       </c>
       <c r="M633" s="22">
-        <v>20120119</v>
+        <v>201200119</v>
       </c>
       <c r="N633" s="3" t="s">
         <v>381</v>
@@ -31844,7 +31844,7 @@
         <v>1</v>
       </c>
       <c r="M634" s="22">
-        <v>20120121</v>
+        <v>201200121</v>
       </c>
       <c r="N634" s="3" t="s">
         <v>391</v>
@@ -31888,7 +31888,7 @@
         <v>1</v>
       </c>
       <c r="M635" s="22">
-        <v>20120137</v>
+        <v>201200137</v>
       </c>
       <c r="N635" s="3" t="s">
         <v>378</v>
@@ -31932,7 +31932,7 @@
         <v>1</v>
       </c>
       <c r="M636" s="22">
-        <v>20120138</v>
+        <v>201200138</v>
       </c>
       <c r="N636" s="3" t="s">
         <v>388</v>
@@ -31976,7 +31976,7 @@
         <v>1</v>
       </c>
       <c r="M637" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N637" s="3" t="s">
         <v>345</v>
@@ -32020,7 +32020,7 @@
         <v>1</v>
       </c>
       <c r="M638" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N638" s="3" t="s">
         <v>335</v>
@@ -32064,7 +32064,7 @@
         <v>1</v>
       </c>
       <c r="M639" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N639" s="3" t="s">
         <v>187</v>
@@ -32108,7 +32108,7 @@
         <v>1</v>
       </c>
       <c r="M640" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N640" s="3" t="s">
         <v>383</v>
@@ -32152,7 +32152,7 @@
         <v>1</v>
       </c>
       <c r="M641" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N641" s="3" t="s">
         <v>337</v>
@@ -32372,7 +32372,7 @@
         <v>1</v>
       </c>
       <c r="M646" s="22">
-        <v>20120105</v>
+        <v>201200105</v>
       </c>
       <c r="N646" s="3" t="s">
         <v>395</v>
@@ -32416,7 +32416,7 @@
         <v>1</v>
       </c>
       <c r="M647" s="22">
-        <v>20120120</v>
+        <v>201200120</v>
       </c>
       <c r="N647" s="3" t="s">
         <v>387</v>
@@ -32460,7 +32460,7 @@
         <v>1</v>
       </c>
       <c r="M648" s="22">
-        <v>20120122</v>
+        <v>201200122</v>
       </c>
       <c r="N648" s="3" t="s">
         <v>396</v>
@@ -32504,7 +32504,7 @@
         <v>1</v>
       </c>
       <c r="M649" s="22">
-        <v>20120138</v>
+        <v>201200138</v>
       </c>
       <c r="N649" s="3" t="s">
         <v>388</v>
@@ -32548,7 +32548,7 @@
         <v>1</v>
       </c>
       <c r="M650" s="22">
-        <v>20120139</v>
+        <v>201200139</v>
       </c>
       <c r="N650" s="3" t="s">
         <v>397</v>
@@ -32592,7 +32592,7 @@
         <v>1</v>
       </c>
       <c r="M651" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N651" s="3" t="s">
         <v>334</v>
@@ -32636,7 +32636,7 @@
         <v>1</v>
       </c>
       <c r="M652" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N652" s="3" t="s">
         <v>346</v>
@@ -32680,7 +32680,7 @@
         <v>1</v>
       </c>
       <c r="M653" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N653" s="3" t="s">
         <v>187</v>
@@ -32724,7 +32724,7 @@
         <v>1</v>
       </c>
       <c r="M654" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N654" s="3" t="s">
         <v>383</v>
@@ -32768,7 +32768,7 @@
         <v>1</v>
       </c>
       <c r="M655" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N655" s="3" t="s">
         <v>347</v>
@@ -33032,7 +33032,7 @@
         <v>1</v>
       </c>
       <c r="M661" s="22">
-        <v>20120105</v>
+        <v>201200105</v>
       </c>
       <c r="N661" s="3" t="s">
         <v>395</v>
@@ -33076,7 +33076,7 @@
         <v>1</v>
       </c>
       <c r="M662" s="22">
-        <v>20120120</v>
+        <v>201200120</v>
       </c>
       <c r="N662" s="3" t="s">
         <v>387</v>
@@ -33120,7 +33120,7 @@
         <v>1</v>
       </c>
       <c r="M663" s="22">
-        <v>20120121</v>
+        <v>201200121</v>
       </c>
       <c r="N663" s="3" t="s">
         <v>391</v>
@@ -33164,7 +33164,7 @@
         <v>1</v>
       </c>
       <c r="M664" s="22">
-        <v>20120122</v>
+        <v>201200122</v>
       </c>
       <c r="N664" s="3" t="s">
         <v>396</v>
@@ -33208,7 +33208,7 @@
         <v>1</v>
       </c>
       <c r="M665" s="22">
-        <v>20120123</v>
+        <v>201200123</v>
       </c>
       <c r="N665" s="3" t="s">
         <v>400</v>
@@ -33252,7 +33252,7 @@
         <v>1</v>
       </c>
       <c r="M666" s="22">
-        <v>20120138</v>
+        <v>201200138</v>
       </c>
       <c r="N666" s="3" t="s">
         <v>388</v>
@@ -33296,7 +33296,7 @@
         <v>1</v>
       </c>
       <c r="M667" s="22">
-        <v>20120139</v>
+        <v>201200139</v>
       </c>
       <c r="N667" s="3" t="s">
         <v>397</v>
@@ -33340,7 +33340,7 @@
         <v>1</v>
       </c>
       <c r="M668" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N668" s="3" t="s">
         <v>345</v>
@@ -33384,7 +33384,7 @@
         <v>1</v>
       </c>
       <c r="M669" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N669" s="3" t="s">
         <v>335</v>
@@ -33428,7 +33428,7 @@
         <v>1</v>
       </c>
       <c r="M670" s="22">
-        <v>20120150</v>
+        <v>201200150</v>
       </c>
       <c r="N670" s="3" t="s">
         <v>187</v>
@@ -33472,7 +33472,7 @@
         <v>1</v>
       </c>
       <c r="M671" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N671" s="3" t="s">
         <v>383</v>
@@ -33516,7 +33516,7 @@
         <v>1</v>
       </c>
       <c r="M672" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N672" s="3" t="s">
         <v>353</v>
@@ -33736,7 +33736,7 @@
         <v>1</v>
       </c>
       <c r="M677" s="22">
-        <v>20120105</v>
+        <v>201200105</v>
       </c>
       <c r="N677" s="3" t="s">
         <v>395</v>
@@ -33780,7 +33780,7 @@
         <v>1</v>
       </c>
       <c r="M678" s="22">
-        <v>20120121</v>
+        <v>201200121</v>
       </c>
       <c r="N678" s="3" t="s">
         <v>391</v>
@@ -33824,7 +33824,7 @@
         <v>1</v>
       </c>
       <c r="M679" s="22">
-        <v>20120123</v>
+        <v>201200123</v>
       </c>
       <c r="N679" s="3" t="s">
         <v>400</v>
@@ -33868,7 +33868,7 @@
         <v>1</v>
       </c>
       <c r="M680" s="22">
-        <v>20120138</v>
+        <v>201200138</v>
       </c>
       <c r="N680" s="3" t="s">
         <v>388</v>
@@ -33912,7 +33912,7 @@
         <v>1</v>
       </c>
       <c r="M681" s="22">
-        <v>20120139</v>
+        <v>201200139</v>
       </c>
       <c r="N681" s="3" t="s">
         <v>397</v>
@@ -33956,7 +33956,7 @@
         <v>1</v>
       </c>
       <c r="M682" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N682" s="3" t="s">
         <v>334</v>
@@ -34000,7 +34000,7 @@
         <v>1</v>
       </c>
       <c r="M683" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N683" s="3" t="s">
         <v>335</v>
@@ -34044,7 +34044,7 @@
         <v>1</v>
       </c>
       <c r="M684" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N684" s="3" t="s">
         <v>210</v>
@@ -34088,7 +34088,7 @@
         <v>1</v>
       </c>
       <c r="M685" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N685" s="3" t="s">
         <v>383</v>
@@ -34132,7 +34132,7 @@
         <v>1</v>
       </c>
       <c r="M686" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N686" s="3" t="s">
         <v>337</v>
@@ -34352,7 +34352,7 @@
         <v>1</v>
       </c>
       <c r="M691" s="22">
-        <v>20120106</v>
+        <v>201200106</v>
       </c>
       <c r="N691" s="3" t="s">
         <v>404</v>
@@ -34396,7 +34396,7 @@
         <v>1</v>
       </c>
       <c r="M692" s="22">
-        <v>20120122</v>
+        <v>201200122</v>
       </c>
       <c r="N692" s="3" t="s">
         <v>396</v>
@@ -34440,7 +34440,7 @@
         <v>1</v>
       </c>
       <c r="M693" s="22">
-        <v>20120124</v>
+        <v>201200124</v>
       </c>
       <c r="N693" s="3" t="s">
         <v>405</v>
@@ -34484,7 +34484,7 @@
         <v>1</v>
       </c>
       <c r="M694" s="22">
-        <v>20120139</v>
+        <v>201200139</v>
       </c>
       <c r="N694" s="3" t="s">
         <v>397</v>
@@ -34528,7 +34528,7 @@
         <v>1</v>
       </c>
       <c r="M695" s="22">
-        <v>20120140</v>
+        <v>201200140</v>
       </c>
       <c r="N695" s="3" t="s">
         <v>406</v>
@@ -34572,7 +34572,7 @@
         <v>1</v>
       </c>
       <c r="M696" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N696" s="3" t="s">
         <v>345</v>
@@ -34616,7 +34616,7 @@
         <v>1</v>
       </c>
       <c r="M697" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N697" s="3" t="s">
         <v>346</v>
@@ -34660,7 +34660,7 @@
         <v>1</v>
       </c>
       <c r="M698" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N698" s="3" t="s">
         <v>210</v>
@@ -34704,7 +34704,7 @@
         <v>1</v>
       </c>
       <c r="M699" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N699" s="3" t="s">
         <v>383</v>
@@ -34748,7 +34748,7 @@
         <v>1</v>
       </c>
       <c r="M700" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N700" s="3" t="s">
         <v>347</v>
@@ -35012,7 +35012,7 @@
         <v>1</v>
       </c>
       <c r="M706" s="22">
-        <v>20120106</v>
+        <v>201200106</v>
       </c>
       <c r="N706" s="3" t="s">
         <v>404</v>
@@ -35056,7 +35056,7 @@
         <v>1</v>
       </c>
       <c r="M707" s="22">
-        <v>20120122</v>
+        <v>201200122</v>
       </c>
       <c r="N707" s="3" t="s">
         <v>396</v>
@@ -35100,7 +35100,7 @@
         <v>1</v>
       </c>
       <c r="M708" s="22">
-        <v>20120123</v>
+        <v>201200123</v>
       </c>
       <c r="N708" s="3" t="s">
         <v>400</v>
@@ -35144,7 +35144,7 @@
         <v>1</v>
       </c>
       <c r="M709" s="22">
-        <v>20120124</v>
+        <v>201200124</v>
       </c>
       <c r="N709" s="3" t="s">
         <v>405</v>
@@ -35188,7 +35188,7 @@
         <v>1</v>
       </c>
       <c r="M710" s="22">
-        <v>20120125</v>
+        <v>201200125</v>
       </c>
       <c r="N710" s="3" t="s">
         <v>409</v>
@@ -35232,7 +35232,7 @@
         <v>1</v>
       </c>
       <c r="M711" s="22">
-        <v>20120139</v>
+        <v>201200139</v>
       </c>
       <c r="N711" s="3" t="s">
         <v>397</v>
@@ -35276,7 +35276,7 @@
         <v>1</v>
       </c>
       <c r="M712" s="22">
-        <v>20120140</v>
+        <v>201200140</v>
       </c>
       <c r="N712" s="3" t="s">
         <v>406</v>
@@ -35320,7 +35320,7 @@
         <v>1</v>
       </c>
       <c r="M713" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N713" s="3" t="s">
         <v>334</v>
@@ -35364,7 +35364,7 @@
         <v>1</v>
       </c>
       <c r="M714" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N714" s="3" t="s">
         <v>335</v>
@@ -35408,7 +35408,7 @@
         <v>1</v>
       </c>
       <c r="M715" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N715" s="3" t="s">
         <v>210</v>
@@ -35452,7 +35452,7 @@
         <v>1</v>
       </c>
       <c r="M716" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N716" s="3" t="s">
         <v>383</v>
@@ -35496,7 +35496,7 @@
         <v>1</v>
       </c>
       <c r="M717" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N717" s="3" t="s">
         <v>353</v>
@@ -35716,7 +35716,7 @@
         <v>1</v>
       </c>
       <c r="M722" s="22">
-        <v>20120106</v>
+        <v>201200106</v>
       </c>
       <c r="N722" s="3" t="s">
         <v>404</v>
@@ -35760,7 +35760,7 @@
         <v>1</v>
       </c>
       <c r="M723" s="22">
-        <v>20120123</v>
+        <v>201200123</v>
       </c>
       <c r="N723" s="3" t="s">
         <v>400</v>
@@ -35804,7 +35804,7 @@
         <v>1</v>
       </c>
       <c r="M724" s="22">
-        <v>20120125</v>
+        <v>201200125</v>
       </c>
       <c r="N724" s="3" t="s">
         <v>409</v>
@@ -35848,7 +35848,7 @@
         <v>1</v>
       </c>
       <c r="M725" s="22">
-        <v>20120139</v>
+        <v>201200139</v>
       </c>
       <c r="N725" s="3" t="s">
         <v>397</v>
@@ -35892,7 +35892,7 @@
         <v>1</v>
       </c>
       <c r="M726" s="22">
-        <v>20120140</v>
+        <v>201200140</v>
       </c>
       <c r="N726" s="3" t="s">
         <v>406</v>
@@ -35936,7 +35936,7 @@
         <v>1</v>
       </c>
       <c r="M727" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N727" s="3" t="s">
         <v>345</v>
@@ -35980,7 +35980,7 @@
         <v>1</v>
       </c>
       <c r="M728" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N728" s="3" t="s">
         <v>346</v>
@@ -36024,7 +36024,7 @@
         <v>1</v>
       </c>
       <c r="M729" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N729" s="3" t="s">
         <v>210</v>
@@ -36068,7 +36068,7 @@
         <v>1</v>
       </c>
       <c r="M730" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N730" s="3" t="s">
         <v>383</v>
@@ -36112,7 +36112,7 @@
         <v>1</v>
       </c>
       <c r="M731" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N731" s="3" t="s">
         <v>337</v>
@@ -36332,7 +36332,7 @@
         <v>1</v>
       </c>
       <c r="M736" s="22">
-        <v>20120107</v>
+        <v>201200107</v>
       </c>
       <c r="N736" s="3" t="s">
         <v>413</v>
@@ -36376,7 +36376,7 @@
         <v>1</v>
       </c>
       <c r="M737" s="22">
-        <v>20120124</v>
+        <v>201200124</v>
       </c>
       <c r="N737" s="3" t="s">
         <v>405</v>
@@ -36420,7 +36420,7 @@
         <v>1</v>
       </c>
       <c r="M738" s="22">
-        <v>20120126</v>
+        <v>201200126</v>
       </c>
       <c r="N738" s="3" t="s">
         <v>414</v>
@@ -36464,7 +36464,7 @@
         <v>1</v>
       </c>
       <c r="M739" s="22">
-        <v>20120140</v>
+        <v>201200140</v>
       </c>
       <c r="N739" s="3" t="s">
         <v>406</v>
@@ -36508,7 +36508,7 @@
         <v>1</v>
       </c>
       <c r="M740" s="22">
-        <v>20120141</v>
+        <v>201200141</v>
       </c>
       <c r="N740" s="3" t="s">
         <v>415</v>
@@ -36552,7 +36552,7 @@
         <v>1</v>
       </c>
       <c r="M741" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N741" s="3" t="s">
         <v>334</v>
@@ -36596,7 +36596,7 @@
         <v>1</v>
       </c>
       <c r="M742" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N742" s="3" t="s">
         <v>335</v>
@@ -36640,7 +36640,7 @@
         <v>1</v>
       </c>
       <c r="M743" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N743" s="3" t="s">
         <v>210</v>
@@ -36684,7 +36684,7 @@
         <v>1</v>
       </c>
       <c r="M744" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N744" s="3" t="s">
         <v>383</v>
@@ -36728,7 +36728,7 @@
         <v>1</v>
       </c>
       <c r="M745" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N745" s="3" t="s">
         <v>347</v>
@@ -36992,7 +36992,7 @@
         <v>1</v>
       </c>
       <c r="M751" s="22">
-        <v>20120107</v>
+        <v>201200107</v>
       </c>
       <c r="N751" s="3" t="s">
         <v>413</v>
@@ -37036,7 +37036,7 @@
         <v>1</v>
       </c>
       <c r="M752" s="22">
-        <v>20120124</v>
+        <v>201200124</v>
       </c>
       <c r="N752" s="3" t="s">
         <v>405</v>
@@ -37080,7 +37080,7 @@
         <v>1</v>
       </c>
       <c r="M753" s="22">
-        <v>20120125</v>
+        <v>201200125</v>
       </c>
       <c r="N753" s="3" t="s">
         <v>409</v>
@@ -37124,7 +37124,7 @@
         <v>1</v>
       </c>
       <c r="M754" s="22">
-        <v>20120126</v>
+        <v>201200126</v>
       </c>
       <c r="N754" s="3" t="s">
         <v>414</v>
@@ -37168,7 +37168,7 @@
         <v>1</v>
       </c>
       <c r="M755" s="22">
-        <v>20120127</v>
+        <v>201200127</v>
       </c>
       <c r="N755" s="3" t="s">
         <v>418</v>
@@ -37212,7 +37212,7 @@
         <v>1</v>
       </c>
       <c r="M756" s="22">
-        <v>20120140</v>
+        <v>201200140</v>
       </c>
       <c r="N756" s="3" t="s">
         <v>406</v>
@@ -37256,7 +37256,7 @@
         <v>1</v>
       </c>
       <c r="M757" s="22">
-        <v>20120141</v>
+        <v>201200141</v>
       </c>
       <c r="N757" s="3" t="s">
         <v>415</v>
@@ -37300,7 +37300,7 @@
         <v>1</v>
       </c>
       <c r="M758" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N758" s="3" t="s">
         <v>345</v>
@@ -37344,7 +37344,7 @@
         <v>1</v>
       </c>
       <c r="M759" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N759" s="3" t="s">
         <v>346</v>
@@ -37388,7 +37388,7 @@
         <v>1</v>
       </c>
       <c r="M760" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N760" s="3" t="s">
         <v>210</v>
@@ -37432,7 +37432,7 @@
         <v>1</v>
       </c>
       <c r="M761" s="22">
-        <v>20120152</v>
+        <v>201200152</v>
       </c>
       <c r="N761" s="3" t="s">
         <v>383</v>
@@ -37476,7 +37476,7 @@
         <v>1</v>
       </c>
       <c r="M762" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N762" s="3" t="s">
         <v>353</v>
@@ -37696,7 +37696,7 @@
         <v>1</v>
       </c>
       <c r="M767" s="22">
-        <v>20120107</v>
+        <v>201200107</v>
       </c>
       <c r="N767" s="3" t="s">
         <v>413</v>
@@ -37740,7 +37740,7 @@
         <v>1</v>
       </c>
       <c r="M768" s="22">
-        <v>20120125</v>
+        <v>201200125</v>
       </c>
       <c r="N768" s="3" t="s">
         <v>409</v>
@@ -37784,7 +37784,7 @@
         <v>1</v>
       </c>
       <c r="M769" s="22">
-        <v>20120127</v>
+        <v>201200127</v>
       </c>
       <c r="N769" s="3" t="s">
         <v>418</v>
@@ -37828,7 +37828,7 @@
         <v>1</v>
       </c>
       <c r="M770" s="22">
-        <v>20120140</v>
+        <v>201200140</v>
       </c>
       <c r="N770" s="3" t="s">
         <v>406</v>
@@ -37872,7 +37872,7 @@
         <v>1</v>
       </c>
       <c r="M771" s="22">
-        <v>20120141</v>
+        <v>201200141</v>
       </c>
       <c r="N771" s="3" t="s">
         <v>415</v>
@@ -37916,7 +37916,7 @@
         <v>1</v>
       </c>
       <c r="M772" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N772" s="3" t="s">
         <v>334</v>
@@ -37960,7 +37960,7 @@
         <v>1</v>
       </c>
       <c r="M773" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N773" s="3" t="s">
         <v>335</v>
@@ -38004,7 +38004,7 @@
         <v>1</v>
       </c>
       <c r="M774" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N774" s="3" t="s">
         <v>210</v>
@@ -38048,7 +38048,7 @@
         <v>1</v>
       </c>
       <c r="M775" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N775" s="3" t="s">
         <v>420</v>
@@ -38092,7 +38092,7 @@
         <v>1</v>
       </c>
       <c r="M776" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N776" s="3" t="s">
         <v>337</v>
@@ -38312,7 +38312,7 @@
         <v>1</v>
       </c>
       <c r="M781" s="22">
-        <v>20120108</v>
+        <v>201200108</v>
       </c>
       <c r="N781" s="3" t="s">
         <v>423</v>
@@ -38356,7 +38356,7 @@
         <v>1</v>
       </c>
       <c r="M782" s="22">
-        <v>20120126</v>
+        <v>201200126</v>
       </c>
       <c r="N782" s="3" t="s">
         <v>414</v>
@@ -38400,7 +38400,7 @@
         <v>1</v>
       </c>
       <c r="M783" s="22">
-        <v>20120128</v>
+        <v>201200128</v>
       </c>
       <c r="N783" s="3" t="s">
         <v>424</v>
@@ -38444,7 +38444,7 @@
         <v>1</v>
       </c>
       <c r="M784" s="22">
-        <v>20120141</v>
+        <v>201200141</v>
       </c>
       <c r="N784" s="3" t="s">
         <v>415</v>
@@ -38488,7 +38488,7 @@
         <v>1</v>
       </c>
       <c r="M785" s="22">
-        <v>20120142</v>
+        <v>201200142</v>
       </c>
       <c r="N785" s="3" t="s">
         <v>425</v>
@@ -38532,7 +38532,7 @@
         <v>1</v>
       </c>
       <c r="M786" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N786" s="3" t="s">
         <v>345</v>
@@ -38576,7 +38576,7 @@
         <v>1</v>
       </c>
       <c r="M787" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N787" s="3" t="s">
         <v>346</v>
@@ -38620,7 +38620,7 @@
         <v>1</v>
       </c>
       <c r="M788" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N788" s="3" t="s">
         <v>210</v>
@@ -38664,7 +38664,7 @@
         <v>1</v>
       </c>
       <c r="M789" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N789" s="3" t="s">
         <v>420</v>
@@ -38708,7 +38708,7 @@
         <v>1</v>
       </c>
       <c r="M790" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N790" s="3" t="s">
         <v>347</v>
@@ -38972,7 +38972,7 @@
         <v>1</v>
       </c>
       <c r="M796" s="22">
-        <v>20120108</v>
+        <v>201200108</v>
       </c>
       <c r="N796" s="3" t="s">
         <v>423</v>
@@ -39016,7 +39016,7 @@
         <v>1</v>
       </c>
       <c r="M797" s="22">
-        <v>20120126</v>
+        <v>201200126</v>
       </c>
       <c r="N797" s="3" t="s">
         <v>414</v>
@@ -39060,7 +39060,7 @@
         <v>1</v>
       </c>
       <c r="M798" s="22">
-        <v>20120127</v>
+        <v>201200127</v>
       </c>
       <c r="N798" s="3" t="s">
         <v>418</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="M799" s="22">
-        <v>20120128</v>
+        <v>201200128</v>
       </c>
       <c r="N799" s="3" t="s">
         <v>424</v>
@@ -39148,7 +39148,7 @@
         <v>1</v>
       </c>
       <c r="M800" s="22">
-        <v>20120129</v>
+        <v>201200129</v>
       </c>
       <c r="N800" s="3" t="s">
         <v>428</v>
@@ -39192,7 +39192,7 @@
         <v>1</v>
       </c>
       <c r="M801" s="22">
-        <v>20120141</v>
+        <v>201200141</v>
       </c>
       <c r="N801" s="3" t="s">
         <v>415</v>
@@ -39236,7 +39236,7 @@
         <v>1</v>
       </c>
       <c r="M802" s="22">
-        <v>20120142</v>
+        <v>201200142</v>
       </c>
       <c r="N802" s="3" t="s">
         <v>425</v>
@@ -39280,7 +39280,7 @@
         <v>1</v>
       </c>
       <c r="M803" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N803" s="3" t="s">
         <v>334</v>
@@ -39324,7 +39324,7 @@
         <v>1</v>
       </c>
       <c r="M804" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N804" s="3" t="s">
         <v>335</v>
@@ -39368,7 +39368,7 @@
         <v>1</v>
       </c>
       <c r="M805" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N805" s="3" t="s">
         <v>210</v>
@@ -39412,7 +39412,7 @@
         <v>1</v>
       </c>
       <c r="M806" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N806" s="3" t="s">
         <v>420</v>
@@ -39456,7 +39456,7 @@
         <v>1</v>
       </c>
       <c r="M807" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N807" s="3" t="s">
         <v>353</v>
@@ -39676,7 +39676,7 @@
         <v>1</v>
       </c>
       <c r="M812" s="22">
-        <v>20120108</v>
+        <v>201200108</v>
       </c>
       <c r="N812" s="3" t="s">
         <v>423</v>
@@ -39720,7 +39720,7 @@
         <v>1</v>
       </c>
       <c r="M813" s="22">
-        <v>20120127</v>
+        <v>201200127</v>
       </c>
       <c r="N813" s="3" t="s">
         <v>418</v>
@@ -39764,7 +39764,7 @@
         <v>1</v>
       </c>
       <c r="M814" s="22">
-        <v>20120129</v>
+        <v>201200129</v>
       </c>
       <c r="N814" s="3" t="s">
         <v>428</v>
@@ -39808,7 +39808,7 @@
         <v>1</v>
       </c>
       <c r="M815" s="22">
-        <v>20120141</v>
+        <v>201200141</v>
       </c>
       <c r="N815" s="3" t="s">
         <v>415</v>
@@ -39852,7 +39852,7 @@
         <v>1</v>
       </c>
       <c r="M816" s="22">
-        <v>20120142</v>
+        <v>201200142</v>
       </c>
       <c r="N816" s="3" t="s">
         <v>425</v>
@@ -39896,7 +39896,7 @@
         <v>1</v>
       </c>
       <c r="M817" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N817" s="3" t="s">
         <v>345</v>
@@ -39940,7 +39940,7 @@
         <v>1</v>
       </c>
       <c r="M818" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N818" s="3" t="s">
         <v>346</v>
@@ -39984,7 +39984,7 @@
         <v>1</v>
       </c>
       <c r="M819" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N819" s="3" t="s">
         <v>210</v>
@@ -40028,7 +40028,7 @@
         <v>1</v>
       </c>
       <c r="M820" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N820" s="3" t="s">
         <v>420</v>
@@ -40072,7 +40072,7 @@
         <v>1</v>
       </c>
       <c r="M821" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N821" s="3" t="s">
         <v>337</v>
@@ -40292,7 +40292,7 @@
         <v>1</v>
       </c>
       <c r="M826" s="22">
-        <v>20120109</v>
+        <v>201200109</v>
       </c>
       <c r="N826" s="3" t="s">
         <v>432</v>
@@ -40336,7 +40336,7 @@
         <v>1</v>
       </c>
       <c r="M827" s="22">
-        <v>20120128</v>
+        <v>201200128</v>
       </c>
       <c r="N827" s="3" t="s">
         <v>424</v>
@@ -40380,7 +40380,7 @@
         <v>1</v>
       </c>
       <c r="M828" s="22">
-        <v>20120130</v>
+        <v>201200130</v>
       </c>
       <c r="N828" s="3" t="s">
         <v>433</v>
@@ -40424,7 +40424,7 @@
         <v>1</v>
       </c>
       <c r="M829" s="22">
-        <v>20120142</v>
+        <v>201200142</v>
       </c>
       <c r="N829" s="3" t="s">
         <v>425</v>
@@ -40468,7 +40468,7 @@
         <v>1</v>
       </c>
       <c r="M830" s="22">
-        <v>20120143</v>
+        <v>201200143</v>
       </c>
       <c r="N830" s="3" t="s">
         <v>434</v>
@@ -40512,7 +40512,7 @@
         <v>1</v>
       </c>
       <c r="M831" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N831" s="3" t="s">
         <v>334</v>
@@ -40556,7 +40556,7 @@
         <v>1</v>
       </c>
       <c r="M832" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N832" s="3" t="s">
         <v>346</v>
@@ -40600,7 +40600,7 @@
         <v>1</v>
       </c>
       <c r="M833" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N833" s="3" t="s">
         <v>210</v>
@@ -40644,7 +40644,7 @@
         <v>1</v>
       </c>
       <c r="M834" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N834" s="3" t="s">
         <v>420</v>
@@ -40688,7 +40688,7 @@
         <v>1</v>
       </c>
       <c r="M835" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N835" s="3" t="s">
         <v>347</v>
@@ -40952,7 +40952,7 @@
         <v>1</v>
       </c>
       <c r="M841" s="22">
-        <v>20120109</v>
+        <v>201200109</v>
       </c>
       <c r="N841" s="3" t="s">
         <v>432</v>
@@ -40996,7 +40996,7 @@
         <v>1</v>
       </c>
       <c r="M842" s="22">
-        <v>20120128</v>
+        <v>201200128</v>
       </c>
       <c r="N842" s="3" t="s">
         <v>424</v>
@@ -41040,7 +41040,7 @@
         <v>1</v>
       </c>
       <c r="M843" s="22">
-        <v>20120129</v>
+        <v>201200129</v>
       </c>
       <c r="N843" s="3" t="s">
         <v>428</v>
@@ -41084,7 +41084,7 @@
         <v>1</v>
       </c>
       <c r="M844" s="22">
-        <v>20120130</v>
+        <v>201200130</v>
       </c>
       <c r="N844" s="3" t="s">
         <v>433</v>
@@ -41128,7 +41128,7 @@
         <v>1</v>
       </c>
       <c r="M845" s="22">
-        <v>20120131</v>
+        <v>201200131</v>
       </c>
       <c r="N845" s="3" t="s">
         <v>437</v>
@@ -41172,7 +41172,7 @@
         <v>1</v>
       </c>
       <c r="M846" s="22">
-        <v>20120142</v>
+        <v>201200142</v>
       </c>
       <c r="N846" s="3" t="s">
         <v>425</v>
@@ -41216,7 +41216,7 @@
         <v>1</v>
       </c>
       <c r="M847" s="22">
-        <v>20120143</v>
+        <v>201200143</v>
       </c>
       <c r="N847" s="3" t="s">
         <v>434</v>
@@ -41260,7 +41260,7 @@
         <v>1</v>
       </c>
       <c r="M848" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N848" s="3" t="s">
         <v>345</v>
@@ -41304,7 +41304,7 @@
         <v>1</v>
       </c>
       <c r="M849" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N849" s="3" t="s">
         <v>335</v>
@@ -41348,7 +41348,7 @@
         <v>1</v>
       </c>
       <c r="M850" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N850" s="3" t="s">
         <v>210</v>
@@ -41392,7 +41392,7 @@
         <v>1</v>
       </c>
       <c r="M851" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N851" s="3" t="s">
         <v>420</v>
@@ -41436,7 +41436,7 @@
         <v>1</v>
       </c>
       <c r="M852" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N852" s="3" t="s">
         <v>353</v>
@@ -41656,7 +41656,7 @@
         <v>1</v>
       </c>
       <c r="M857" s="22">
-        <v>20120109</v>
+        <v>201200109</v>
       </c>
       <c r="N857" s="3" t="s">
         <v>432</v>
@@ -41700,7 +41700,7 @@
         <v>1</v>
       </c>
       <c r="M858" s="22">
-        <v>20120129</v>
+        <v>201200129</v>
       </c>
       <c r="N858" s="3" t="s">
         <v>428</v>
@@ -41744,7 +41744,7 @@
         <v>1</v>
       </c>
       <c r="M859" s="22">
-        <v>20120131</v>
+        <v>201200131</v>
       </c>
       <c r="N859" s="3" t="s">
         <v>437</v>
@@ -41788,7 +41788,7 @@
         <v>1</v>
       </c>
       <c r="M860" s="22">
-        <v>20120142</v>
+        <v>201200142</v>
       </c>
       <c r="N860" s="3" t="s">
         <v>425</v>
@@ -41832,7 +41832,7 @@
         <v>1</v>
       </c>
       <c r="M861" s="22">
-        <v>20120143</v>
+        <v>201200143</v>
       </c>
       <c r="N861" s="3" t="s">
         <v>434</v>
@@ -41876,7 +41876,7 @@
         <v>1</v>
       </c>
       <c r="M862" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N862" s="3" t="s">
         <v>334</v>
@@ -41920,7 +41920,7 @@
         <v>1</v>
       </c>
       <c r="M863" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N863" s="3" t="s">
         <v>346</v>
@@ -41964,7 +41964,7 @@
         <v>1</v>
       </c>
       <c r="M864" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N864" s="3" t="s">
         <v>210</v>
@@ -42008,7 +42008,7 @@
         <v>1</v>
       </c>
       <c r="M865" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N865" s="3" t="s">
         <v>420</v>
@@ -42052,7 +42052,7 @@
         <v>1</v>
       </c>
       <c r="M866" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N866" s="3" t="s">
         <v>337</v>
@@ -42272,7 +42272,7 @@
         <v>1</v>
       </c>
       <c r="M871" s="22">
-        <v>20120110</v>
+        <v>201200110</v>
       </c>
       <c r="N871" s="3" t="s">
         <v>441</v>
@@ -42316,7 +42316,7 @@
         <v>1</v>
       </c>
       <c r="M872" s="22">
-        <v>20120130</v>
+        <v>201200130</v>
       </c>
       <c r="N872" s="3" t="s">
         <v>433</v>
@@ -42360,7 +42360,7 @@
         <v>1</v>
       </c>
       <c r="M873" s="22">
-        <v>20120132</v>
+        <v>201200132</v>
       </c>
       <c r="N873" s="3" t="s">
         <v>442</v>
@@ -42404,7 +42404,7 @@
         <v>1</v>
       </c>
       <c r="M874" s="22">
-        <v>20120143</v>
+        <v>201200143</v>
       </c>
       <c r="N874" s="3" t="s">
         <v>434</v>
@@ -42448,7 +42448,7 @@
         <v>1</v>
       </c>
       <c r="M875" s="22">
-        <v>20120144</v>
+        <v>201200144</v>
       </c>
       <c r="N875" s="3" t="s">
         <v>443</v>
@@ -42492,7 +42492,7 @@
         <v>1</v>
       </c>
       <c r="M876" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N876" s="3" t="s">
         <v>345</v>
@@ -42536,7 +42536,7 @@
         <v>1</v>
       </c>
       <c r="M877" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N877" s="3" t="s">
         <v>335</v>
@@ -42580,7 +42580,7 @@
         <v>1</v>
       </c>
       <c r="M878" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N878" s="3" t="s">
         <v>210</v>
@@ -42624,7 +42624,7 @@
         <v>1</v>
       </c>
       <c r="M879" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N879" s="3" t="s">
         <v>420</v>
@@ -42668,7 +42668,7 @@
         <v>1</v>
       </c>
       <c r="M880" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N880" s="3" t="s">
         <v>347</v>
@@ -42932,7 +42932,7 @@
         <v>1</v>
       </c>
       <c r="M886" s="22">
-        <v>20120110</v>
+        <v>201200110</v>
       </c>
       <c r="N886" s="3" t="s">
         <v>441</v>
@@ -42976,7 +42976,7 @@
         <v>1</v>
       </c>
       <c r="M887" s="22">
-        <v>20120130</v>
+        <v>201200130</v>
       </c>
       <c r="N887" s="3" t="s">
         <v>433</v>
@@ -43020,7 +43020,7 @@
         <v>1</v>
       </c>
       <c r="M888" s="22">
-        <v>20120131</v>
+        <v>201200131</v>
       </c>
       <c r="N888" s="3" t="s">
         <v>437</v>
@@ -43064,7 +43064,7 @@
         <v>1</v>
       </c>
       <c r="M889" s="22">
-        <v>20120132</v>
+        <v>201200132</v>
       </c>
       <c r="N889" s="3" t="s">
         <v>442</v>
@@ -43108,7 +43108,7 @@
         <v>1</v>
       </c>
       <c r="M890" s="22">
-        <v>20120133</v>
+        <v>201200133</v>
       </c>
       <c r="N890" s="3" t="s">
         <v>446</v>
@@ -43152,7 +43152,7 @@
         <v>1</v>
       </c>
       <c r="M891" s="22">
-        <v>20120143</v>
+        <v>201200143</v>
       </c>
       <c r="N891" s="3" t="s">
         <v>434</v>
@@ -43196,7 +43196,7 @@
         <v>1</v>
       </c>
       <c r="M892" s="22">
-        <v>20120144</v>
+        <v>201200144</v>
       </c>
       <c r="N892" s="3" t="s">
         <v>443</v>
@@ -43240,7 +43240,7 @@
         <v>1</v>
       </c>
       <c r="M893" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N893" s="3" t="s">
         <v>334</v>
@@ -43284,7 +43284,7 @@
         <v>1</v>
       </c>
       <c r="M894" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N894" s="3" t="s">
         <v>346</v>
@@ -43328,7 +43328,7 @@
         <v>1</v>
       </c>
       <c r="M895" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N895" s="3" t="s">
         <v>210</v>
@@ -43372,7 +43372,7 @@
         <v>1</v>
       </c>
       <c r="M896" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N896" s="3" t="s">
         <v>420</v>
@@ -43416,7 +43416,7 @@
         <v>1</v>
       </c>
       <c r="M897" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N897" s="3" t="s">
         <v>353</v>
@@ -43636,7 +43636,7 @@
         <v>1</v>
       </c>
       <c r="M902" s="22">
-        <v>20120110</v>
+        <v>201200110</v>
       </c>
       <c r="N902" s="3" t="s">
         <v>441</v>
@@ -43680,7 +43680,7 @@
         <v>1</v>
       </c>
       <c r="M903" s="22">
-        <v>20120131</v>
+        <v>201200131</v>
       </c>
       <c r="N903" s="3" t="s">
         <v>437</v>
@@ -43724,7 +43724,7 @@
         <v>1</v>
       </c>
       <c r="M904" s="22">
-        <v>20120133</v>
+        <v>201200133</v>
       </c>
       <c r="N904" s="3" t="s">
         <v>446</v>
@@ -43768,7 +43768,7 @@
         <v>1</v>
       </c>
       <c r="M905" s="22">
-        <v>20120143</v>
+        <v>201200143</v>
       </c>
       <c r="N905" s="3" t="s">
         <v>434</v>
@@ -43812,7 +43812,7 @@
         <v>1</v>
       </c>
       <c r="M906" s="22">
-        <v>20120144</v>
+        <v>201200144</v>
       </c>
       <c r="N906" s="3" t="s">
         <v>443</v>
@@ -43856,7 +43856,7 @@
         <v>1</v>
       </c>
       <c r="M907" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N907" s="3" t="s">
         <v>345</v>
@@ -43900,7 +43900,7 @@
         <v>1</v>
       </c>
       <c r="M908" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N908" s="3" t="s">
         <v>335</v>
@@ -43944,7 +43944,7 @@
         <v>1</v>
       </c>
       <c r="M909" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N909" s="3" t="s">
         <v>210</v>
@@ -43988,7 +43988,7 @@
         <v>1</v>
       </c>
       <c r="M910" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N910" s="3" t="s">
         <v>420</v>
@@ -44032,7 +44032,7 @@
         <v>1</v>
       </c>
       <c r="M911" s="22">
-        <v>20120154</v>
+        <v>201200154</v>
       </c>
       <c r="N911" s="3" t="s">
         <v>337</v>
@@ -44208,7 +44208,7 @@
         <v>1</v>
       </c>
       <c r="M915" s="22">
-        <v>20120111</v>
+        <v>201200111</v>
       </c>
       <c r="N915" s="3" t="s">
         <v>449</v>
@@ -44252,7 +44252,7 @@
         <v>1</v>
       </c>
       <c r="M916" s="22">
-        <v>20120132</v>
+        <v>201200132</v>
       </c>
       <c r="N916" s="3" t="s">
         <v>442</v>
@@ -44296,7 +44296,7 @@
         <v>1</v>
       </c>
       <c r="M917" s="22">
-        <v>20120144</v>
+        <v>201200144</v>
       </c>
       <c r="N917" s="3" t="s">
         <v>443</v>
@@ -44340,7 +44340,7 @@
         <v>1</v>
       </c>
       <c r="M918" s="22">
-        <v>20120147</v>
+        <v>201200147</v>
       </c>
       <c r="N918" s="3" t="s">
         <v>334</v>
@@ -44384,7 +44384,7 @@
         <v>1</v>
       </c>
       <c r="M919" s="22">
-        <v>20120146</v>
+        <v>201200146</v>
       </c>
       <c r="N919" s="3" t="s">
         <v>346</v>
@@ -44428,7 +44428,7 @@
         <v>1</v>
       </c>
       <c r="M920" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N920" s="3" t="s">
         <v>210</v>
@@ -44472,7 +44472,7 @@
         <v>1</v>
       </c>
       <c r="M921" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N921" s="3" t="s">
         <v>420</v>
@@ -44516,7 +44516,7 @@
         <v>1</v>
       </c>
       <c r="M922" s="22">
-        <v>20120155</v>
+        <v>201200155</v>
       </c>
       <c r="N922" s="3" t="s">
         <v>347</v>
@@ -44736,7 +44736,7 @@
         <v>1</v>
       </c>
       <c r="M927" s="22">
-        <v>20120111</v>
+        <v>201200111</v>
       </c>
       <c r="N927" s="3" t="s">
         <v>449</v>
@@ -44780,7 +44780,7 @@
         <v>1</v>
       </c>
       <c r="M928" s="22">
-        <v>20120132</v>
+        <v>201200132</v>
       </c>
       <c r="N928" s="3" t="s">
         <v>442</v>
@@ -44824,7 +44824,7 @@
         <v>1</v>
       </c>
       <c r="M929" s="22">
-        <v>20120133</v>
+        <v>201200133</v>
       </c>
       <c r="N929" s="3" t="s">
         <v>446</v>
@@ -44868,7 +44868,7 @@
         <v>1</v>
       </c>
       <c r="M930" s="22">
-        <v>20120144</v>
+        <v>201200144</v>
       </c>
       <c r="N930" s="3" t="s">
         <v>443</v>
@@ -44912,7 +44912,7 @@
         <v>1</v>
       </c>
       <c r="M931" s="22">
-        <v>20120148</v>
+        <v>201200148</v>
       </c>
       <c r="N931" s="3" t="s">
         <v>345</v>
@@ -44956,7 +44956,7 @@
         <v>1</v>
       </c>
       <c r="M932" s="22">
-        <v>20120145</v>
+        <v>201200145</v>
       </c>
       <c r="N932" s="3" t="s">
         <v>335</v>
@@ -45000,7 +45000,7 @@
         <v>1</v>
       </c>
       <c r="M933" s="22">
-        <v>20120149</v>
+        <v>201200149</v>
       </c>
       <c r="N933" s="3" t="s">
         <v>210</v>
@@ -45044,7 +45044,7 @@
         <v>1</v>
       </c>
       <c r="M934" s="22">
-        <v>20120153</v>
+        <v>201200153</v>
       </c>
       <c r="N934" s="3" t="s">
         <v>420</v>
@@ -45088,7 +45088,7 @@
         <v>1</v>
       </c>
       <c r="M935" s="22">
-        <v>20120156</v>
+        <v>201200156</v>
       </c>
       <c r="N935" s="3" t="s">
         <v>353</v>
@@ -45264,7 +45264,7 @@
         <v>1</v>
       </c>
       <c r="M939" s="22">
-        <v>20120111</v>
+        <v>201200111</v>
       </c>
       <c r="N939" s="3" t="s">
         <v>449</v>
@@ -45308,7 +45308,7 @@
         <v>1</v>
       </c>
       <c r="M940" s="22">
-        <v>20120133</v>
+        <v>201200133</v>
       </c>
       <c r="N940" s="3" t="s">
         <v>446</v>
@@ -45352,7 +45352,7 @@
         <v>1</v>
       </c>
       <c r="M941" s="22">
-        <v>20120144</v>
+        <v>201200144</v>
       </c>
       <c r="N941" s="3" t="s">
         <v>443</v>
@@ -45626,7 +45626,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:U478" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:U947" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="S337">

--- a/table/resources/sample/WinPosWeight.xlsx
+++ b/table/resources/sample/WinPosWeight.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="WinPosWeight" sheetId="20" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WinPosWeight!$A$1:$U$947</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WinPosWeight!$A$1:$U$478</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -22252,7 +22252,7 @@
         <v>1</v>
       </c>
       <c r="M416" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N416" s="3" t="s">
         <v>334</v>
@@ -22296,7 +22296,7 @@
         <v>1</v>
       </c>
       <c r="M417" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N417" s="3" t="s">
         <v>335</v>
@@ -22340,7 +22340,7 @@
         <v>1</v>
       </c>
       <c r="M418" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N418" s="3" t="s">
         <v>187</v>
@@ -22384,7 +22384,7 @@
         <v>1</v>
       </c>
       <c r="M419" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N419" s="23" t="s">
         <v>336</v>
@@ -22428,7 +22428,7 @@
         <v>1</v>
       </c>
       <c r="M420" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N420" s="3" t="s">
         <v>337</v>
@@ -22692,7 +22692,7 @@
         <v>1</v>
       </c>
       <c r="M426" s="22">
-        <v>201200100</v>
+        <v>20120100</v>
       </c>
       <c r="N426" s="3" t="s">
         <v>342</v>
@@ -22736,7 +22736,7 @@
         <v>1</v>
       </c>
       <c r="M427" s="22">
-        <v>201200112</v>
+        <v>20120112</v>
       </c>
       <c r="N427" s="3" t="s">
         <v>343</v>
@@ -22780,7 +22780,7 @@
         <v>1</v>
       </c>
       <c r="M428" s="22">
-        <v>201200134</v>
+        <v>20120134</v>
       </c>
       <c r="N428" s="3" t="s">
         <v>344</v>
@@ -22824,7 +22824,7 @@
         <v>1</v>
       </c>
       <c r="M429" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N429" s="3" t="s">
         <v>345</v>
@@ -22868,7 +22868,7 @@
         <v>1</v>
       </c>
       <c r="M430" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N430" s="3" t="s">
         <v>346</v>
@@ -22912,7 +22912,7 @@
         <v>1</v>
       </c>
       <c r="M431" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N431" s="3" t="s">
         <v>187</v>
@@ -22956,7 +22956,7 @@
         <v>1</v>
       </c>
       <c r="M432" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N432" s="3" t="s">
         <v>336</v>
@@ -23000,7 +23000,7 @@
         <v>1</v>
       </c>
       <c r="M433" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N433" s="3" t="s">
         <v>347</v>
@@ -23352,7 +23352,7 @@
         <v>1</v>
       </c>
       <c r="M441" s="22">
-        <v>201200100</v>
+        <v>20120100</v>
       </c>
       <c r="N441" s="3" t="s">
         <v>342</v>
@@ -23396,7 +23396,7 @@
         <v>1</v>
       </c>
       <c r="M442" s="22">
-        <v>201200112</v>
+        <v>20120112</v>
       </c>
       <c r="N442" s="3" t="s">
         <v>343</v>
@@ -23440,7 +23440,7 @@
         <v>1</v>
       </c>
       <c r="M443" s="22">
-        <v>201200113</v>
+        <v>20120113</v>
       </c>
       <c r="N443" s="3" t="s">
         <v>352</v>
@@ -23484,7 +23484,7 @@
         <v>1</v>
       </c>
       <c r="M444" s="22">
-        <v>201200134</v>
+        <v>20120134</v>
       </c>
       <c r="N444" s="3" t="s">
         <v>344</v>
@@ -23528,7 +23528,7 @@
         <v>1</v>
       </c>
       <c r="M445" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N445" s="3" t="s">
         <v>334</v>
@@ -23572,7 +23572,7 @@
         <v>1</v>
       </c>
       <c r="M446" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N446" s="3" t="s">
         <v>335</v>
@@ -23616,7 +23616,7 @@
         <v>1</v>
       </c>
       <c r="M447" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N447" s="3" t="s">
         <v>187</v>
@@ -23660,7 +23660,7 @@
         <v>1</v>
       </c>
       <c r="M448" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N448" s="3" t="s">
         <v>336</v>
@@ -23704,7 +23704,7 @@
         <v>1</v>
       </c>
       <c r="M449" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N449" s="3" t="s">
         <v>353</v>
@@ -23968,7 +23968,7 @@
         <v>1</v>
       </c>
       <c r="M455" s="22">
-        <v>201200100</v>
+        <v>20120100</v>
       </c>
       <c r="N455" s="3" t="s">
         <v>342</v>
@@ -24012,7 +24012,7 @@
         <v>1</v>
       </c>
       <c r="M456" s="22">
-        <v>201200113</v>
+        <v>20120113</v>
       </c>
       <c r="N456" s="3" t="s">
         <v>352</v>
@@ -24056,7 +24056,7 @@
         <v>1</v>
       </c>
       <c r="M457" s="22">
-        <v>201200134</v>
+        <v>20120134</v>
       </c>
       <c r="N457" s="3" t="s">
         <v>344</v>
@@ -24100,7 +24100,7 @@
         <v>1</v>
       </c>
       <c r="M458" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N458" s="3" t="s">
         <v>345</v>
@@ -24144,7 +24144,7 @@
         <v>1</v>
       </c>
       <c r="M459" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N459" s="3" t="s">
         <v>346</v>
@@ -24188,7 +24188,7 @@
         <v>1</v>
       </c>
       <c r="M460" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N460" s="3" t="s">
         <v>187</v>
@@ -24232,7 +24232,7 @@
         <v>1</v>
       </c>
       <c r="M461" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N461" s="3" t="s">
         <v>336</v>
@@ -24276,7 +24276,7 @@
         <v>1</v>
       </c>
       <c r="M462" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N462" s="3" t="s">
         <v>337</v>
@@ -24496,7 +24496,7 @@
         <v>1</v>
       </c>
       <c r="M467" s="22">
-        <v>201200101</v>
+        <v>20120101</v>
       </c>
       <c r="N467" s="3" t="s">
         <v>358</v>
@@ -24540,7 +24540,7 @@
         <v>1</v>
       </c>
       <c r="M468" s="22">
-        <v>201200112</v>
+        <v>20120112</v>
       </c>
       <c r="N468" s="3" t="s">
         <v>343</v>
@@ -24584,7 +24584,7 @@
         <v>1</v>
       </c>
       <c r="M469" s="22">
-        <v>201200114</v>
+        <v>20120114</v>
       </c>
       <c r="N469" s="3" t="s">
         <v>359</v>
@@ -24628,7 +24628,7 @@
         <v>1</v>
       </c>
       <c r="M470" s="22">
-        <v>201200134</v>
+        <v>20120134</v>
       </c>
       <c r="N470" s="3" t="s">
         <v>344</v>
@@ -24672,7 +24672,7 @@
         <v>1</v>
       </c>
       <c r="M471" s="22">
-        <v>201200135</v>
+        <v>20120135</v>
       </c>
       <c r="N471" s="3" t="s">
         <v>360</v>
@@ -24716,7 +24716,7 @@
         <v>1</v>
       </c>
       <c r="M472" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N472" s="3" t="s">
         <v>334</v>
@@ -24760,7 +24760,7 @@
         <v>1</v>
       </c>
       <c r="M473" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N473" s="3" t="s">
         <v>335</v>
@@ -24804,7 +24804,7 @@
         <v>1</v>
       </c>
       <c r="M474" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N474" s="3" t="s">
         <v>187</v>
@@ -24848,7 +24848,7 @@
         <v>1</v>
       </c>
       <c r="M475" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N475" s="3" t="s">
         <v>336</v>
@@ -24892,7 +24892,7 @@
         <v>1</v>
       </c>
       <c r="M476" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N476" s="3" t="s">
         <v>347</v>
@@ -25156,7 +25156,7 @@
         <v>1</v>
       </c>
       <c r="M482" s="22">
-        <v>201200101</v>
+        <v>20120101</v>
       </c>
       <c r="N482" s="3" t="s">
         <v>358</v>
@@ -25200,7 +25200,7 @@
         <v>1</v>
       </c>
       <c r="M483" s="22">
-        <v>201200112</v>
+        <v>20120112</v>
       </c>
       <c r="N483" s="3" t="s">
         <v>343</v>
@@ -25244,7 +25244,7 @@
         <v>1</v>
       </c>
       <c r="M484" s="22">
-        <v>201200113</v>
+        <v>20120113</v>
       </c>
       <c r="N484" s="3" t="s">
         <v>352</v>
@@ -25288,7 +25288,7 @@
         <v>1</v>
       </c>
       <c r="M485" s="22">
-        <v>201200114</v>
+        <v>20120114</v>
       </c>
       <c r="N485" s="3" t="s">
         <v>359</v>
@@ -25332,7 +25332,7 @@
         <v>1</v>
       </c>
       <c r="M486" s="22">
-        <v>201200115</v>
+        <v>20120115</v>
       </c>
       <c r="N486" s="3" t="s">
         <v>363</v>
@@ -25376,7 +25376,7 @@
         <v>1</v>
       </c>
       <c r="M487" s="22">
-        <v>201200134</v>
+        <v>20120134</v>
       </c>
       <c r="N487" s="3" t="s">
         <v>344</v>
@@ -25420,7 +25420,7 @@
         <v>1</v>
       </c>
       <c r="M488" s="22">
-        <v>201200135</v>
+        <v>20120135</v>
       </c>
       <c r="N488" s="3" t="s">
         <v>360</v>
@@ -25464,7 +25464,7 @@
         <v>1</v>
       </c>
       <c r="M489" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N489" s="3" t="s">
         <v>345</v>
@@ -25508,7 +25508,7 @@
         <v>1</v>
       </c>
       <c r="M490" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N490" s="3" t="s">
         <v>346</v>
@@ -25552,7 +25552,7 @@
         <v>1</v>
       </c>
       <c r="M491" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N491" s="3" t="s">
         <v>187</v>
@@ -25596,7 +25596,7 @@
         <v>1</v>
       </c>
       <c r="M492" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N492" s="3" t="s">
         <v>336</v>
@@ -25640,7 +25640,7 @@
         <v>1</v>
       </c>
       <c r="M493" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N493" s="3" t="s">
         <v>353</v>
@@ -25860,7 +25860,7 @@
         <v>1</v>
       </c>
       <c r="M498" s="22">
-        <v>201200101</v>
+        <v>20120101</v>
       </c>
       <c r="N498" s="3" t="s">
         <v>358</v>
@@ -25904,7 +25904,7 @@
         <v>1</v>
       </c>
       <c r="M499" s="22">
-        <v>201200113</v>
+        <v>20120113</v>
       </c>
       <c r="N499" s="3" t="s">
         <v>352</v>
@@ -25948,7 +25948,7 @@
         <v>1</v>
       </c>
       <c r="M500" s="22">
-        <v>201200115</v>
+        <v>20120115</v>
       </c>
       <c r="N500" s="3" t="s">
         <v>363</v>
@@ -25992,7 +25992,7 @@
         <v>1</v>
       </c>
       <c r="M501" s="22">
-        <v>201200134</v>
+        <v>20120134</v>
       </c>
       <c r="N501" s="3" t="s">
         <v>344</v>
@@ -26036,7 +26036,7 @@
         <v>1</v>
       </c>
       <c r="M502" s="22">
-        <v>201200135</v>
+        <v>20120135</v>
       </c>
       <c r="N502" s="3" t="s">
         <v>360</v>
@@ -26080,7 +26080,7 @@
         <v>1</v>
       </c>
       <c r="M503" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N503" s="3" t="s">
         <v>334</v>
@@ -26124,7 +26124,7 @@
         <v>1</v>
       </c>
       <c r="M504" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N504" s="3" t="s">
         <v>335</v>
@@ -26168,7 +26168,7 @@
         <v>1</v>
       </c>
       <c r="M505" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N505" s="3" t="s">
         <v>187</v>
@@ -26212,7 +26212,7 @@
         <v>1</v>
       </c>
       <c r="M506" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N506" s="3" t="s">
         <v>336</v>
@@ -26256,7 +26256,7 @@
         <v>1</v>
       </c>
       <c r="M507" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N507" s="3" t="s">
         <v>337</v>
@@ -26476,7 +26476,7 @@
         <v>1</v>
       </c>
       <c r="M512" s="22">
-        <v>201200102</v>
+        <v>20120102</v>
       </c>
       <c r="N512" s="3" t="s">
         <v>367</v>
@@ -26520,7 +26520,7 @@
         <v>1</v>
       </c>
       <c r="M513" s="22">
-        <v>201200114</v>
+        <v>20120114</v>
       </c>
       <c r="N513" s="3" t="s">
         <v>359</v>
@@ -26564,7 +26564,7 @@
         <v>1</v>
       </c>
       <c r="M514" s="22">
-        <v>201200116</v>
+        <v>20120116</v>
       </c>
       <c r="N514" s="3" t="s">
         <v>368</v>
@@ -26608,7 +26608,7 @@
         <v>1</v>
       </c>
       <c r="M515" s="22">
-        <v>201200135</v>
+        <v>20120135</v>
       </c>
       <c r="N515" s="3" t="s">
         <v>360</v>
@@ -26652,7 +26652,7 @@
         <v>1</v>
       </c>
       <c r="M516" s="22">
-        <v>201200136</v>
+        <v>20120136</v>
       </c>
       <c r="N516" s="3" t="s">
         <v>369</v>
@@ -26696,7 +26696,7 @@
         <v>1</v>
       </c>
       <c r="M517" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N517" s="3" t="s">
         <v>345</v>
@@ -26740,7 +26740,7 @@
         <v>1</v>
       </c>
       <c r="M518" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N518" s="3" t="s">
         <v>346</v>
@@ -26784,7 +26784,7 @@
         <v>1</v>
       </c>
       <c r="M519" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N519" s="3" t="s">
         <v>187</v>
@@ -26828,7 +26828,7 @@
         <v>1</v>
       </c>
       <c r="M520" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N520" s="3" t="s">
         <v>336</v>
@@ -26872,7 +26872,7 @@
         <v>1</v>
       </c>
       <c r="M521" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N521" s="3" t="s">
         <v>347</v>
@@ -27136,7 +27136,7 @@
         <v>1</v>
       </c>
       <c r="M527" s="22">
-        <v>201200102</v>
+        <v>20120102</v>
       </c>
       <c r="N527" s="3" t="s">
         <v>367</v>
@@ -27180,7 +27180,7 @@
         <v>1</v>
       </c>
       <c r="M528" s="22">
-        <v>201200114</v>
+        <v>20120114</v>
       </c>
       <c r="N528" s="3" t="s">
         <v>359</v>
@@ -27224,7 +27224,7 @@
         <v>1</v>
       </c>
       <c r="M529" s="22">
-        <v>201200115</v>
+        <v>20120115</v>
       </c>
       <c r="N529" s="3" t="s">
         <v>363</v>
@@ -27268,7 +27268,7 @@
         <v>1</v>
       </c>
       <c r="M530" s="22">
-        <v>201200116</v>
+        <v>20120116</v>
       </c>
       <c r="N530" s="3" t="s">
         <v>368</v>
@@ -27312,7 +27312,7 @@
         <v>1</v>
       </c>
       <c r="M531" s="22">
-        <v>201200117</v>
+        <v>20120117</v>
       </c>
       <c r="N531" s="3" t="s">
         <v>372</v>
@@ -27356,7 +27356,7 @@
         <v>1</v>
       </c>
       <c r="M532" s="22">
-        <v>201200135</v>
+        <v>20120135</v>
       </c>
       <c r="N532" s="3" t="s">
         <v>360</v>
@@ -27400,7 +27400,7 @@
         <v>1</v>
       </c>
       <c r="M533" s="22">
-        <v>201200136</v>
+        <v>20120136</v>
       </c>
       <c r="N533" s="3" t="s">
         <v>369</v>
@@ -27444,7 +27444,7 @@
         <v>1</v>
       </c>
       <c r="M534" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N534" s="3" t="s">
         <v>334</v>
@@ -27488,7 +27488,7 @@
         <v>1</v>
       </c>
       <c r="M535" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N535" s="3" t="s">
         <v>335</v>
@@ -27532,7 +27532,7 @@
         <v>1</v>
       </c>
       <c r="M536" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N536" s="3" t="s">
         <v>187</v>
@@ -27576,7 +27576,7 @@
         <v>1</v>
       </c>
       <c r="M537" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N537" s="3" t="s">
         <v>336</v>
@@ -27620,7 +27620,7 @@
         <v>1</v>
       </c>
       <c r="M538" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N538" s="3" t="s">
         <v>353</v>
@@ -27840,7 +27840,7 @@
         <v>1</v>
       </c>
       <c r="M543" s="22">
-        <v>201200102</v>
+        <v>20120102</v>
       </c>
       <c r="N543" s="3" t="s">
         <v>367</v>
@@ -27884,7 +27884,7 @@
         <v>1</v>
       </c>
       <c r="M544" s="22">
-        <v>201200115</v>
+        <v>20120115</v>
       </c>
       <c r="N544" s="3" t="s">
         <v>363</v>
@@ -27928,7 +27928,7 @@
         <v>1</v>
       </c>
       <c r="M545" s="22">
-        <v>201200117</v>
+        <v>20120117</v>
       </c>
       <c r="N545" s="3" t="s">
         <v>372</v>
@@ -27972,7 +27972,7 @@
         <v>1</v>
       </c>
       <c r="M546" s="22">
-        <v>201200135</v>
+        <v>20120135</v>
       </c>
       <c r="N546" s="3" t="s">
         <v>360</v>
@@ -28016,7 +28016,7 @@
         <v>1</v>
       </c>
       <c r="M547" s="22">
-        <v>201200136</v>
+        <v>20120136</v>
       </c>
       <c r="N547" s="3" t="s">
         <v>369</v>
@@ -28060,7 +28060,7 @@
         <v>1</v>
       </c>
       <c r="M548" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N548" s="3" t="s">
         <v>345</v>
@@ -28104,7 +28104,7 @@
         <v>1</v>
       </c>
       <c r="M549" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N549" s="3" t="s">
         <v>346</v>
@@ -28148,7 +28148,7 @@
         <v>1</v>
       </c>
       <c r="M550" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N550" s="3" t="s">
         <v>187</v>
@@ -28192,7 +28192,7 @@
         <v>1</v>
       </c>
       <c r="M551" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N551" s="3" t="s">
         <v>336</v>
@@ -28236,7 +28236,7 @@
         <v>1</v>
       </c>
       <c r="M552" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N552" s="3" t="s">
         <v>337</v>
@@ -28456,7 +28456,7 @@
         <v>1</v>
       </c>
       <c r="M557" s="22">
-        <v>201200103</v>
+        <v>20120103</v>
       </c>
       <c r="N557" s="3" t="s">
         <v>376</v>
@@ -28500,7 +28500,7 @@
         <v>1</v>
       </c>
       <c r="M558" s="22">
-        <v>201200116</v>
+        <v>20120116</v>
       </c>
       <c r="N558" s="3" t="s">
         <v>368</v>
@@ -28544,7 +28544,7 @@
         <v>1</v>
       </c>
       <c r="M559" s="22">
-        <v>201200118</v>
+        <v>20120118</v>
       </c>
       <c r="N559" s="3" t="s">
         <v>377</v>
@@ -28588,7 +28588,7 @@
         <v>1</v>
       </c>
       <c r="M560" s="22">
-        <v>201200137</v>
+        <v>20120137</v>
       </c>
       <c r="N560" s="3" t="s">
         <v>378</v>
@@ -28632,7 +28632,7 @@
         <v>1</v>
       </c>
       <c r="M561" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N561" s="3" t="s">
         <v>334</v>
@@ -28676,7 +28676,7 @@
         <v>1</v>
       </c>
       <c r="M562" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N562" s="3" t="s">
         <v>346</v>
@@ -28720,7 +28720,7 @@
         <v>1</v>
       </c>
       <c r="M563" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N563" s="3" t="s">
         <v>187</v>
@@ -28764,7 +28764,7 @@
         <v>1</v>
       </c>
       <c r="M564" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N564" s="3" t="s">
         <v>336</v>
@@ -28808,7 +28808,7 @@
         <v>1</v>
       </c>
       <c r="M565" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N565" s="3" t="s">
         <v>347</v>
@@ -29072,7 +29072,7 @@
         <v>1</v>
       </c>
       <c r="M571" s="22">
-        <v>201200103</v>
+        <v>20120103</v>
       </c>
       <c r="N571" s="3" t="s">
         <v>376</v>
@@ -29116,7 +29116,7 @@
         <v>1</v>
       </c>
       <c r="M572" s="22">
-        <v>201200116</v>
+        <v>20120116</v>
       </c>
       <c r="N572" s="3" t="s">
         <v>368</v>
@@ -29160,7 +29160,7 @@
         <v>1</v>
       </c>
       <c r="M573" s="22">
-        <v>201200117</v>
+        <v>20120117</v>
       </c>
       <c r="N573" s="3" t="s">
         <v>372</v>
@@ -29204,7 +29204,7 @@
         <v>1</v>
       </c>
       <c r="M574" s="22">
-        <v>201200118</v>
+        <v>20120118</v>
       </c>
       <c r="N574" s="3" t="s">
         <v>377</v>
@@ -29248,7 +29248,7 @@
         <v>1</v>
       </c>
       <c r="M575" s="22">
-        <v>201200119</v>
+        <v>20120119</v>
       </c>
       <c r="N575" s="3" t="s">
         <v>381</v>
@@ -29292,7 +29292,7 @@
         <v>1</v>
       </c>
       <c r="M576" s="22">
-        <v>201200136</v>
+        <v>20120136</v>
       </c>
       <c r="N576" s="3" t="s">
         <v>369</v>
@@ -29336,7 +29336,7 @@
         <v>1</v>
       </c>
       <c r="M577" s="22">
-        <v>201200137</v>
+        <v>20120137</v>
       </c>
       <c r="N577" s="3" t="s">
         <v>378</v>
@@ -29380,7 +29380,7 @@
         <v>1</v>
       </c>
       <c r="M578" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N578" s="3" t="s">
         <v>345</v>
@@ -29424,7 +29424,7 @@
         <v>1</v>
       </c>
       <c r="M579" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N579" s="3" t="s">
         <v>335</v>
@@ -29468,7 +29468,7 @@
         <v>1</v>
       </c>
       <c r="M580" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N580" s="3" t="s">
         <v>187</v>
@@ -29512,7 +29512,7 @@
         <v>1</v>
       </c>
       <c r="M581" s="22">
-        <v>201200151</v>
+        <v>20120151</v>
       </c>
       <c r="N581" s="3" t="s">
         <v>336</v>
@@ -29556,7 +29556,7 @@
         <v>1</v>
       </c>
       <c r="M582" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N582" s="3" t="s">
         <v>353</v>
@@ -29776,7 +29776,7 @@
         <v>1</v>
       </c>
       <c r="M587" s="22">
-        <v>201200103</v>
+        <v>20120103</v>
       </c>
       <c r="N587" s="3" t="s">
         <v>376</v>
@@ -29820,7 +29820,7 @@
         <v>1</v>
       </c>
       <c r="M588" s="22">
-        <v>201200117</v>
+        <v>20120117</v>
       </c>
       <c r="N588" s="3" t="s">
         <v>372</v>
@@ -29864,7 +29864,7 @@
         <v>1</v>
       </c>
       <c r="M589" s="22">
-        <v>201200119</v>
+        <v>20120119</v>
       </c>
       <c r="N589" s="3" t="s">
         <v>381</v>
@@ -29908,7 +29908,7 @@
         <v>1</v>
       </c>
       <c r="M590" s="22">
-        <v>201200136</v>
+        <v>20120136</v>
       </c>
       <c r="N590" s="3" t="s">
         <v>369</v>
@@ -29952,7 +29952,7 @@
         <v>1</v>
       </c>
       <c r="M591" s="22">
-        <v>201200137</v>
+        <v>20120137</v>
       </c>
       <c r="N591" s="3" t="s">
         <v>378</v>
@@ -29996,7 +29996,7 @@
         <v>1</v>
       </c>
       <c r="M592" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N592" s="3" t="s">
         <v>334</v>
@@ -30040,7 +30040,7 @@
         <v>1</v>
       </c>
       <c r="M593" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N593" s="3" t="s">
         <v>346</v>
@@ -30084,7 +30084,7 @@
         <v>1</v>
       </c>
       <c r="M594" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N594" s="3" t="s">
         <v>187</v>
@@ -30128,7 +30128,7 @@
         <v>1</v>
       </c>
       <c r="M595" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N595" s="3" t="s">
         <v>383</v>
@@ -30172,7 +30172,7 @@
         <v>1</v>
       </c>
       <c r="M596" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N596" s="3" t="s">
         <v>337</v>
@@ -30392,7 +30392,7 @@
         <v>1</v>
       </c>
       <c r="M601" s="22">
-        <v>201200104</v>
+        <v>20120104</v>
       </c>
       <c r="N601" s="3" t="s">
         <v>386</v>
@@ -30436,7 +30436,7 @@
         <v>1</v>
       </c>
       <c r="M602" s="22">
-        <v>201200118</v>
+        <v>20120118</v>
       </c>
       <c r="N602" s="3" t="s">
         <v>377</v>
@@ -30480,7 +30480,7 @@
         <v>1</v>
       </c>
       <c r="M603" s="22">
-        <v>201200120</v>
+        <v>20120120</v>
       </c>
       <c r="N603" s="3" t="s">
         <v>387</v>
@@ -30524,7 +30524,7 @@
         <v>1</v>
       </c>
       <c r="M604" s="22">
-        <v>201200137</v>
+        <v>20120137</v>
       </c>
       <c r="N604" s="3" t="s">
         <v>378</v>
@@ -30568,7 +30568,7 @@
         <v>1</v>
       </c>
       <c r="M605" s="22">
-        <v>201200138</v>
+        <v>20120138</v>
       </c>
       <c r="N605" s="3" t="s">
         <v>388</v>
@@ -30612,7 +30612,7 @@
         <v>1</v>
       </c>
       <c r="M606" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N606" s="3" t="s">
         <v>345</v>
@@ -30656,7 +30656,7 @@
         <v>1</v>
       </c>
       <c r="M607" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N607" s="3" t="s">
         <v>335</v>
@@ -30700,7 +30700,7 @@
         <v>1</v>
       </c>
       <c r="M608" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N608" s="3" t="s">
         <v>187</v>
@@ -30744,7 +30744,7 @@
         <v>1</v>
       </c>
       <c r="M609" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N609" s="3" t="s">
         <v>383</v>
@@ -30788,7 +30788,7 @@
         <v>1</v>
       </c>
       <c r="M610" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N610" s="3" t="s">
         <v>347</v>
@@ -31052,7 +31052,7 @@
         <v>1</v>
       </c>
       <c r="M616" s="22">
-        <v>201200104</v>
+        <v>20120104</v>
       </c>
       <c r="N616" s="3" t="s">
         <v>386</v>
@@ -31096,7 +31096,7 @@
         <v>1</v>
       </c>
       <c r="M617" s="22">
-        <v>201200119</v>
+        <v>20120119</v>
       </c>
       <c r="N617" s="3" t="s">
         <v>381</v>
@@ -31140,7 +31140,7 @@
         <v>1</v>
       </c>
       <c r="M618" s="22">
-        <v>201200120</v>
+        <v>20120120</v>
       </c>
       <c r="N618" s="3" t="s">
         <v>387</v>
@@ -31184,7 +31184,7 @@
         <v>1</v>
       </c>
       <c r="M619" s="22">
-        <v>201200118</v>
+        <v>20120118</v>
       </c>
       <c r="N619" s="3" t="s">
         <v>377</v>
@@ -31228,7 +31228,7 @@
         <v>1</v>
       </c>
       <c r="M620" s="22">
-        <v>201200121</v>
+        <v>20120121</v>
       </c>
       <c r="N620" s="3" t="s">
         <v>391</v>
@@ -31272,7 +31272,7 @@
         <v>1</v>
       </c>
       <c r="M621" s="22">
-        <v>201200137</v>
+        <v>20120137</v>
       </c>
       <c r="N621" s="3" t="s">
         <v>378</v>
@@ -31316,7 +31316,7 @@
         <v>1</v>
       </c>
       <c r="M622" s="22">
-        <v>201200138</v>
+        <v>20120138</v>
       </c>
       <c r="N622" s="3" t="s">
         <v>388</v>
@@ -31360,7 +31360,7 @@
         <v>1</v>
       </c>
       <c r="M623" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N623" s="3" t="s">
         <v>334</v>
@@ -31404,7 +31404,7 @@
         <v>1</v>
       </c>
       <c r="M624" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N624" s="3" t="s">
         <v>346</v>
@@ -31448,7 +31448,7 @@
         <v>1</v>
       </c>
       <c r="M625" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N625" s="3" t="s">
         <v>187</v>
@@ -31492,7 +31492,7 @@
         <v>1</v>
       </c>
       <c r="M626" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N626" s="3" t="s">
         <v>383</v>
@@ -31536,7 +31536,7 @@
         <v>1</v>
       </c>
       <c r="M627" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N627" s="3" t="s">
         <v>353</v>
@@ -31756,7 +31756,7 @@
         <v>1</v>
       </c>
       <c r="M632" s="22">
-        <v>201200104</v>
+        <v>20120104</v>
       </c>
       <c r="N632" s="3" t="s">
         <v>386</v>
@@ -31800,7 +31800,7 @@
         <v>1</v>
       </c>
       <c r="M633" s="22">
-        <v>201200119</v>
+        <v>20120119</v>
       </c>
       <c r="N633" s="3" t="s">
         <v>381</v>
@@ -31844,7 +31844,7 @@
         <v>1</v>
       </c>
       <c r="M634" s="22">
-        <v>201200121</v>
+        <v>20120121</v>
       </c>
       <c r="N634" s="3" t="s">
         <v>391</v>
@@ -31888,7 +31888,7 @@
         <v>1</v>
       </c>
       <c r="M635" s="22">
-        <v>201200137</v>
+        <v>20120137</v>
       </c>
       <c r="N635" s="3" t="s">
         <v>378</v>
@@ -31932,7 +31932,7 @@
         <v>1</v>
       </c>
       <c r="M636" s="22">
-        <v>201200138</v>
+        <v>20120138</v>
       </c>
       <c r="N636" s="3" t="s">
         <v>388</v>
@@ -31976,7 +31976,7 @@
         <v>1</v>
       </c>
       <c r="M637" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N637" s="3" t="s">
         <v>345</v>
@@ -32020,7 +32020,7 @@
         <v>1</v>
       </c>
       <c r="M638" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N638" s="3" t="s">
         <v>335</v>
@@ -32064,7 +32064,7 @@
         <v>1</v>
       </c>
       <c r="M639" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N639" s="3" t="s">
         <v>187</v>
@@ -32108,7 +32108,7 @@
         <v>1</v>
       </c>
       <c r="M640" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N640" s="3" t="s">
         <v>383</v>
@@ -32152,7 +32152,7 @@
         <v>1</v>
       </c>
       <c r="M641" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N641" s="3" t="s">
         <v>337</v>
@@ -32372,7 +32372,7 @@
         <v>1</v>
       </c>
       <c r="M646" s="22">
-        <v>201200105</v>
+        <v>20120105</v>
       </c>
       <c r="N646" s="3" t="s">
         <v>395</v>
@@ -32416,7 +32416,7 @@
         <v>1</v>
       </c>
       <c r="M647" s="22">
-        <v>201200120</v>
+        <v>20120120</v>
       </c>
       <c r="N647" s="3" t="s">
         <v>387</v>
@@ -32460,7 +32460,7 @@
         <v>1</v>
       </c>
       <c r="M648" s="22">
-        <v>201200122</v>
+        <v>20120122</v>
       </c>
       <c r="N648" s="3" t="s">
         <v>396</v>
@@ -32504,7 +32504,7 @@
         <v>1</v>
       </c>
       <c r="M649" s="22">
-        <v>201200138</v>
+        <v>20120138</v>
       </c>
       <c r="N649" s="3" t="s">
         <v>388</v>
@@ -32548,7 +32548,7 @@
         <v>1</v>
       </c>
       <c r="M650" s="22">
-        <v>201200139</v>
+        <v>20120139</v>
       </c>
       <c r="N650" s="3" t="s">
         <v>397</v>
@@ -32592,7 +32592,7 @@
         <v>1</v>
       </c>
       <c r="M651" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N651" s="3" t="s">
         <v>334</v>
@@ -32636,7 +32636,7 @@
         <v>1</v>
       </c>
       <c r="M652" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N652" s="3" t="s">
         <v>346</v>
@@ -32680,7 +32680,7 @@
         <v>1</v>
       </c>
       <c r="M653" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N653" s="3" t="s">
         <v>187</v>
@@ -32724,7 +32724,7 @@
         <v>1</v>
       </c>
       <c r="M654" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N654" s="3" t="s">
         <v>383</v>
@@ -32768,7 +32768,7 @@
         <v>1</v>
       </c>
       <c r="M655" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N655" s="3" t="s">
         <v>347</v>
@@ -33032,7 +33032,7 @@
         <v>1</v>
       </c>
       <c r="M661" s="22">
-        <v>201200105</v>
+        <v>20120105</v>
       </c>
       <c r="N661" s="3" t="s">
         <v>395</v>
@@ -33076,7 +33076,7 @@
         <v>1</v>
       </c>
       <c r="M662" s="22">
-        <v>201200120</v>
+        <v>20120120</v>
       </c>
       <c r="N662" s="3" t="s">
         <v>387</v>
@@ -33120,7 +33120,7 @@
         <v>1</v>
       </c>
       <c r="M663" s="22">
-        <v>201200121</v>
+        <v>20120121</v>
       </c>
       <c r="N663" s="3" t="s">
         <v>391</v>
@@ -33164,7 +33164,7 @@
         <v>1</v>
       </c>
       <c r="M664" s="22">
-        <v>201200122</v>
+        <v>20120122</v>
       </c>
       <c r="N664" s="3" t="s">
         <v>396</v>
@@ -33208,7 +33208,7 @@
         <v>1</v>
       </c>
       <c r="M665" s="22">
-        <v>201200123</v>
+        <v>20120123</v>
       </c>
       <c r="N665" s="3" t="s">
         <v>400</v>
@@ -33252,7 +33252,7 @@
         <v>1</v>
       </c>
       <c r="M666" s="22">
-        <v>201200138</v>
+        <v>20120138</v>
       </c>
       <c r="N666" s="3" t="s">
         <v>388</v>
@@ -33296,7 +33296,7 @@
         <v>1</v>
       </c>
       <c r="M667" s="22">
-        <v>201200139</v>
+        <v>20120139</v>
       </c>
       <c r="N667" s="3" t="s">
         <v>397</v>
@@ -33340,7 +33340,7 @@
         <v>1</v>
       </c>
       <c r="M668" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N668" s="3" t="s">
         <v>345</v>
@@ -33384,7 +33384,7 @@
         <v>1</v>
       </c>
       <c r="M669" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N669" s="3" t="s">
         <v>335</v>
@@ -33428,7 +33428,7 @@
         <v>1</v>
       </c>
       <c r="M670" s="22">
-        <v>201200150</v>
+        <v>20120150</v>
       </c>
       <c r="N670" s="3" t="s">
         <v>187</v>
@@ -33472,7 +33472,7 @@
         <v>1</v>
       </c>
       <c r="M671" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N671" s="3" t="s">
         <v>383</v>
@@ -33516,7 +33516,7 @@
         <v>1</v>
       </c>
       <c r="M672" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N672" s="3" t="s">
         <v>353</v>
@@ -33736,7 +33736,7 @@
         <v>1</v>
       </c>
       <c r="M677" s="22">
-        <v>201200105</v>
+        <v>20120105</v>
       </c>
       <c r="N677" s="3" t="s">
         <v>395</v>
@@ -33780,7 +33780,7 @@
         <v>1</v>
       </c>
       <c r="M678" s="22">
-        <v>201200121</v>
+        <v>20120121</v>
       </c>
       <c r="N678" s="3" t="s">
         <v>391</v>
@@ -33824,7 +33824,7 @@
         <v>1</v>
       </c>
       <c r="M679" s="22">
-        <v>201200123</v>
+        <v>20120123</v>
       </c>
       <c r="N679" s="3" t="s">
         <v>400</v>
@@ -33868,7 +33868,7 @@
         <v>1</v>
       </c>
       <c r="M680" s="22">
-        <v>201200138</v>
+        <v>20120138</v>
       </c>
       <c r="N680" s="3" t="s">
         <v>388</v>
@@ -33912,7 +33912,7 @@
         <v>1</v>
       </c>
       <c r="M681" s="22">
-        <v>201200139</v>
+        <v>20120139</v>
       </c>
       <c r="N681" s="3" t="s">
         <v>397</v>
@@ -33956,7 +33956,7 @@
         <v>1</v>
       </c>
       <c r="M682" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N682" s="3" t="s">
         <v>334</v>
@@ -34000,7 +34000,7 @@
         <v>1</v>
       </c>
       <c r="M683" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N683" s="3" t="s">
         <v>335</v>
@@ -34044,7 +34044,7 @@
         <v>1</v>
       </c>
       <c r="M684" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N684" s="3" t="s">
         <v>210</v>
@@ -34088,7 +34088,7 @@
         <v>1</v>
       </c>
       <c r="M685" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N685" s="3" t="s">
         <v>383</v>
@@ -34132,7 +34132,7 @@
         <v>1</v>
       </c>
       <c r="M686" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N686" s="3" t="s">
         <v>337</v>
@@ -34352,7 +34352,7 @@
         <v>1</v>
       </c>
       <c r="M691" s="22">
-        <v>201200106</v>
+        <v>20120106</v>
       </c>
       <c r="N691" s="3" t="s">
         <v>404</v>
@@ -34396,7 +34396,7 @@
         <v>1</v>
       </c>
       <c r="M692" s="22">
-        <v>201200122</v>
+        <v>20120122</v>
       </c>
       <c r="N692" s="3" t="s">
         <v>396</v>
@@ -34440,7 +34440,7 @@
         <v>1</v>
       </c>
       <c r="M693" s="22">
-        <v>201200124</v>
+        <v>20120124</v>
       </c>
       <c r="N693" s="3" t="s">
         <v>405</v>
@@ -34484,7 +34484,7 @@
         <v>1</v>
       </c>
       <c r="M694" s="22">
-        <v>201200139</v>
+        <v>20120139</v>
       </c>
       <c r="N694" s="3" t="s">
         <v>397</v>
@@ -34528,7 +34528,7 @@
         <v>1</v>
       </c>
       <c r="M695" s="22">
-        <v>201200140</v>
+        <v>20120140</v>
       </c>
       <c r="N695" s="3" t="s">
         <v>406</v>
@@ -34572,7 +34572,7 @@
         <v>1</v>
       </c>
       <c r="M696" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N696" s="3" t="s">
         <v>345</v>
@@ -34616,7 +34616,7 @@
         <v>1</v>
       </c>
       <c r="M697" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N697" s="3" t="s">
         <v>346</v>
@@ -34660,7 +34660,7 @@
         <v>1</v>
       </c>
       <c r="M698" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N698" s="3" t="s">
         <v>210</v>
@@ -34704,7 +34704,7 @@
         <v>1</v>
       </c>
       <c r="M699" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N699" s="3" t="s">
         <v>383</v>
@@ -34748,7 +34748,7 @@
         <v>1</v>
       </c>
       <c r="M700" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N700" s="3" t="s">
         <v>347</v>
@@ -35012,7 +35012,7 @@
         <v>1</v>
       </c>
       <c r="M706" s="22">
-        <v>201200106</v>
+        <v>20120106</v>
       </c>
       <c r="N706" s="3" t="s">
         <v>404</v>
@@ -35056,7 +35056,7 @@
         <v>1</v>
       </c>
       <c r="M707" s="22">
-        <v>201200122</v>
+        <v>20120122</v>
       </c>
       <c r="N707" s="3" t="s">
         <v>396</v>
@@ -35100,7 +35100,7 @@
         <v>1</v>
       </c>
       <c r="M708" s="22">
-        <v>201200123</v>
+        <v>20120123</v>
       </c>
       <c r="N708" s="3" t="s">
         <v>400</v>
@@ -35144,7 +35144,7 @@
         <v>1</v>
       </c>
       <c r="M709" s="22">
-        <v>201200124</v>
+        <v>20120124</v>
       </c>
       <c r="N709" s="3" t="s">
         <v>405</v>
@@ -35188,7 +35188,7 @@
         <v>1</v>
       </c>
       <c r="M710" s="22">
-        <v>201200125</v>
+        <v>20120125</v>
       </c>
       <c r="N710" s="3" t="s">
         <v>409</v>
@@ -35232,7 +35232,7 @@
         <v>1</v>
       </c>
       <c r="M711" s="22">
-        <v>201200139</v>
+        <v>20120139</v>
       </c>
       <c r="N711" s="3" t="s">
         <v>397</v>
@@ -35276,7 +35276,7 @@
         <v>1</v>
       </c>
       <c r="M712" s="22">
-        <v>201200140</v>
+        <v>20120140</v>
       </c>
       <c r="N712" s="3" t="s">
         <v>406</v>
@@ -35320,7 +35320,7 @@
         <v>1</v>
       </c>
       <c r="M713" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N713" s="3" t="s">
         <v>334</v>
@@ -35364,7 +35364,7 @@
         <v>1</v>
       </c>
       <c r="M714" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N714" s="3" t="s">
         <v>335</v>
@@ -35408,7 +35408,7 @@
         <v>1</v>
       </c>
       <c r="M715" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N715" s="3" t="s">
         <v>210</v>
@@ -35452,7 +35452,7 @@
         <v>1</v>
       </c>
       <c r="M716" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N716" s="3" t="s">
         <v>383</v>
@@ -35496,7 +35496,7 @@
         <v>1</v>
       </c>
       <c r="M717" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N717" s="3" t="s">
         <v>353</v>
@@ -35716,7 +35716,7 @@
         <v>1</v>
       </c>
       <c r="M722" s="22">
-        <v>201200106</v>
+        <v>20120106</v>
       </c>
       <c r="N722" s="3" t="s">
         <v>404</v>
@@ -35760,7 +35760,7 @@
         <v>1</v>
       </c>
       <c r="M723" s="22">
-        <v>201200123</v>
+        <v>20120123</v>
       </c>
       <c r="N723" s="3" t="s">
         <v>400</v>
@@ -35804,7 +35804,7 @@
         <v>1</v>
       </c>
       <c r="M724" s="22">
-        <v>201200125</v>
+        <v>20120125</v>
       </c>
       <c r="N724" s="3" t="s">
         <v>409</v>
@@ -35848,7 +35848,7 @@
         <v>1</v>
       </c>
       <c r="M725" s="22">
-        <v>201200139</v>
+        <v>20120139</v>
       </c>
       <c r="N725" s="3" t="s">
         <v>397</v>
@@ -35892,7 +35892,7 @@
         <v>1</v>
       </c>
       <c r="M726" s="22">
-        <v>201200140</v>
+        <v>20120140</v>
       </c>
       <c r="N726" s="3" t="s">
         <v>406</v>
@@ -35936,7 +35936,7 @@
         <v>1</v>
       </c>
       <c r="M727" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N727" s="3" t="s">
         <v>345</v>
@@ -35980,7 +35980,7 @@
         <v>1</v>
       </c>
       <c r="M728" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N728" s="3" t="s">
         <v>346</v>
@@ -36024,7 +36024,7 @@
         <v>1</v>
       </c>
       <c r="M729" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N729" s="3" t="s">
         <v>210</v>
@@ -36068,7 +36068,7 @@
         <v>1</v>
       </c>
       <c r="M730" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N730" s="3" t="s">
         <v>383</v>
@@ -36112,7 +36112,7 @@
         <v>1</v>
       </c>
       <c r="M731" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N731" s="3" t="s">
         <v>337</v>
@@ -36332,7 +36332,7 @@
         <v>1</v>
       </c>
       <c r="M736" s="22">
-        <v>201200107</v>
+        <v>20120107</v>
       </c>
       <c r="N736" s="3" t="s">
         <v>413</v>
@@ -36376,7 +36376,7 @@
         <v>1</v>
       </c>
       <c r="M737" s="22">
-        <v>201200124</v>
+        <v>20120124</v>
       </c>
       <c r="N737" s="3" t="s">
         <v>405</v>
@@ -36420,7 +36420,7 @@
         <v>1</v>
       </c>
       <c r="M738" s="22">
-        <v>201200126</v>
+        <v>20120126</v>
       </c>
       <c r="N738" s="3" t="s">
         <v>414</v>
@@ -36464,7 +36464,7 @@
         <v>1</v>
       </c>
       <c r="M739" s="22">
-        <v>201200140</v>
+        <v>20120140</v>
       </c>
       <c r="N739" s="3" t="s">
         <v>406</v>
@@ -36508,7 +36508,7 @@
         <v>1</v>
       </c>
       <c r="M740" s="22">
-        <v>201200141</v>
+        <v>20120141</v>
       </c>
       <c r="N740" s="3" t="s">
         <v>415</v>
@@ -36552,7 +36552,7 @@
         <v>1</v>
       </c>
       <c r="M741" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N741" s="3" t="s">
         <v>334</v>
@@ -36596,7 +36596,7 @@
         <v>1</v>
       </c>
       <c r="M742" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N742" s="3" t="s">
         <v>335</v>
@@ -36640,7 +36640,7 @@
         <v>1</v>
       </c>
       <c r="M743" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N743" s="3" t="s">
         <v>210</v>
@@ -36684,7 +36684,7 @@
         <v>1</v>
       </c>
       <c r="M744" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N744" s="3" t="s">
         <v>383</v>
@@ -36728,7 +36728,7 @@
         <v>1</v>
       </c>
       <c r="M745" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N745" s="3" t="s">
         <v>347</v>
@@ -36992,7 +36992,7 @@
         <v>1</v>
       </c>
       <c r="M751" s="22">
-        <v>201200107</v>
+        <v>20120107</v>
       </c>
       <c r="N751" s="3" t="s">
         <v>413</v>
@@ -37036,7 +37036,7 @@
         <v>1</v>
       </c>
       <c r="M752" s="22">
-        <v>201200124</v>
+        <v>20120124</v>
       </c>
       <c r="N752" s="3" t="s">
         <v>405</v>
@@ -37080,7 +37080,7 @@
         <v>1</v>
       </c>
       <c r="M753" s="22">
-        <v>201200125</v>
+        <v>20120125</v>
       </c>
       <c r="N753" s="3" t="s">
         <v>409</v>
@@ -37124,7 +37124,7 @@
         <v>1</v>
       </c>
       <c r="M754" s="22">
-        <v>201200126</v>
+        <v>20120126</v>
       </c>
       <c r="N754" s="3" t="s">
         <v>414</v>
@@ -37168,7 +37168,7 @@
         <v>1</v>
       </c>
       <c r="M755" s="22">
-        <v>201200127</v>
+        <v>20120127</v>
       </c>
       <c r="N755" s="3" t="s">
         <v>418</v>
@@ -37212,7 +37212,7 @@
         <v>1</v>
       </c>
       <c r="M756" s="22">
-        <v>201200140</v>
+        <v>20120140</v>
       </c>
       <c r="N756" s="3" t="s">
         <v>406</v>
@@ -37256,7 +37256,7 @@
         <v>1</v>
       </c>
       <c r="M757" s="22">
-        <v>201200141</v>
+        <v>20120141</v>
       </c>
       <c r="N757" s="3" t="s">
         <v>415</v>
@@ -37300,7 +37300,7 @@
         <v>1</v>
       </c>
       <c r="M758" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N758" s="3" t="s">
         <v>345</v>
@@ -37344,7 +37344,7 @@
         <v>1</v>
       </c>
       <c r="M759" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N759" s="3" t="s">
         <v>346</v>
@@ -37388,7 +37388,7 @@
         <v>1</v>
       </c>
       <c r="M760" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N760" s="3" t="s">
         <v>210</v>
@@ -37432,7 +37432,7 @@
         <v>1</v>
       </c>
       <c r="M761" s="22">
-        <v>201200152</v>
+        <v>20120152</v>
       </c>
       <c r="N761" s="3" t="s">
         <v>383</v>
@@ -37476,7 +37476,7 @@
         <v>1</v>
       </c>
       <c r="M762" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N762" s="3" t="s">
         <v>353</v>
@@ -37696,7 +37696,7 @@
         <v>1</v>
       </c>
       <c r="M767" s="22">
-        <v>201200107</v>
+        <v>20120107</v>
       </c>
       <c r="N767" s="3" t="s">
         <v>413</v>
@@ -37740,7 +37740,7 @@
         <v>1</v>
       </c>
       <c r="M768" s="22">
-        <v>201200125</v>
+        <v>20120125</v>
       </c>
       <c r="N768" s="3" t="s">
         <v>409</v>
@@ -37784,7 +37784,7 @@
         <v>1</v>
       </c>
       <c r="M769" s="22">
-        <v>201200127</v>
+        <v>20120127</v>
       </c>
       <c r="N769" s="3" t="s">
         <v>418</v>
@@ -37828,7 +37828,7 @@
         <v>1</v>
       </c>
       <c r="M770" s="22">
-        <v>201200140</v>
+        <v>20120140</v>
       </c>
       <c r="N770" s="3" t="s">
         <v>406</v>
@@ -37872,7 +37872,7 @@
         <v>1</v>
       </c>
       <c r="M771" s="22">
-        <v>201200141</v>
+        <v>20120141</v>
       </c>
       <c r="N771" s="3" t="s">
         <v>415</v>
@@ -37916,7 +37916,7 @@
         <v>1</v>
       </c>
       <c r="M772" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N772" s="3" t="s">
         <v>334</v>
@@ -37960,7 +37960,7 @@
         <v>1</v>
       </c>
       <c r="M773" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N773" s="3" t="s">
         <v>335</v>
@@ -38004,7 +38004,7 @@
         <v>1</v>
       </c>
       <c r="M774" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N774" s="3" t="s">
         <v>210</v>
@@ -38048,7 +38048,7 @@
         <v>1</v>
       </c>
       <c r="M775" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N775" s="3" t="s">
         <v>420</v>
@@ -38092,7 +38092,7 @@
         <v>1</v>
       </c>
       <c r="M776" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N776" s="3" t="s">
         <v>337</v>
@@ -38312,7 +38312,7 @@
         <v>1</v>
       </c>
       <c r="M781" s="22">
-        <v>201200108</v>
+        <v>20120108</v>
       </c>
       <c r="N781" s="3" t="s">
         <v>423</v>
@@ -38356,7 +38356,7 @@
         <v>1</v>
       </c>
       <c r="M782" s="22">
-        <v>201200126</v>
+        <v>20120126</v>
       </c>
       <c r="N782" s="3" t="s">
         <v>414</v>
@@ -38400,7 +38400,7 @@
         <v>1</v>
       </c>
       <c r="M783" s="22">
-        <v>201200128</v>
+        <v>20120128</v>
       </c>
       <c r="N783" s="3" t="s">
         <v>424</v>
@@ -38444,7 +38444,7 @@
         <v>1</v>
       </c>
       <c r="M784" s="22">
-        <v>201200141</v>
+        <v>20120141</v>
       </c>
       <c r="N784" s="3" t="s">
         <v>415</v>
@@ -38488,7 +38488,7 @@
         <v>1</v>
       </c>
       <c r="M785" s="22">
-        <v>201200142</v>
+        <v>20120142</v>
       </c>
       <c r="N785" s="3" t="s">
         <v>425</v>
@@ -38532,7 +38532,7 @@
         <v>1</v>
       </c>
       <c r="M786" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N786" s="3" t="s">
         <v>345</v>
@@ -38576,7 +38576,7 @@
         <v>1</v>
       </c>
       <c r="M787" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N787" s="3" t="s">
         <v>346</v>
@@ -38620,7 +38620,7 @@
         <v>1</v>
       </c>
       <c r="M788" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N788" s="3" t="s">
         <v>210</v>
@@ -38664,7 +38664,7 @@
         <v>1</v>
       </c>
       <c r="M789" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N789" s="3" t="s">
         <v>420</v>
@@ -38708,7 +38708,7 @@
         <v>1</v>
       </c>
       <c r="M790" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N790" s="3" t="s">
         <v>347</v>
@@ -38972,7 +38972,7 @@
         <v>1</v>
       </c>
       <c r="M796" s="22">
-        <v>201200108</v>
+        <v>20120108</v>
       </c>
       <c r="N796" s="3" t="s">
         <v>423</v>
@@ -39016,7 +39016,7 @@
         <v>1</v>
       </c>
       <c r="M797" s="22">
-        <v>201200126</v>
+        <v>20120126</v>
       </c>
       <c r="N797" s="3" t="s">
         <v>414</v>
@@ -39060,7 +39060,7 @@
         <v>1</v>
       </c>
       <c r="M798" s="22">
-        <v>201200127</v>
+        <v>20120127</v>
       </c>
       <c r="N798" s="3" t="s">
         <v>418</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="M799" s="22">
-        <v>201200128</v>
+        <v>20120128</v>
       </c>
       <c r="N799" s="3" t="s">
         <v>424</v>
@@ -39148,7 +39148,7 @@
         <v>1</v>
       </c>
       <c r="M800" s="22">
-        <v>201200129</v>
+        <v>20120129</v>
       </c>
       <c r="N800" s="3" t="s">
         <v>428</v>
@@ -39192,7 +39192,7 @@
         <v>1</v>
       </c>
       <c r="M801" s="22">
-        <v>201200141</v>
+        <v>20120141</v>
       </c>
       <c r="N801" s="3" t="s">
         <v>415</v>
@@ -39236,7 +39236,7 @@
         <v>1</v>
       </c>
       <c r="M802" s="22">
-        <v>201200142</v>
+        <v>20120142</v>
       </c>
       <c r="N802" s="3" t="s">
         <v>425</v>
@@ -39280,7 +39280,7 @@
         <v>1</v>
       </c>
       <c r="M803" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N803" s="3" t="s">
         <v>334</v>
@@ -39324,7 +39324,7 @@
         <v>1</v>
       </c>
       <c r="M804" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N804" s="3" t="s">
         <v>335</v>
@@ -39368,7 +39368,7 @@
         <v>1</v>
       </c>
       <c r="M805" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N805" s="3" t="s">
         <v>210</v>
@@ -39412,7 +39412,7 @@
         <v>1</v>
       </c>
       <c r="M806" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N806" s="3" t="s">
         <v>420</v>
@@ -39456,7 +39456,7 @@
         <v>1</v>
       </c>
       <c r="M807" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N807" s="3" t="s">
         <v>353</v>
@@ -39676,7 +39676,7 @@
         <v>1</v>
       </c>
       <c r="M812" s="22">
-        <v>201200108</v>
+        <v>20120108</v>
       </c>
       <c r="N812" s="3" t="s">
         <v>423</v>
@@ -39720,7 +39720,7 @@
         <v>1</v>
       </c>
       <c r="M813" s="22">
-        <v>201200127</v>
+        <v>20120127</v>
       </c>
       <c r="N813" s="3" t="s">
         <v>418</v>
@@ -39764,7 +39764,7 @@
         <v>1</v>
       </c>
       <c r="M814" s="22">
-        <v>201200129</v>
+        <v>20120129</v>
       </c>
       <c r="N814" s="3" t="s">
         <v>428</v>
@@ -39808,7 +39808,7 @@
         <v>1</v>
       </c>
       <c r="M815" s="22">
-        <v>201200141</v>
+        <v>20120141</v>
       </c>
       <c r="N815" s="3" t="s">
         <v>415</v>
@@ -39852,7 +39852,7 @@
         <v>1</v>
       </c>
       <c r="M816" s="22">
-        <v>201200142</v>
+        <v>20120142</v>
       </c>
       <c r="N816" s="3" t="s">
         <v>425</v>
@@ -39896,7 +39896,7 @@
         <v>1</v>
       </c>
       <c r="M817" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N817" s="3" t="s">
         <v>345</v>
@@ -39940,7 +39940,7 @@
         <v>1</v>
       </c>
       <c r="M818" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N818" s="3" t="s">
         <v>346</v>
@@ -39984,7 +39984,7 @@
         <v>1</v>
       </c>
       <c r="M819" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N819" s="3" t="s">
         <v>210</v>
@@ -40028,7 +40028,7 @@
         <v>1</v>
       </c>
       <c r="M820" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N820" s="3" t="s">
         <v>420</v>
@@ -40072,7 +40072,7 @@
         <v>1</v>
       </c>
       <c r="M821" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N821" s="3" t="s">
         <v>337</v>
@@ -40292,7 +40292,7 @@
         <v>1</v>
       </c>
       <c r="M826" s="22">
-        <v>201200109</v>
+        <v>20120109</v>
       </c>
       <c r="N826" s="3" t="s">
         <v>432</v>
@@ -40336,7 +40336,7 @@
         <v>1</v>
       </c>
       <c r="M827" s="22">
-        <v>201200128</v>
+        <v>20120128</v>
       </c>
       <c r="N827" s="3" t="s">
         <v>424</v>
@@ -40380,7 +40380,7 @@
         <v>1</v>
       </c>
       <c r="M828" s="22">
-        <v>201200130</v>
+        <v>20120130</v>
       </c>
       <c r="N828" s="3" t="s">
         <v>433</v>
@@ -40424,7 +40424,7 @@
         <v>1</v>
       </c>
       <c r="M829" s="22">
-        <v>201200142</v>
+        <v>20120142</v>
       </c>
       <c r="N829" s="3" t="s">
         <v>425</v>
@@ -40468,7 +40468,7 @@
         <v>1</v>
       </c>
       <c r="M830" s="22">
-        <v>201200143</v>
+        <v>20120143</v>
       </c>
       <c r="N830" s="3" t="s">
         <v>434</v>
@@ -40512,7 +40512,7 @@
         <v>1</v>
       </c>
       <c r="M831" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N831" s="3" t="s">
         <v>334</v>
@@ -40556,7 +40556,7 @@
         <v>1</v>
       </c>
       <c r="M832" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N832" s="3" t="s">
         <v>346</v>
@@ -40600,7 +40600,7 @@
         <v>1</v>
       </c>
       <c r="M833" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N833" s="3" t="s">
         <v>210</v>
@@ -40644,7 +40644,7 @@
         <v>1</v>
       </c>
       <c r="M834" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N834" s="3" t="s">
         <v>420</v>
@@ -40688,7 +40688,7 @@
         <v>1</v>
       </c>
       <c r="M835" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N835" s="3" t="s">
         <v>347</v>
@@ -40952,7 +40952,7 @@
         <v>1</v>
       </c>
       <c r="M841" s="22">
-        <v>201200109</v>
+        <v>20120109</v>
       </c>
       <c r="N841" s="3" t="s">
         <v>432</v>
@@ -40996,7 +40996,7 @@
         <v>1</v>
       </c>
       <c r="M842" s="22">
-        <v>201200128</v>
+        <v>20120128</v>
       </c>
       <c r="N842" s="3" t="s">
         <v>424</v>
@@ -41040,7 +41040,7 @@
         <v>1</v>
       </c>
       <c r="M843" s="22">
-        <v>201200129</v>
+        <v>20120129</v>
       </c>
       <c r="N843" s="3" t="s">
         <v>428</v>
@@ -41084,7 +41084,7 @@
         <v>1</v>
       </c>
       <c r="M844" s="22">
-        <v>201200130</v>
+        <v>20120130</v>
       </c>
       <c r="N844" s="3" t="s">
         <v>433</v>
@@ -41128,7 +41128,7 @@
         <v>1</v>
       </c>
       <c r="M845" s="22">
-        <v>201200131</v>
+        <v>20120131</v>
       </c>
       <c r="N845" s="3" t="s">
         <v>437</v>
@@ -41172,7 +41172,7 @@
         <v>1</v>
       </c>
       <c r="M846" s="22">
-        <v>201200142</v>
+        <v>20120142</v>
       </c>
       <c r="N846" s="3" t="s">
         <v>425</v>
@@ -41216,7 +41216,7 @@
         <v>1</v>
       </c>
       <c r="M847" s="22">
-        <v>201200143</v>
+        <v>20120143</v>
       </c>
       <c r="N847" s="3" t="s">
         <v>434</v>
@@ -41260,7 +41260,7 @@
         <v>1</v>
       </c>
       <c r="M848" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N848" s="3" t="s">
         <v>345</v>
@@ -41304,7 +41304,7 @@
         <v>1</v>
       </c>
       <c r="M849" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N849" s="3" t="s">
         <v>335</v>
@@ -41348,7 +41348,7 @@
         <v>1</v>
       </c>
       <c r="M850" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N850" s="3" t="s">
         <v>210</v>
@@ -41392,7 +41392,7 @@
         <v>1</v>
       </c>
       <c r="M851" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N851" s="3" t="s">
         <v>420</v>
@@ -41436,7 +41436,7 @@
         <v>1</v>
       </c>
       <c r="M852" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N852" s="3" t="s">
         <v>353</v>
@@ -41656,7 +41656,7 @@
         <v>1</v>
       </c>
       <c r="M857" s="22">
-        <v>201200109</v>
+        <v>20120109</v>
       </c>
       <c r="N857" s="3" t="s">
         <v>432</v>
@@ -41700,7 +41700,7 @@
         <v>1</v>
       </c>
       <c r="M858" s="22">
-        <v>201200129</v>
+        <v>20120129</v>
       </c>
       <c r="N858" s="3" t="s">
         <v>428</v>
@@ -41744,7 +41744,7 @@
         <v>1</v>
       </c>
       <c r="M859" s="22">
-        <v>201200131</v>
+        <v>20120131</v>
       </c>
       <c r="N859" s="3" t="s">
         <v>437</v>
@@ -41788,7 +41788,7 @@
         <v>1</v>
       </c>
       <c r="M860" s="22">
-        <v>201200142</v>
+        <v>20120142</v>
       </c>
       <c r="N860" s="3" t="s">
         <v>425</v>
@@ -41832,7 +41832,7 @@
         <v>1</v>
       </c>
       <c r="M861" s="22">
-        <v>201200143</v>
+        <v>20120143</v>
       </c>
       <c r="N861" s="3" t="s">
         <v>434</v>
@@ -41876,7 +41876,7 @@
         <v>1</v>
       </c>
       <c r="M862" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N862" s="3" t="s">
         <v>334</v>
@@ -41920,7 +41920,7 @@
         <v>1</v>
       </c>
       <c r="M863" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N863" s="3" t="s">
         <v>346</v>
@@ -41964,7 +41964,7 @@
         <v>1</v>
       </c>
       <c r="M864" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N864" s="3" t="s">
         <v>210</v>
@@ -42008,7 +42008,7 @@
         <v>1</v>
       </c>
       <c r="M865" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N865" s="3" t="s">
         <v>420</v>
@@ -42052,7 +42052,7 @@
         <v>1</v>
       </c>
       <c r="M866" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N866" s="3" t="s">
         <v>337</v>
@@ -42272,7 +42272,7 @@
         <v>1</v>
       </c>
       <c r="M871" s="22">
-        <v>201200110</v>
+        <v>20120110</v>
       </c>
       <c r="N871" s="3" t="s">
         <v>441</v>
@@ -42316,7 +42316,7 @@
         <v>1</v>
       </c>
       <c r="M872" s="22">
-        <v>201200130</v>
+        <v>20120130</v>
       </c>
       <c r="N872" s="3" t="s">
         <v>433</v>
@@ -42360,7 +42360,7 @@
         <v>1</v>
       </c>
       <c r="M873" s="22">
-        <v>201200132</v>
+        <v>20120132</v>
       </c>
       <c r="N873" s="3" t="s">
         <v>442</v>
@@ -42404,7 +42404,7 @@
         <v>1</v>
       </c>
       <c r="M874" s="22">
-        <v>201200143</v>
+        <v>20120143</v>
       </c>
       <c r="N874" s="3" t="s">
         <v>434</v>
@@ -42448,7 +42448,7 @@
         <v>1</v>
       </c>
       <c r="M875" s="22">
-        <v>201200144</v>
+        <v>20120144</v>
       </c>
       <c r="N875" s="3" t="s">
         <v>443</v>
@@ -42492,7 +42492,7 @@
         <v>1</v>
       </c>
       <c r="M876" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N876" s="3" t="s">
         <v>345</v>
@@ -42536,7 +42536,7 @@
         <v>1</v>
       </c>
       <c r="M877" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N877" s="3" t="s">
         <v>335</v>
@@ -42580,7 +42580,7 @@
         <v>1</v>
       </c>
       <c r="M878" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N878" s="3" t="s">
         <v>210</v>
@@ -42624,7 +42624,7 @@
         <v>1</v>
       </c>
       <c r="M879" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N879" s="3" t="s">
         <v>420</v>
@@ -42668,7 +42668,7 @@
         <v>1</v>
       </c>
       <c r="M880" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N880" s="3" t="s">
         <v>347</v>
@@ -42932,7 +42932,7 @@
         <v>1</v>
       </c>
       <c r="M886" s="22">
-        <v>201200110</v>
+        <v>20120110</v>
       </c>
       <c r="N886" s="3" t="s">
         <v>441</v>
@@ -42976,7 +42976,7 @@
         <v>1</v>
       </c>
       <c r="M887" s="22">
-        <v>201200130</v>
+        <v>20120130</v>
       </c>
       <c r="N887" s="3" t="s">
         <v>433</v>
@@ -43020,7 +43020,7 @@
         <v>1</v>
       </c>
       <c r="M888" s="22">
-        <v>201200131</v>
+        <v>20120131</v>
       </c>
       <c r="N888" s="3" t="s">
         <v>437</v>
@@ -43064,7 +43064,7 @@
         <v>1</v>
       </c>
       <c r="M889" s="22">
-        <v>201200132</v>
+        <v>20120132</v>
       </c>
       <c r="N889" s="3" t="s">
         <v>442</v>
@@ -43108,7 +43108,7 @@
         <v>1</v>
       </c>
       <c r="M890" s="22">
-        <v>201200133</v>
+        <v>20120133</v>
       </c>
       <c r="N890" s="3" t="s">
         <v>446</v>
@@ -43152,7 +43152,7 @@
         <v>1</v>
       </c>
       <c r="M891" s="22">
-        <v>201200143</v>
+        <v>20120143</v>
       </c>
       <c r="N891" s="3" t="s">
         <v>434</v>
@@ -43196,7 +43196,7 @@
         <v>1</v>
       </c>
       <c r="M892" s="22">
-        <v>201200144</v>
+        <v>20120144</v>
       </c>
       <c r="N892" s="3" t="s">
         <v>443</v>
@@ -43240,7 +43240,7 @@
         <v>1</v>
       </c>
       <c r="M893" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N893" s="3" t="s">
         <v>334</v>
@@ -43284,7 +43284,7 @@
         <v>1</v>
       </c>
       <c r="M894" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N894" s="3" t="s">
         <v>346</v>
@@ -43328,7 +43328,7 @@
         <v>1</v>
       </c>
       <c r="M895" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N895" s="3" t="s">
         <v>210</v>
@@ -43372,7 +43372,7 @@
         <v>1</v>
       </c>
       <c r="M896" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N896" s="3" t="s">
         <v>420</v>
@@ -43416,7 +43416,7 @@
         <v>1</v>
       </c>
       <c r="M897" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N897" s="3" t="s">
         <v>353</v>
@@ -43636,7 +43636,7 @@
         <v>1</v>
       </c>
       <c r="M902" s="22">
-        <v>201200110</v>
+        <v>20120110</v>
       </c>
       <c r="N902" s="3" t="s">
         <v>441</v>
@@ -43680,7 +43680,7 @@
         <v>1</v>
       </c>
       <c r="M903" s="22">
-        <v>201200131</v>
+        <v>20120131</v>
       </c>
       <c r="N903" s="3" t="s">
         <v>437</v>
@@ -43724,7 +43724,7 @@
         <v>1</v>
       </c>
       <c r="M904" s="22">
-        <v>201200133</v>
+        <v>20120133</v>
       </c>
       <c r="N904" s="3" t="s">
         <v>446</v>
@@ -43768,7 +43768,7 @@
         <v>1</v>
       </c>
       <c r="M905" s="22">
-        <v>201200143</v>
+        <v>20120143</v>
       </c>
       <c r="N905" s="3" t="s">
         <v>434</v>
@@ -43812,7 +43812,7 @@
         <v>1</v>
       </c>
       <c r="M906" s="22">
-        <v>201200144</v>
+        <v>20120144</v>
       </c>
       <c r="N906" s="3" t="s">
         <v>443</v>
@@ -43856,7 +43856,7 @@
         <v>1</v>
       </c>
       <c r="M907" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N907" s="3" t="s">
         <v>345</v>
@@ -43900,7 +43900,7 @@
         <v>1</v>
       </c>
       <c r="M908" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N908" s="3" t="s">
         <v>335</v>
@@ -43944,7 +43944,7 @@
         <v>1</v>
       </c>
       <c r="M909" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N909" s="3" t="s">
         <v>210</v>
@@ -43988,7 +43988,7 @@
         <v>1</v>
       </c>
       <c r="M910" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N910" s="3" t="s">
         <v>420</v>
@@ -44032,7 +44032,7 @@
         <v>1</v>
       </c>
       <c r="M911" s="22">
-        <v>201200154</v>
+        <v>20120154</v>
       </c>
       <c r="N911" s="3" t="s">
         <v>337</v>
@@ -44208,7 +44208,7 @@
         <v>1</v>
       </c>
       <c r="M915" s="22">
-        <v>201200111</v>
+        <v>20120111</v>
       </c>
       <c r="N915" s="3" t="s">
         <v>449</v>
@@ -44252,7 +44252,7 @@
         <v>1</v>
       </c>
       <c r="M916" s="22">
-        <v>201200132</v>
+        <v>20120132</v>
       </c>
       <c r="N916" s="3" t="s">
         <v>442</v>
@@ -44296,7 +44296,7 @@
         <v>1</v>
       </c>
       <c r="M917" s="22">
-        <v>201200144</v>
+        <v>20120144</v>
       </c>
       <c r="N917" s="3" t="s">
         <v>443</v>
@@ -44340,7 +44340,7 @@
         <v>1</v>
       </c>
       <c r="M918" s="22">
-        <v>201200147</v>
+        <v>20120147</v>
       </c>
       <c r="N918" s="3" t="s">
         <v>334</v>
@@ -44384,7 +44384,7 @@
         <v>1</v>
       </c>
       <c r="M919" s="22">
-        <v>201200146</v>
+        <v>20120146</v>
       </c>
       <c r="N919" s="3" t="s">
         <v>346</v>
@@ -44428,7 +44428,7 @@
         <v>1</v>
       </c>
       <c r="M920" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N920" s="3" t="s">
         <v>210</v>
@@ -44472,7 +44472,7 @@
         <v>1</v>
       </c>
       <c r="M921" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N921" s="3" t="s">
         <v>420</v>
@@ -44516,7 +44516,7 @@
         <v>1</v>
       </c>
       <c r="M922" s="22">
-        <v>201200155</v>
+        <v>20120155</v>
       </c>
       <c r="N922" s="3" t="s">
         <v>347</v>
@@ -44736,7 +44736,7 @@
         <v>1</v>
       </c>
       <c r="M927" s="22">
-        <v>201200111</v>
+        <v>20120111</v>
       </c>
       <c r="N927" s="3" t="s">
         <v>449</v>
@@ -44780,7 +44780,7 @@
         <v>1</v>
       </c>
       <c r="M928" s="22">
-        <v>201200132</v>
+        <v>20120132</v>
       </c>
       <c r="N928" s="3" t="s">
         <v>442</v>
@@ -44824,7 +44824,7 @@
         <v>1</v>
       </c>
       <c r="M929" s="22">
-        <v>201200133</v>
+        <v>20120133</v>
       </c>
       <c r="N929" s="3" t="s">
         <v>446</v>
@@ -44868,7 +44868,7 @@
         <v>1</v>
       </c>
       <c r="M930" s="22">
-        <v>201200144</v>
+        <v>20120144</v>
       </c>
       <c r="N930" s="3" t="s">
         <v>443</v>
@@ -44912,7 +44912,7 @@
         <v>1</v>
       </c>
       <c r="M931" s="22">
-        <v>201200148</v>
+        <v>20120148</v>
       </c>
       <c r="N931" s="3" t="s">
         <v>345</v>
@@ -44956,7 +44956,7 @@
         <v>1</v>
       </c>
       <c r="M932" s="22">
-        <v>201200145</v>
+        <v>20120145</v>
       </c>
       <c r="N932" s="3" t="s">
         <v>335</v>
@@ -45000,7 +45000,7 @@
         <v>1</v>
       </c>
       <c r="M933" s="22">
-        <v>201200149</v>
+        <v>20120149</v>
       </c>
       <c r="N933" s="3" t="s">
         <v>210</v>
@@ -45044,7 +45044,7 @@
         <v>1</v>
       </c>
       <c r="M934" s="22">
-        <v>201200153</v>
+        <v>20120153</v>
       </c>
       <c r="N934" s="3" t="s">
         <v>420</v>
@@ -45088,7 +45088,7 @@
         <v>1</v>
       </c>
       <c r="M935" s="22">
-        <v>201200156</v>
+        <v>20120156</v>
       </c>
       <c r="N935" s="3" t="s">
         <v>353</v>
@@ -45264,7 +45264,7 @@
         <v>1</v>
       </c>
       <c r="M939" s="22">
-        <v>201200111</v>
+        <v>20120111</v>
       </c>
       <c r="N939" s="3" t="s">
         <v>449</v>
@@ -45308,7 +45308,7 @@
         <v>1</v>
       </c>
       <c r="M940" s="22">
-        <v>201200133</v>
+        <v>20120133</v>
       </c>
       <c r="N940" s="3" t="s">
         <v>446</v>
@@ -45352,7 +45352,7 @@
         <v>1</v>
       </c>
       <c r="M941" s="22">
-        <v>201200144</v>
+        <v>20120144</v>
       </c>
       <c r="N941" s="3" t="s">
         <v>443</v>
@@ -45626,7 +45626,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:U947" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:U478" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="S337">
